--- a/URUVS/Datasheets/URUV/04.2024/April_RecordingData.xlsx
+++ b/URUVS/Datasheets/URUV/04.2024/April_RecordingData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="21727"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sophi\Documents\GitHub\TanakekeProject\URUVS\Datasheets\URUV\04.2024\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\swulfing\Documents\GitHub\TanakekeProject\URUVS\Datasheets\URUV\04.2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{768C7067-C855-472F-8488-532D006AF8F4}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AFD1C74-50CF-4846-A3E0-26E533A9FB95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4800" yWindow="980" windowWidth="14400" windowHeight="7270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-3840" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RecordingData_04.2024" sheetId="2" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Metadata" sheetId="6" r:id="rId3"/>
     <sheet name="LATLON" sheetId="5" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -26,6 +26,12 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -33,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="227">
   <si>
     <t>DATE</t>
   </si>
@@ -678,6 +684,42 @@
   </si>
   <si>
     <t>28/04/2024</t>
+  </si>
+  <si>
+    <t>MAXN_MUDCRAB</t>
+  </si>
+  <si>
+    <t>TIME_1STMUDCRAB</t>
+  </si>
+  <si>
+    <t>T1_MUDCRAB</t>
+  </si>
+  <si>
+    <t>MAXN_SWIMMERCRAB</t>
+  </si>
+  <si>
+    <t>TIME_1STSWIMMERCRAB</t>
+  </si>
+  <si>
+    <t>T1_SWIMMERCRAB</t>
+  </si>
+  <si>
+    <t>MAXN_ULAR</t>
+  </si>
+  <si>
+    <t>TIME_1STULAR</t>
+  </si>
+  <si>
+    <t>T1_ULAR</t>
+  </si>
+  <si>
+    <t>MAXNSHRIMP</t>
+  </si>
+  <si>
+    <t>TIME_1STSHRIMP</t>
+  </si>
+  <si>
+    <t>T1_SHRIMP</t>
   </si>
 </sst>
 </file>
@@ -979,15 +1021,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="107">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="20" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="20" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1000,8 +1042,8 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="46" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="46" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="46" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="46" fontId="0" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1012,16 +1054,15 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="46" fontId="0" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="21" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="21" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="21" fontId="0" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="46" fontId="0" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1029,13 +1070,13 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="16" fontId="0" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="0" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="20" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1044,10 +1085,10 @@
     <xf numFmtId="46" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="46" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="46" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1059,11 +1100,11 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="46" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="46" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1077,38 +1118,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="20" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="20" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="21" fontId="0" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="20" fontId="0" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="21" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="21" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="21" fontId="0" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="46" fontId="0" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="20" fontId="0" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="20" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="21" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1393,7 +1423,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAF2D75B-3330-44BB-BF8B-27BF0F133624}">
-  <dimension ref="A1:DI22"/>
+  <dimension ref="A1:DU22"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="10.453125" bestFit="1" customWidth="1"/>
@@ -1411,20 +1441,21 @@
     <col min="59" max="59" width="12.26953125" bestFit="1" customWidth="1"/>
     <col min="61" max="61" width="8.90625" bestFit="1" customWidth="1"/>
     <col min="62" max="62" width="12" bestFit="1" customWidth="1"/>
-    <col min="74" max="74" width="8.7265625" style="73"/>
-    <col min="77" max="77" width="8.7265625" style="73"/>
-    <col min="83" max="83" width="8.7265625" style="73"/>
     <col min="85" max="85" width="9.36328125" bestFit="1" customWidth="1"/>
     <col min="91" max="91" width="18.36328125" bestFit="1" customWidth="1"/>
-    <col min="96" max="96" width="8.7265625" style="102"/>
+    <col min="96" max="96" width="8.7265625" style="85"/>
     <col min="106" max="106" width="11.1796875" bestFit="1" customWidth="1"/>
     <col min="109" max="109" width="11.1796875" bestFit="1" customWidth="1"/>
     <col min="112" max="112" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="113" max="113" width="13.90625" bestFit="1" customWidth="1"/>
+    <col min="115" max="115" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="118" max="118" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="121" max="121" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="124" max="124" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="125" max="125" width="13.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:113" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="105" t="s">
+    <row r="1" spans="1:125" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="93" t="s">
         <v>212</v>
       </c>
       <c r="B1" s="3" t="s">
@@ -1439,7 +1470,7 @@
       <c r="E1" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="F1" s="75" t="s">
+      <c r="F1" s="73" t="s">
         <v>98</v>
       </c>
       <c r="G1" s="3" t="s">
@@ -1532,268 +1563,304 @@
       <c r="AJ1" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="AK1" s="60" t="s">
+      <c r="AK1" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="AL1" s="83" t="s">
+      <c r="AL1" s="81" t="s">
         <v>48</v>
       </c>
       <c r="AM1" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="AN1" s="60" t="s">
+      <c r="AN1" s="59" t="s">
         <v>67</v>
       </c>
-      <c r="AO1" s="83" t="s">
+      <c r="AO1" s="81" t="s">
         <v>55</v>
       </c>
       <c r="AP1" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="AQ1" s="60" t="s">
+      <c r="AQ1" s="59" t="s">
         <v>57</v>
       </c>
-      <c r="AR1" s="83" t="s">
+      <c r="AR1" s="81" t="s">
         <v>39</v>
       </c>
       <c r="AS1" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="AT1" s="60" t="s">
+      <c r="AT1" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="AU1" s="83" t="s">
+      <c r="AU1" s="81" t="s">
         <v>52</v>
       </c>
       <c r="AV1" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="AW1" s="60" t="s">
+      <c r="AW1" s="59" t="s">
         <v>54</v>
       </c>
-      <c r="AX1" s="83" t="s">
+      <c r="AX1" s="81" t="s">
         <v>129</v>
       </c>
       <c r="AY1" s="27" t="s">
         <v>130</v>
       </c>
-      <c r="AZ1" s="60" t="s">
+      <c r="AZ1" s="59" t="s">
         <v>131</v>
       </c>
-      <c r="BA1" s="83" t="s">
+      <c r="BA1" s="81" t="s">
         <v>205</v>
       </c>
       <c r="BB1" s="27" t="s">
         <v>206</v>
       </c>
-      <c r="BC1" s="60" t="s">
+      <c r="BC1" s="59" t="s">
         <v>207</v>
       </c>
-      <c r="BD1" s="83" t="s">
+      <c r="BD1" s="81" t="s">
         <v>36</v>
       </c>
       <c r="BE1" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="BF1" s="60" t="s">
+      <c r="BF1" s="59" t="s">
         <v>38</v>
       </c>
-      <c r="BG1" s="83" t="s">
+      <c r="BG1" s="81" t="s">
         <v>45</v>
       </c>
       <c r="BH1" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="BI1" s="60" t="s">
+      <c r="BI1" s="59" t="s">
         <v>47</v>
       </c>
-      <c r="BJ1" s="83" t="s">
+      <c r="BJ1" s="81" t="s">
         <v>42</v>
       </c>
       <c r="BK1" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="BL1" s="60" t="s">
+      <c r="BL1" s="59" t="s">
         <v>44</v>
       </c>
-      <c r="BM1" s="83" t="s">
+      <c r="BM1" s="81" t="s">
         <v>50</v>
       </c>
       <c r="BN1" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="BO1" s="60" t="s">
+      <c r="BO1" s="59" t="s">
         <v>58</v>
       </c>
-      <c r="BP1" s="83" t="s">
+      <c r="BP1" s="81" t="s">
         <v>59</v>
       </c>
       <c r="BQ1" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="BR1" s="60" t="s">
+      <c r="BR1" s="59" t="s">
         <v>61</v>
       </c>
-      <c r="BS1" s="83" t="s">
+      <c r="BS1" s="81" t="s">
         <v>62</v>
       </c>
       <c r="BT1" s="27" t="s">
         <v>63</v>
       </c>
-      <c r="BU1" s="60" t="s">
+      <c r="BU1" s="59" t="s">
         <v>64</v>
       </c>
-      <c r="BV1" s="84" t="s">
+      <c r="BV1" s="81" t="s">
         <v>65</v>
       </c>
       <c r="BW1" s="27" t="s">
         <v>211</v>
       </c>
-      <c r="BX1" s="60" t="s">
+      <c r="BX1" s="59" t="s">
         <v>66</v>
       </c>
-      <c r="BY1" s="84" t="s">
+      <c r="BY1" s="81" t="s">
         <v>117</v>
       </c>
       <c r="BZ1" s="27" t="s">
         <v>118</v>
       </c>
-      <c r="CA1" s="60" t="s">
+      <c r="CA1" s="59" t="s">
         <v>119</v>
       </c>
-      <c r="CB1" s="83" t="s">
+      <c r="CB1" s="81" t="s">
         <v>120</v>
       </c>
       <c r="CC1" s="27" t="s">
         <v>121</v>
       </c>
-      <c r="CD1" s="60" t="s">
+      <c r="CD1" s="59" t="s">
         <v>122</v>
       </c>
-      <c r="CE1" s="84" t="s">
+      <c r="CE1" s="81" t="s">
         <v>126</v>
       </c>
       <c r="CF1" s="27" t="s">
         <v>127</v>
       </c>
-      <c r="CG1" s="60" t="s">
+      <c r="CG1" s="59" t="s">
         <v>128</v>
       </c>
-      <c r="CH1" s="83" t="s">
+      <c r="CH1" s="81" t="s">
         <v>138</v>
       </c>
       <c r="CI1" s="27" t="s">
         <v>139</v>
       </c>
-      <c r="CJ1" s="60" t="s">
+      <c r="CJ1" s="59" t="s">
         <v>140</v>
       </c>
-      <c r="CK1" s="83" t="s">
+      <c r="CK1" s="81" t="s">
         <v>123</v>
       </c>
       <c r="CL1" s="27" t="s">
         <v>124</v>
       </c>
-      <c r="CM1" s="60" t="s">
+      <c r="CM1" s="59" t="s">
         <v>125</v>
       </c>
-      <c r="CN1" s="83" t="s">
+      <c r="CN1" s="81" t="s">
         <v>208</v>
       </c>
       <c r="CO1" s="27" t="s">
         <v>209</v>
       </c>
-      <c r="CP1" s="60" t="s">
+      <c r="CP1" s="59" t="s">
         <v>210</v>
       </c>
-      <c r="CQ1" s="83" t="s">
+      <c r="CQ1" s="81" t="s">
         <v>201</v>
       </c>
-      <c r="CR1" s="101" t="s">
+      <c r="CR1" s="90" t="s">
         <v>202</v>
       </c>
-      <c r="CS1" s="60" t="s">
+      <c r="CS1" s="59" t="s">
         <v>203</v>
       </c>
-      <c r="CT1" s="83" t="s">
+      <c r="CT1" s="81" t="s">
         <v>132</v>
       </c>
       <c r="CU1" s="27" t="s">
         <v>133</v>
       </c>
-      <c r="CV1" s="60" t="s">
+      <c r="CV1" s="59" t="s">
         <v>134</v>
       </c>
-      <c r="CW1" s="83" t="s">
+      <c r="CW1" s="81" t="s">
         <v>135</v>
       </c>
       <c r="CX1" s="27" t="s">
         <v>136</v>
       </c>
-      <c r="CY1" s="60" t="s">
+      <c r="CY1" s="59" t="s">
         <v>137</v>
       </c>
-      <c r="CZ1" s="83" t="s">
+      <c r="CZ1" s="81" t="s">
         <v>141</v>
       </c>
       <c r="DA1" s="27" t="s">
         <v>142</v>
       </c>
-      <c r="DB1" s="60" t="s">
+      <c r="DB1" s="59" t="s">
         <v>143</v>
       </c>
-      <c r="DC1" s="83" t="s">
+      <c r="DC1" s="81" t="s">
         <v>200</v>
       </c>
       <c r="DD1" s="27" t="s">
         <v>198</v>
       </c>
-      <c r="DE1" s="60" t="s">
+      <c r="DE1" s="59" t="s">
         <v>199</v>
       </c>
-      <c r="DF1" s="83" t="s">
+      <c r="DF1" s="81" t="s">
         <v>12</v>
       </c>
       <c r="DG1" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="DH1" s="60" t="s">
+      <c r="DH1" s="59" t="s">
         <v>33</v>
       </c>
-      <c r="DI1" s="28" t="s">
+      <c r="DI1" s="81" t="s">
+        <v>215</v>
+      </c>
+      <c r="DJ1" s="27" t="s">
+        <v>216</v>
+      </c>
+      <c r="DK1" s="59" t="s">
+        <v>217</v>
+      </c>
+      <c r="DL1" s="81" t="s">
+        <v>218</v>
+      </c>
+      <c r="DM1" s="27" t="s">
+        <v>219</v>
+      </c>
+      <c r="DN1" s="59" t="s">
+        <v>220</v>
+      </c>
+      <c r="DO1" s="81" t="s">
+        <v>224</v>
+      </c>
+      <c r="DP1" s="27" t="s">
+        <v>225</v>
+      </c>
+      <c r="DQ1" s="59" t="s">
+        <v>226</v>
+      </c>
+      <c r="DR1" s="81" t="s">
+        <v>221</v>
+      </c>
+      <c r="DS1" s="27" t="s">
+        <v>222</v>
+      </c>
+      <c r="DT1" s="59" t="s">
+        <v>223</v>
+      </c>
+      <c r="DU1" s="28" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:113" x14ac:dyDescent="0.35">
-      <c r="A2" s="95" t="s">
+    <row r="2" spans="1:125" x14ac:dyDescent="0.35">
+      <c r="A2" s="88" t="s">
         <v>213</v>
       </c>
-      <c r="B2" s="103" t="s">
+      <c r="B2" s="91" t="s">
         <v>146</v>
       </c>
-      <c r="C2" s="93" t="s">
+      <c r="C2" s="86" t="s">
         <v>147</v>
       </c>
-      <c r="D2" s="94" t="s">
+      <c r="D2" s="87" t="s">
         <v>148</v>
       </c>
-      <c r="E2" s="94">
+      <c r="E2" s="87">
         <v>4</v>
       </c>
-      <c r="F2" s="76" t="str">
+      <c r="F2" s="74" t="str">
         <f>D2&amp;""&amp;E2</f>
         <v>D4</v>
       </c>
-      <c r="G2" s="94">
+      <c r="G2" s="87">
         <v>1</v>
       </c>
-      <c r="H2" s="94">
+      <c r="H2" s="87">
         <v>12</v>
       </c>
-      <c r="I2" s="97">
+      <c r="I2" s="89">
         <v>0.51944444444444449</v>
       </c>
-      <c r="J2" s="97">
+      <c r="J2" s="89">
         <v>0.63124999999999998</v>
       </c>
       <c r="K2" s="7">
@@ -1804,35 +1871,35 @@
         <f>VLOOKUP(F2,LATLON!$A$2:$C$19,3)</f>
         <v>119.300459</v>
       </c>
-      <c r="M2" s="94">
+      <c r="M2" s="87">
         <v>30</v>
       </c>
-      <c r="N2" s="94">
+      <c r="N2" s="87">
         <v>12</v>
       </c>
-      <c r="O2" s="94" t="s">
+      <c r="O2" s="87" t="s">
         <v>155</v>
       </c>
-      <c r="P2" s="94">
+      <c r="P2" s="87">
         <v>4</v>
       </c>
       <c r="Q2" s="6">
         <f>J2-I2</f>
         <v>0.11180555555555549</v>
       </c>
-      <c r="R2" s="97" t="s">
+      <c r="R2" s="89" t="s">
         <v>177</v>
       </c>
-      <c r="S2" s="94" t="s">
+      <c r="S2" s="87" t="s">
         <v>178</v>
       </c>
-      <c r="T2" s="94">
+      <c r="T2" s="87">
         <v>0.27</v>
       </c>
-      <c r="U2" s="94" t="s">
+      <c r="U2" s="87" t="s">
         <v>148</v>
       </c>
-      <c r="V2" s="94"/>
+      <c r="V2" s="87"/>
       <c r="W2" s="19">
         <v>2.1851851851851848E-2</v>
       </c>
@@ -1881,193 +1948,225 @@
         <v>NA</v>
       </c>
       <c r="AO2" s="31"/>
-      <c r="AP2" s="57"/>
+      <c r="AP2" s="56"/>
       <c r="AQ2" s="33" t="str">
         <f t="shared" ref="AQ2:AQ13" si="2">IF(AO2=0,"NA",AP2-$AD2)</f>
         <v>NA</v>
       </c>
-      <c r="AR2" s="59"/>
-      <c r="AS2" s="58"/>
+      <c r="AR2" s="58"/>
+      <c r="AS2" s="57"/>
       <c r="AT2" s="33" t="str">
         <f t="shared" ref="AT2:AT13" si="3">IF(AR2=0,"NA",AS2-$AD2)</f>
         <v>NA</v>
       </c>
-      <c r="AU2" s="59"/>
-      <c r="AV2" s="58"/>
+      <c r="AU2" s="58"/>
+      <c r="AV2" s="57"/>
       <c r="AW2" s="33" t="str">
         <f t="shared" ref="AW2:AW13" si="4">IF(AU2=0,"NA",AV2-$AD2)</f>
         <v>NA</v>
       </c>
-      <c r="AX2" s="59"/>
-      <c r="AY2" s="58"/>
+      <c r="AX2" s="58"/>
+      <c r="AY2" s="57"/>
       <c r="AZ2" s="33" t="str">
         <f t="shared" ref="AZ2:AZ22" si="5">IF(AX2=0,"NA",AY2-$AD2)</f>
         <v>NA</v>
       </c>
-      <c r="BA2" s="59"/>
-      <c r="BB2" s="58"/>
+      <c r="BA2" s="58"/>
+      <c r="BB2" s="57"/>
       <c r="BC2" s="33" t="str">
         <f t="shared" ref="BC2:BC22" si="6">IF(BA2=0,"NA",BB2-$AD2)</f>
         <v>NA</v>
       </c>
-      <c r="BD2" s="59"/>
-      <c r="BE2" s="58"/>
+      <c r="BD2" s="58"/>
+      <c r="BE2" s="57"/>
       <c r="BF2" s="33" t="str">
         <f t="shared" ref="BF2:BF13" si="7">IF(BD2=0,"NA",BE2-$AD2)</f>
         <v>NA</v>
       </c>
-      <c r="BG2" s="59"/>
-      <c r="BH2" s="58"/>
+      <c r="BG2" s="58"/>
+      <c r="BH2" s="57"/>
       <c r="BI2" s="33" t="str">
         <f t="shared" ref="BI2:BI13" si="8">IF(BG2=0,"NA",BH2-$AD2)</f>
         <v>NA</v>
       </c>
-      <c r="BJ2" s="59"/>
-      <c r="BK2" s="58"/>
+      <c r="BJ2" s="58"/>
+      <c r="BK2" s="57"/>
       <c r="BL2" s="33" t="str">
         <f t="shared" ref="BL2:BL13" si="9">IF(BJ2=0,"NA",BK2-$AD2)</f>
         <v>NA</v>
       </c>
-      <c r="BM2" s="59">
-        <v>10</v>
-      </c>
-      <c r="BN2" s="72">
+      <c r="BM2" s="58">
+        <v>4</v>
+      </c>
+      <c r="BN2" s="71">
         <v>8.8310185185185176E-3</v>
       </c>
       <c r="BO2" s="33">
         <f t="shared" ref="BO2:BO13" si="10">IF(BM2=0,"NA",BN2-$AD2)</f>
         <v>5.0347222222222217E-3</v>
       </c>
-      <c r="BP2" s="59"/>
-      <c r="BQ2" s="58"/>
+      <c r="BP2" s="58"/>
+      <c r="BQ2" s="57"/>
       <c r="BR2" s="33" t="str">
         <f t="shared" ref="BR2:BR13" si="11">IF(BP2=0,"NA",BQ2-$AD2)</f>
         <v>NA</v>
       </c>
-      <c r="BS2" s="59"/>
-      <c r="BT2" s="58"/>
+      <c r="BS2" s="58"/>
+      <c r="BT2" s="57"/>
       <c r="BU2" s="33" t="str">
         <f t="shared" ref="BU2:BU13" si="12">IF(BS2=0,"NA",BT2-$AD2)</f>
         <v>NA</v>
       </c>
-      <c r="BV2" s="99"/>
-      <c r="BW2" s="74"/>
+      <c r="BV2" s="58"/>
+      <c r="BW2" s="72"/>
       <c r="BX2" s="33" t="str">
         <f t="shared" ref="BX2:BX22" si="13">IF(BV2=0,"NA",BW2-$AD2)</f>
         <v>NA</v>
       </c>
-      <c r="BY2" s="99"/>
-      <c r="BZ2" s="74"/>
+      <c r="BY2" s="58"/>
+      <c r="BZ2" s="72"/>
       <c r="CA2" s="33" t="str">
         <f t="shared" ref="CA2:CA13" si="14">IF(BY2=0,"NA",BZ2-$AD2)</f>
         <v>NA</v>
       </c>
-      <c r="CB2" s="59"/>
-      <c r="CC2" s="58"/>
+      <c r="CB2" s="58"/>
+      <c r="CC2" s="57"/>
       <c r="CD2" s="33" t="str">
         <f t="shared" ref="CD2:CD22" si="15">IF(CB2=0,"NA",CC2-$AD2)</f>
         <v>NA</v>
       </c>
-      <c r="CE2" s="41">
+      <c r="CE2" s="31">
         <v>1</v>
       </c>
-      <c r="CF2" s="57">
+      <c r="CF2" s="56">
         <v>2.1270833333333332</v>
       </c>
       <c r="CG2" s="33">
         <f t="shared" ref="CG2:CG22" si="16">IF(CE2=0,"NA",CF2-$AD2)</f>
         <v>2.1232870370370369</v>
       </c>
-      <c r="CH2" s="59"/>
-      <c r="CI2" s="72"/>
+      <c r="CH2" s="58"/>
+      <c r="CI2" s="71"/>
       <c r="CJ2" s="33" t="str">
         <f t="shared" ref="CJ2:CJ22" si="17">IF(CH2=0,"NA",CI2-$AD2)</f>
         <v>NA</v>
       </c>
-      <c r="CK2" s="59"/>
-      <c r="CL2" s="72"/>
+      <c r="CK2" s="58"/>
+      <c r="CL2" s="71"/>
       <c r="CM2" s="33" t="str">
         <f t="shared" ref="CM2:CM22" si="18">IF(CK2=0,"NA",CL2-$AD2)</f>
         <v>NA</v>
       </c>
-      <c r="CN2" s="59"/>
-      <c r="CO2" s="72"/>
+      <c r="CN2" s="58"/>
+      <c r="CO2" s="71"/>
       <c r="CP2" s="33" t="str">
         <f t="shared" ref="CP2:CP22" si="19">IF(CN2=0,"NA",CO2-$AD2)</f>
         <v>NA</v>
       </c>
-      <c r="CQ2" s="59"/>
-      <c r="CR2" s="72"/>
+      <c r="CQ2" s="58"/>
+      <c r="CR2" s="71"/>
       <c r="CS2" s="33" t="str">
         <f t="shared" ref="CS2:CS22" si="20">IF(CQ2=0,"NA",CR2-$AD2)</f>
         <v>NA</v>
       </c>
-      <c r="CT2" s="59"/>
-      <c r="CU2" s="72"/>
+      <c r="CT2" s="58"/>
+      <c r="CU2" s="71"/>
       <c r="CV2" s="33" t="str">
         <f t="shared" ref="CV2:CV22" si="21">IF(CT2=0,"NA",CU2-$AD2)</f>
         <v>NA</v>
       </c>
-      <c r="CW2" s="59"/>
-      <c r="CX2" s="72"/>
+      <c r="CW2" s="58"/>
+      <c r="CX2" s="71"/>
       <c r="CY2" s="33" t="str">
         <f t="shared" ref="CY2:CY22" si="22">IF(CW2=0,"NA",CX2-$AD2)</f>
         <v>NA</v>
       </c>
-      <c r="CZ2" s="59"/>
-      <c r="DA2" s="72"/>
+      <c r="CZ2" s="58"/>
+      <c r="DA2" s="71"/>
       <c r="DB2" s="33" t="str">
         <f t="shared" ref="DB2:DB22" si="23">IF(CZ2=0,"NA",DA2-$AD2)</f>
         <v>NA</v>
       </c>
-      <c r="DC2" s="59"/>
-      <c r="DD2" s="72"/>
+      <c r="DC2" s="58"/>
+      <c r="DD2" s="71"/>
       <c r="DE2" s="33" t="str">
         <f t="shared" ref="DE2:DE22" si="24">IF(DC2=0,"NA",DD2-$AD2)</f>
         <v>NA</v>
       </c>
-      <c r="DF2" s="59">
+      <c r="DF2" s="58">
         <v>3</v>
       </c>
-      <c r="DG2" s="72">
-        <v>2.2129629629629628E-2</v>
+      <c r="DG2" s="71">
+        <v>3.8541666666666668E-3</v>
       </c>
       <c r="DH2" s="33">
-        <f t="shared" ref="DH2:DH13" si="25">IF(DF2=0,"NA",DG2-$AD2)</f>
-        <v>1.833333333333333E-2</v>
-      </c>
-      <c r="DI2" s="35"/>
+        <f t="shared" ref="DH2:DH22" si="25">IF(DF2=0,"NA",DG2-$AD2)</f>
+        <v>5.7870370370370454E-5</v>
+      </c>
+      <c r="DI2" s="58">
+        <v>1</v>
+      </c>
+      <c r="DJ2" s="71">
+        <v>1.8194444444444444E-2</v>
+      </c>
+      <c r="DK2" s="33">
+        <f t="shared" ref="DK2:DK22" si="26">IF(DI2=0,"NA",DJ2-$AD2)</f>
+        <v>1.4398148148148148E-2</v>
+      </c>
+      <c r="DL2" s="58">
+        <v>1</v>
+      </c>
+      <c r="DM2" s="71">
+        <v>6.851851851851852E-3</v>
+      </c>
+      <c r="DN2" s="33">
+        <f t="shared" ref="DN2:DN22" si="27">IF(DL2=0,"NA",DM2-$AD2)</f>
+        <v>3.0555555555555557E-3</v>
+      </c>
+      <c r="DO2" s="58"/>
+      <c r="DP2" s="71"/>
+      <c r="DQ2" s="33" t="str">
+        <f t="shared" ref="DQ2:DQ22" si="28">IF(DO2=0,"NA",DP2-$AD2)</f>
+        <v>NA</v>
+      </c>
+      <c r="DR2" s="58"/>
+      <c r="DS2" s="71"/>
+      <c r="DT2" s="33" t="str">
+        <f t="shared" ref="DT2:DT13" si="29">IF(DR2=0,"NA",DS2-$AD2)</f>
+        <v>NA</v>
+      </c>
+      <c r="DU2" s="35"/>
     </row>
-    <row r="3" spans="1:113" x14ac:dyDescent="0.35">
-      <c r="A3" s="95" t="s">
+    <row r="3" spans="1:125" x14ac:dyDescent="0.35">
+      <c r="A3" s="88" t="s">
         <v>213</v>
       </c>
-      <c r="B3" s="104" t="s">
+      <c r="B3" s="92" t="s">
         <v>146</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="D3" s="96" t="s">
+      <c r="D3" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="E3" s="96">
+      <c r="E3" s="5">
         <v>6</v>
       </c>
-      <c r="F3" s="76" t="str">
-        <f t="shared" ref="F3:F22" si="26">D3&amp;""&amp;E3</f>
+      <c r="F3" s="74" t="str">
+        <f t="shared" ref="F3:F22" si="30">D3&amp;""&amp;E3</f>
         <v>L6</v>
       </c>
-      <c r="G3" s="96">
+      <c r="G3" s="5">
         <v>2</v>
       </c>
-      <c r="H3" s="96">
+      <c r="H3" s="5">
         <v>1</v>
       </c>
-      <c r="I3" s="98">
+      <c r="I3" s="6">
         <v>0.53541666666666665</v>
       </c>
-      <c r="J3" s="98">
+      <c r="J3" s="6">
         <v>0.63124999999999998</v>
       </c>
       <c r="K3" s="7">
@@ -2078,35 +2177,35 @@
         <f>VLOOKUP(F3,LATLON!$A$2:$C$19,3)</f>
         <v>119.300428</v>
       </c>
-      <c r="M3" s="96">
+      <c r="M3" s="5">
         <v>31</v>
       </c>
-      <c r="N3" s="96">
+      <c r="N3" s="5">
         <v>18</v>
       </c>
-      <c r="O3" s="96" t="s">
+      <c r="O3" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="P3" s="96">
+      <c r="P3" s="5">
         <v>4</v>
       </c>
       <c r="Q3" s="6">
-        <f t="shared" ref="Q3:Q22" si="27">J3-I3</f>
+        <f t="shared" ref="Q3:Q22" si="31">J3-I3</f>
         <v>9.5833333333333326E-2</v>
       </c>
-      <c r="R3" s="98" t="s">
+      <c r="R3" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="S3" s="96" t="s">
+      <c r="S3" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="T3" s="96">
+      <c r="T3" s="5">
         <v>0.26</v>
       </c>
-      <c r="U3" s="96" t="s">
+      <c r="U3" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="V3" s="96"/>
+      <c r="V3" s="5"/>
       <c r="W3" s="19">
         <v>1.9803240740740739E-2</v>
       </c>
@@ -2120,7 +2219,7 @@
       <c r="AA3" s="20"/>
       <c r="AB3" s="20"/>
       <c r="AC3" s="20">
-        <f t="shared" ref="AC3:AC22" si="28">SUM(W3:AB3)</f>
+        <f t="shared" ref="AC3:AC22" si="32">SUM(W3:AB3)</f>
         <v>6.008101851851852E-2</v>
       </c>
       <c r="AD3" s="20">
@@ -2141,10 +2240,10 @@
       </c>
       <c r="AI3" s="22"/>
       <c r="AJ3" s="29">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AK3" s="30">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL3" s="31">
         <v>1</v>
@@ -2226,13 +2325,13 @@
         <f t="shared" si="12"/>
         <v>NA</v>
       </c>
-      <c r="BV3" s="41"/>
+      <c r="BV3" s="31"/>
       <c r="BW3" s="32"/>
       <c r="BX3" s="33" t="str">
         <f t="shared" si="13"/>
         <v>NA</v>
       </c>
-      <c r="BY3" s="41"/>
+      <c r="BY3" s="31"/>
       <c r="BZ3" s="32"/>
       <c r="CA3" s="33" t="str">
         <f t="shared" si="14"/>
@@ -2244,8 +2343,8 @@
         <f t="shared" si="15"/>
         <v>NA</v>
       </c>
-      <c r="CE3" s="41"/>
-      <c r="CF3" s="57"/>
+      <c r="CE3" s="31"/>
+      <c r="CF3" s="56"/>
       <c r="CG3" s="33" t="str">
         <f t="shared" si="16"/>
         <v>NA</v>
@@ -2312,38 +2411,66 @@
         <f t="shared" si="25"/>
         <v>4.0509259259259231E-4</v>
       </c>
-      <c r="DI3" s="35"/>
+      <c r="DI3" s="31"/>
+      <c r="DJ3" s="34"/>
+      <c r="DK3" s="33" t="str">
+        <f t="shared" si="26"/>
+        <v>NA</v>
+      </c>
+      <c r="DL3" s="31"/>
+      <c r="DM3" s="34"/>
+      <c r="DN3" s="33" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DO3" s="31"/>
+      <c r="DP3" s="34"/>
+      <c r="DQ3" s="33" t="str">
+        <f t="shared" si="28"/>
+        <v>NA</v>
+      </c>
+      <c r="DR3" s="31">
+        <v>1</v>
+      </c>
+      <c r="DS3" s="34">
+        <v>1.4409722222222223E-2</v>
+      </c>
+      <c r="DT3" s="33">
+        <f t="shared" si="29"/>
+        <v>1.0405092592592594E-2</v>
+      </c>
+      <c r="DU3" s="35"/>
     </row>
-    <row r="4" spans="1:113" x14ac:dyDescent="0.35">
-      <c r="A4" s="95" t="s">
+    <row r="4" spans="1:125" x14ac:dyDescent="0.35">
+      <c r="A4" s="88" t="s">
         <v>213</v>
       </c>
-      <c r="B4" s="104" t="s">
+      <c r="B4" s="92" t="s">
         <v>146</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="D4" s="96" t="s">
+      <c r="D4" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="E4" s="96">
+      <c r="E4" s="5">
         <v>5</v>
       </c>
-      <c r="F4" s="76" t="str">
-        <f t="shared" si="26"/>
+      <c r="F4" s="74" t="str">
+        <f t="shared" si="30"/>
         <v>L5</v>
       </c>
-      <c r="G4" s="96">
+      <c r="G4" s="5">
         <v>3</v>
       </c>
-      <c r="H4" s="96">
+      <c r="H4" s="5">
         <v>11</v>
       </c>
-      <c r="I4" s="98">
+      <c r="I4" s="6">
         <v>0.54583333333333328</v>
       </c>
-      <c r="J4" s="98">
+      <c r="J4" s="6">
         <v>0.625</v>
       </c>
       <c r="K4" s="7">
@@ -2354,35 +2481,35 @@
         <f>VLOOKUP(F4,LATLON!$A$2:$C$19,3)</f>
         <v>119.301957</v>
       </c>
-      <c r="M4" s="96">
+      <c r="M4" s="5">
         <v>19</v>
       </c>
-      <c r="N4" s="96">
+      <c r="N4" s="5">
         <v>5</v>
       </c>
-      <c r="O4" s="96" t="s">
+      <c r="O4" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="P4" s="96">
+      <c r="P4" s="5">
         <v>3</v>
       </c>
       <c r="Q4" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>7.9166666666666718E-2</v>
       </c>
-      <c r="R4" s="98" t="s">
+      <c r="R4" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="S4" s="96" t="s">
+      <c r="S4" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="T4" s="96">
+      <c r="T4" s="5">
         <v>0.26</v>
       </c>
-      <c r="U4" s="96" t="s">
+      <c r="U4" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="V4" s="96" t="s">
+      <c r="V4" s="5" t="s">
         <v>181</v>
       </c>
       <c r="W4" s="19"/>
@@ -2392,7 +2519,7 @@
       <c r="AA4" s="20"/>
       <c r="AB4" s="20"/>
       <c r="AC4" s="20">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="AD4" s="20"/>
@@ -2478,13 +2605,13 @@
         <f t="shared" si="12"/>
         <v>NA</v>
       </c>
-      <c r="BV4" s="41"/>
+      <c r="BV4" s="31"/>
       <c r="BW4" s="32"/>
       <c r="BX4" s="33" t="str">
         <f t="shared" si="13"/>
         <v>NA</v>
       </c>
-      <c r="BY4" s="41"/>
+      <c r="BY4" s="31"/>
       <c r="BZ4" s="32"/>
       <c r="CA4" s="33" t="str">
         <f t="shared" si="14"/>
@@ -2496,8 +2623,8 @@
         <f t="shared" si="15"/>
         <v>NA</v>
       </c>
-      <c r="CE4" s="41"/>
-      <c r="CF4" s="57"/>
+      <c r="CE4" s="31"/>
+      <c r="CF4" s="56"/>
       <c r="CG4" s="33" t="str">
         <f t="shared" si="16"/>
         <v>NA</v>
@@ -2556,38 +2683,62 @@
         <f t="shared" si="25"/>
         <v>NA</v>
       </c>
-      <c r="DI4" s="35"/>
+      <c r="DI4" s="31"/>
+      <c r="DJ4" s="34"/>
+      <c r="DK4" s="33" t="str">
+        <f t="shared" si="26"/>
+        <v>NA</v>
+      </c>
+      <c r="DL4" s="31"/>
+      <c r="DM4" s="34"/>
+      <c r="DN4" s="33" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DO4" s="31"/>
+      <c r="DP4" s="34"/>
+      <c r="DQ4" s="33" t="str">
+        <f t="shared" si="28"/>
+        <v>NA</v>
+      </c>
+      <c r="DR4" s="31"/>
+      <c r="DS4" s="34"/>
+      <c r="DT4" s="33" t="str">
+        <f t="shared" si="29"/>
+        <v>NA</v>
+      </c>
+      <c r="DU4" s="35"/>
     </row>
-    <row r="5" spans="1:113" x14ac:dyDescent="0.35">
-      <c r="A5" s="95" t="s">
+    <row r="5" spans="1:125" x14ac:dyDescent="0.35">
+      <c r="A5" s="88" t="s">
         <v>213</v>
       </c>
-      <c r="B5" s="104" t="s">
+      <c r="B5" s="92" t="s">
         <v>146</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="D5" s="96" t="s">
+      <c r="D5" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="E5" s="96">
+      <c r="E5" s="5">
         <v>5</v>
       </c>
-      <c r="F5" s="76" t="str">
-        <f t="shared" si="26"/>
+      <c r="F5" s="74" t="str">
+        <f t="shared" si="30"/>
         <v>D5</v>
       </c>
-      <c r="G5" s="96">
+      <c r="G5" s="5">
         <v>4</v>
       </c>
-      <c r="H5" s="96" t="s">
+      <c r="H5" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="I5" s="98">
+      <c r="I5" s="6">
         <v>0.54166666666666663</v>
       </c>
-      <c r="J5" s="98">
+      <c r="J5" s="6">
         <v>0.625</v>
       </c>
       <c r="K5" s="7">
@@ -2598,35 +2749,35 @@
         <f>VLOOKUP(F5,LATLON!$A$2:$C$19,3)</f>
         <v>119.30207900000001</v>
       </c>
-      <c r="M5" s="96">
+      <c r="M5" s="5">
         <v>21</v>
       </c>
-      <c r="N5" s="96">
+      <c r="N5" s="5">
         <v>8</v>
       </c>
-      <c r="O5" s="96" t="s">
+      <c r="O5" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="P5" s="96">
+      <c r="P5" s="5">
         <v>4</v>
       </c>
       <c r="Q5" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>8.333333333333337E-2</v>
       </c>
-      <c r="R5" s="98" t="s">
+      <c r="R5" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="S5" s="96" t="s">
+      <c r="S5" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="T5" s="96">
+      <c r="T5" s="5">
         <v>0.26</v>
       </c>
-      <c r="U5" s="96" t="s">
+      <c r="U5" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="V5" s="96" t="s">
+      <c r="V5" s="5" t="s">
         <v>181</v>
       </c>
       <c r="W5" s="19"/>
@@ -2636,7 +2787,7 @@
       <c r="AA5" s="20"/>
       <c r="AB5" s="20"/>
       <c r="AC5" s="20">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="AD5" s="20"/>
@@ -2722,13 +2873,13 @@
         <f t="shared" si="12"/>
         <v>NA</v>
       </c>
-      <c r="BV5" s="41"/>
+      <c r="BV5" s="31"/>
       <c r="BW5" s="32"/>
       <c r="BX5" s="33" t="str">
         <f t="shared" si="13"/>
         <v>NA</v>
       </c>
-      <c r="BY5" s="41"/>
+      <c r="BY5" s="31"/>
       <c r="BZ5" s="32"/>
       <c r="CA5" s="33" t="str">
         <f t="shared" si="14"/>
@@ -2740,8 +2891,8 @@
         <f t="shared" si="15"/>
         <v>NA</v>
       </c>
-      <c r="CE5" s="41"/>
-      <c r="CF5" s="57"/>
+      <c r="CE5" s="31"/>
+      <c r="CF5" s="56"/>
       <c r="CG5" s="33" t="str">
         <f t="shared" si="16"/>
         <v>NA</v>
@@ -2800,38 +2951,62 @@
         <f t="shared" si="25"/>
         <v>NA</v>
       </c>
-      <c r="DI5" s="35"/>
+      <c r="DI5" s="31"/>
+      <c r="DJ5" s="32"/>
+      <c r="DK5" s="33" t="str">
+        <f t="shared" si="26"/>
+        <v>NA</v>
+      </c>
+      <c r="DL5" s="31"/>
+      <c r="DM5" s="32"/>
+      <c r="DN5" s="33" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DO5" s="31"/>
+      <c r="DP5" s="32"/>
+      <c r="DQ5" s="33" t="str">
+        <f t="shared" si="28"/>
+        <v>NA</v>
+      </c>
+      <c r="DR5" s="31"/>
+      <c r="DS5" s="32"/>
+      <c r="DT5" s="33" t="str">
+        <f t="shared" si="29"/>
+        <v>NA</v>
+      </c>
+      <c r="DU5" s="35"/>
     </row>
-    <row r="6" spans="1:113" x14ac:dyDescent="0.35">
-      <c r="A6" s="95" t="s">
+    <row r="6" spans="1:125" x14ac:dyDescent="0.35">
+      <c r="A6" s="88" t="s">
         <v>213</v>
       </c>
-      <c r="B6" s="104" t="s">
+      <c r="B6" s="92" t="s">
         <v>146</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="D6" s="96" t="s">
+      <c r="D6" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="E6" s="96">
+      <c r="E6" s="5">
         <v>4</v>
       </c>
-      <c r="F6" s="76" t="str">
-        <f t="shared" si="26"/>
+      <c r="F6" s="74" t="str">
+        <f t="shared" si="30"/>
         <v>L4</v>
       </c>
-      <c r="G6" s="96">
+      <c r="G6" s="5">
         <v>5</v>
       </c>
-      <c r="H6" s="96">
+      <c r="H6" s="5">
         <v>5</v>
       </c>
-      <c r="I6" s="98">
+      <c r="I6" s="6">
         <v>0.55694444444444446</v>
       </c>
-      <c r="J6" s="98">
+      <c r="J6" s="6">
         <v>0.61875000000000002</v>
       </c>
       <c r="K6" s="7">
@@ -2842,35 +3017,35 @@
         <f>VLOOKUP(F6,LATLON!$A$2:$C$19,3)</f>
         <v>119.30229</v>
       </c>
-      <c r="M6" s="96">
+      <c r="M6" s="5">
         <v>30</v>
       </c>
-      <c r="N6" s="96">
+      <c r="N6" s="5">
         <v>18</v>
       </c>
-      <c r="O6" s="96" t="s">
+      <c r="O6" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="P6" s="96">
+      <c r="P6" s="5">
         <v>2</v>
       </c>
       <c r="Q6" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>6.1805555555555558E-2</v>
       </c>
-      <c r="R6" s="98" t="s">
+      <c r="R6" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="S6" s="96" t="s">
+      <c r="S6" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="T6" s="96">
+      <c r="T6" s="5">
         <v>0.24</v>
       </c>
-      <c r="U6" s="96" t="s">
+      <c r="U6" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="V6" s="96"/>
+      <c r="V6" s="5"/>
       <c r="W6" s="19">
         <v>2.2789351851851852E-2</v>
       </c>
@@ -2882,7 +3057,7 @@
       <c r="AA6" s="20"/>
       <c r="AB6" s="20"/>
       <c r="AC6" s="20">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>4.2187500000000003E-2</v>
       </c>
       <c r="AD6" s="20">
@@ -2982,13 +3157,13 @@
         <f t="shared" si="12"/>
         <v>NA</v>
       </c>
-      <c r="BV6" s="41"/>
+      <c r="BV6" s="31"/>
       <c r="BW6" s="32"/>
       <c r="BX6" s="33" t="str">
         <f t="shared" si="13"/>
         <v>NA</v>
       </c>
-      <c r="BY6" s="41"/>
+      <c r="BY6" s="31"/>
       <c r="BZ6" s="32"/>
       <c r="CA6" s="33" t="str">
         <f t="shared" si="14"/>
@@ -3000,8 +3175,8 @@
         <f t="shared" si="15"/>
         <v>NA</v>
       </c>
-      <c r="CE6" s="41"/>
-      <c r="CF6" s="57"/>
+      <c r="CE6" s="31"/>
+      <c r="CF6" s="56"/>
       <c r="CG6" s="33" t="str">
         <f t="shared" si="16"/>
         <v>NA</v>
@@ -3064,38 +3239,70 @@
         <f t="shared" si="25"/>
         <v>1.7361111111111223E-4</v>
       </c>
-      <c r="DI6" s="35"/>
+      <c r="DI6" s="31">
+        <v>2</v>
+      </c>
+      <c r="DJ6" s="34">
+        <v>6.5856481481481478E-3</v>
+      </c>
+      <c r="DK6" s="33">
+        <f t="shared" si="26"/>
+        <v>3.3564814814814829E-4</v>
+      </c>
+      <c r="DL6" s="31">
+        <v>1</v>
+      </c>
+      <c r="DM6" s="34">
+        <v>2.5798611111111112E-2</v>
+      </c>
+      <c r="DN6" s="33">
+        <f t="shared" si="27"/>
+        <v>1.9548611111111114E-2</v>
+      </c>
+      <c r="DO6" s="31"/>
+      <c r="DP6" s="34"/>
+      <c r="DQ6" s="33" t="str">
+        <f t="shared" si="28"/>
+        <v>NA</v>
+      </c>
+      <c r="DR6" s="31"/>
+      <c r="DS6" s="34"/>
+      <c r="DT6" s="33" t="str">
+        <f t="shared" si="29"/>
+        <v>NA</v>
+      </c>
+      <c r="DU6" s="35"/>
     </row>
-    <row r="7" spans="1:113" x14ac:dyDescent="0.35">
-      <c r="A7" s="95" t="s">
+    <row r="7" spans="1:125" x14ac:dyDescent="0.35">
+      <c r="A7" s="88" t="s">
         <v>213</v>
       </c>
-      <c r="B7" s="104" t="s">
+      <c r="B7" s="92" t="s">
         <v>146</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="D7" s="96" t="s">
+      <c r="D7" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="E7" s="96">
+      <c r="E7" s="5">
         <v>6</v>
       </c>
-      <c r="F7" s="76" t="str">
-        <f t="shared" si="26"/>
+      <c r="F7" s="74" t="str">
+        <f t="shared" si="30"/>
         <v>D6</v>
       </c>
-      <c r="G7" s="96">
+      <c r="G7" s="5">
         <v>6</v>
       </c>
-      <c r="H7" s="96">
+      <c r="H7" s="5">
         <v>14</v>
       </c>
-      <c r="I7" s="98">
+      <c r="I7" s="6">
         <v>0.5625</v>
       </c>
-      <c r="J7" s="98">
+      <c r="J7" s="6">
         <v>0.61875000000000002</v>
       </c>
       <c r="K7" s="7">
@@ -3106,35 +3313,35 @@
         <f>VLOOKUP(F7,LATLON!$A$2:$C$19,3)</f>
         <v>119.302812</v>
       </c>
-      <c r="M7" s="96">
+      <c r="M7" s="5">
         <v>22</v>
       </c>
-      <c r="N7" s="96">
+      <c r="N7" s="5">
         <v>10</v>
       </c>
-      <c r="O7" s="96" t="s">
+      <c r="O7" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="P7" s="96">
+      <c r="P7" s="5">
         <v>3</v>
       </c>
       <c r="Q7" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>5.6250000000000022E-2</v>
       </c>
-      <c r="R7" s="98" t="s">
+      <c r="R7" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="S7" s="96" t="s">
+      <c r="S7" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="T7" s="96">
+      <c r="T7" s="5">
         <v>0.24</v>
       </c>
-      <c r="U7" s="96" t="s">
+      <c r="U7" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="V7" s="96"/>
+      <c r="V7" s="5"/>
       <c r="W7" s="19">
         <v>1.7858796296296296E-2</v>
       </c>
@@ -3148,7 +3355,7 @@
       <c r="AA7" s="20"/>
       <c r="AB7" s="20"/>
       <c r="AC7" s="20">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>4.0115740740740743E-2</v>
       </c>
       <c r="AD7" s="20">
@@ -3244,13 +3451,13 @@
         <f t="shared" si="12"/>
         <v>NA</v>
       </c>
-      <c r="BV7" s="41"/>
+      <c r="BV7" s="31"/>
       <c r="BW7" s="32"/>
       <c r="BX7" s="33" t="str">
         <f t="shared" si="13"/>
         <v>NA</v>
       </c>
-      <c r="BY7" s="41"/>
+      <c r="BY7" s="31"/>
       <c r="BZ7" s="32"/>
       <c r="CA7" s="33" t="str">
         <f t="shared" si="14"/>
@@ -3262,8 +3469,8 @@
         <f t="shared" si="15"/>
         <v>NA</v>
       </c>
-      <c r="CE7" s="41"/>
-      <c r="CF7" s="57"/>
+      <c r="CE7" s="31"/>
+      <c r="CF7" s="56"/>
       <c r="CG7" s="33" t="str">
         <f t="shared" si="16"/>
         <v>NA</v>
@@ -3330,10 +3537,42 @@
         <f t="shared" si="25"/>
         <v>1.8865740740740744E-3</v>
       </c>
-      <c r="DI7" s="35"/>
+      <c r="DI7" s="31">
+        <v>1</v>
+      </c>
+      <c r="DJ7" s="34">
+        <v>1.0138888888888888E-2</v>
+      </c>
+      <c r="DK7" s="33">
+        <f t="shared" si="26"/>
+        <v>6.1111111111111106E-3</v>
+      </c>
+      <c r="DL7" s="31"/>
+      <c r="DM7" s="34"/>
+      <c r="DN7" s="33" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DO7" s="31">
+        <v>1</v>
+      </c>
+      <c r="DP7" s="34">
+        <v>1.7407407407407406E-2</v>
+      </c>
+      <c r="DQ7" s="33">
+        <f t="shared" si="28"/>
+        <v>1.3379629629629628E-2</v>
+      </c>
+      <c r="DR7" s="31"/>
+      <c r="DS7" s="34"/>
+      <c r="DT7" s="33" t="str">
+        <f t="shared" si="29"/>
+        <v>NA</v>
+      </c>
+      <c r="DU7" s="35"/>
     </row>
-    <row r="8" spans="1:113" x14ac:dyDescent="0.35">
-      <c r="A8" s="95" t="s">
+    <row r="8" spans="1:125" x14ac:dyDescent="0.35">
+      <c r="A8" s="88" t="s">
         <v>213</v>
       </c>
       <c r="B8" s="8" t="s">
@@ -3342,26 +3581,26 @@
       <c r="C8" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="D8" s="96" t="s">
+      <c r="D8" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="E8" s="96">
+      <c r="E8" s="5">
         <v>5</v>
       </c>
-      <c r="F8" s="76" t="str">
-        <f t="shared" si="26"/>
+      <c r="F8" s="74" t="str">
+        <f t="shared" si="30"/>
         <v>D5</v>
       </c>
-      <c r="G8" s="96">
+      <c r="G8" s="5">
         <v>1</v>
       </c>
-      <c r="H8" s="96">
+      <c r="H8" s="5">
         <v>11</v>
       </c>
-      <c r="I8" s="98">
+      <c r="I8" s="6">
         <v>0.4201388888888889</v>
       </c>
-      <c r="J8" s="98">
+      <c r="J8" s="6">
         <v>0.69027777777777777</v>
       </c>
       <c r="K8" s="7">
@@ -3372,35 +3611,35 @@
         <f>VLOOKUP(F8,LATLON!$A$2:$C$19,3)</f>
         <v>119.30207900000001</v>
       </c>
-      <c r="M8" s="96">
+      <c r="M8" s="5">
         <v>29</v>
       </c>
-      <c r="N8" s="96" t="s">
+      <c r="N8" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="O8" s="96" t="s">
+      <c r="O8" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="P8" s="96">
+      <c r="P8" s="5">
         <v>3</v>
       </c>
       <c r="Q8" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>0.27013888888888887</v>
       </c>
-      <c r="R8" s="98" t="s">
+      <c r="R8" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="S8" s="96" t="s">
+      <c r="S8" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="T8" s="96">
+      <c r="T8" s="5">
         <v>0.21</v>
       </c>
-      <c r="U8" s="96" t="s">
+      <c r="U8" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="V8" s="96" t="s">
+      <c r="V8" s="5" t="s">
         <v>187</v>
       </c>
       <c r="W8" s="19">
@@ -3416,7 +3655,7 @@
       <c r="AA8" s="20"/>
       <c r="AB8" s="20"/>
       <c r="AC8" s="20">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>4.4374999999999998E-2</v>
       </c>
       <c r="AD8" s="20">
@@ -3435,25 +3674,21 @@
       </c>
       <c r="AI8" s="22"/>
       <c r="AJ8" s="29">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AK8" s="30">
         <v>3</v>
       </c>
-      <c r="AL8" s="31">
-        <v>1</v>
-      </c>
-      <c r="AM8" s="34">
-        <v>3.3425925925925921E-2</v>
-      </c>
-      <c r="AN8" s="33">
+      <c r="AL8" s="31"/>
+      <c r="AM8" s="34"/>
+      <c r="AN8" s="33" t="str">
         <f t="shared" si="1"/>
-        <v>2.9513888888888885E-2</v>
+        <v>NA</v>
       </c>
       <c r="AO8" s="31">
         <v>1</v>
       </c>
-      <c r="AP8" s="71">
+      <c r="AP8" s="70">
         <v>3.1585648148148147E-2</v>
       </c>
       <c r="AQ8" s="33">
@@ -3520,13 +3755,13 @@
         <f t="shared" si="12"/>
         <v>NA</v>
       </c>
-      <c r="BV8" s="41"/>
+      <c r="BV8" s="31"/>
       <c r="BW8" s="32"/>
       <c r="BX8" s="33" t="str">
         <f t="shared" si="13"/>
         <v>NA</v>
       </c>
-      <c r="BY8" s="41"/>
+      <c r="BY8" s="31"/>
       <c r="BZ8" s="32"/>
       <c r="CA8" s="33" t="str">
         <f t="shared" si="14"/>
@@ -3538,8 +3773,8 @@
         <f t="shared" si="15"/>
         <v>NA</v>
       </c>
-      <c r="CE8" s="41"/>
-      <c r="CF8" s="57"/>
+      <c r="CE8" s="31"/>
+      <c r="CF8" s="56"/>
       <c r="CG8" s="33" t="str">
         <f t="shared" si="16"/>
         <v>NA</v>
@@ -3581,15 +3816,15 @@
         <v>NA</v>
       </c>
       <c r="CZ8" s="31"/>
-      <c r="DA8" s="71"/>
+      <c r="DA8" s="70"/>
       <c r="DB8" s="33" t="str">
         <f t="shared" si="23"/>
         <v>NA</v>
       </c>
       <c r="DC8" s="31">
-        <v>3</v>
-      </c>
-      <c r="DD8" s="71">
+        <v>2</v>
+      </c>
+      <c r="DD8" s="70">
         <v>4.0856481481481481E-3</v>
       </c>
       <c r="DE8" s="33">
@@ -3599,17 +3834,45 @@
       <c r="DF8" s="31">
         <v>1</v>
       </c>
-      <c r="DG8" s="71">
+      <c r="DG8" s="70">
         <v>2.6041666666666668E-2</v>
       </c>
       <c r="DH8" s="33">
         <f t="shared" si="25"/>
         <v>2.2129629629629631E-2</v>
       </c>
-      <c r="DI8" s="35"/>
+      <c r="DI8" s="31"/>
+      <c r="DJ8" s="70"/>
+      <c r="DK8" s="33" t="str">
+        <f t="shared" si="26"/>
+        <v>NA</v>
+      </c>
+      <c r="DL8" s="31">
+        <v>1</v>
+      </c>
+      <c r="DM8" s="70">
+        <v>6.9791666666666665E-3</v>
+      </c>
+      <c r="DN8" s="33">
+        <f t="shared" si="27"/>
+        <v>3.0671296296296297E-3</v>
+      </c>
+      <c r="DO8" s="31"/>
+      <c r="DP8" s="70"/>
+      <c r="DQ8" s="33" t="str">
+        <f t="shared" si="28"/>
+        <v>NA</v>
+      </c>
+      <c r="DR8" s="31"/>
+      <c r="DS8" s="70"/>
+      <c r="DT8" s="33" t="str">
+        <f t="shared" si="29"/>
+        <v>NA</v>
+      </c>
+      <c r="DU8" s="35"/>
     </row>
-    <row r="9" spans="1:113" x14ac:dyDescent="0.35">
-      <c r="A9" s="95" t="s">
+    <row r="9" spans="1:125" x14ac:dyDescent="0.35">
+      <c r="A9" s="88" t="s">
         <v>213</v>
       </c>
       <c r="B9" s="8" t="s">
@@ -3618,26 +3881,26 @@
       <c r="C9" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="D9" s="96" t="s">
+      <c r="D9" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="E9" s="96">
+      <c r="E9" s="5">
         <v>5</v>
       </c>
-      <c r="F9" s="76" t="str">
-        <f t="shared" si="26"/>
+      <c r="F9" s="74" t="str">
+        <f t="shared" si="30"/>
         <v>L5</v>
       </c>
-      <c r="G9" s="96">
+      <c r="G9" s="5">
         <v>2</v>
       </c>
-      <c r="H9" s="96">
+      <c r="H9" s="5">
         <v>1</v>
       </c>
-      <c r="I9" s="98">
+      <c r="I9" s="6">
         <v>0.42083333333333334</v>
       </c>
-      <c r="J9" s="98">
+      <c r="J9" s="6">
         <v>0.69027777777777777</v>
       </c>
       <c r="K9" s="7">
@@ -3648,35 +3911,35 @@
         <f>VLOOKUP(F9,LATLON!$A$2:$C$19,3)</f>
         <v>119.301957</v>
       </c>
-      <c r="M9" s="96">
+      <c r="M9" s="5">
         <v>26</v>
       </c>
-      <c r="N9" s="96" t="s">
+      <c r="N9" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="O9" s="96" t="s">
+      <c r="O9" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="P9" s="96">
+      <c r="P9" s="5">
         <v>3</v>
       </c>
       <c r="Q9" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>0.26944444444444443</v>
       </c>
-      <c r="R9" s="98" t="s">
+      <c r="R9" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="S9" s="96" t="s">
+      <c r="S9" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="T9" s="96">
+      <c r="T9" s="5">
         <v>0.21</v>
       </c>
-      <c r="U9" s="96" t="s">
+      <c r="U9" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="V9" s="96" t="s">
+      <c r="V9" s="5" t="s">
         <v>189</v>
       </c>
       <c r="W9" s="19">
@@ -3692,7 +3955,7 @@
       <c r="AA9" s="20"/>
       <c r="AB9" s="20"/>
       <c r="AC9" s="20">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>6.0324074074074072E-2</v>
       </c>
       <c r="AD9" s="20">
@@ -3713,10 +3976,10 @@
       </c>
       <c r="AI9" s="22"/>
       <c r="AJ9" s="29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK9" s="30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL9" s="31"/>
       <c r="AM9" s="34"/>
@@ -3728,11 +3991,11 @@
         <v>27</v>
       </c>
       <c r="AP9" s="34">
-        <v>8.0439814814814818E-3</v>
+        <v>7.7314814814814815E-3</v>
       </c>
       <c r="AQ9" s="33">
         <f t="shared" si="2"/>
-        <v>3.4143518518518516E-3</v>
+        <v>3.1018518518518513E-3</v>
       </c>
       <c r="AR9" s="31"/>
       <c r="AS9" s="32"/>
@@ -3794,13 +4057,13 @@
         <f t="shared" si="12"/>
         <v>NA</v>
       </c>
-      <c r="BV9" s="41"/>
+      <c r="BV9" s="31"/>
       <c r="BW9" s="32"/>
       <c r="BX9" s="33" t="str">
         <f t="shared" si="13"/>
         <v>NA</v>
       </c>
-      <c r="BY9" s="41"/>
+      <c r="BY9" s="31"/>
       <c r="BZ9" s="32"/>
       <c r="CA9" s="33" t="str">
         <f t="shared" si="14"/>
@@ -3812,8 +4075,8 @@
         <f t="shared" si="15"/>
         <v>NA</v>
       </c>
-      <c r="CE9" s="41"/>
-      <c r="CF9" s="57"/>
+      <c r="CE9" s="31"/>
+      <c r="CF9" s="56"/>
       <c r="CG9" s="33" t="str">
         <f t="shared" si="16"/>
         <v>NA</v>
@@ -3855,31 +4118,71 @@
         <v>NA</v>
       </c>
       <c r="CZ9" s="31"/>
-      <c r="DA9" s="57"/>
+      <c r="DA9" s="56"/>
       <c r="DB9" s="33" t="str">
         <f t="shared" si="23"/>
         <v>NA</v>
       </c>
-      <c r="DC9" s="31"/>
-      <c r="DD9" s="57"/>
-      <c r="DE9" s="33" t="str">
+      <c r="DC9" s="31">
+        <v>2</v>
+      </c>
+      <c r="DD9" s="56">
+        <v>5.5092592592592589E-3</v>
+      </c>
+      <c r="DE9" s="33">
         <f t="shared" si="24"/>
-        <v>NA</v>
+        <v>8.7962962962962864E-4</v>
       </c>
       <c r="DF9" s="31">
-        <v>2</v>
-      </c>
-      <c r="DG9" s="57">
+        <v>3</v>
+      </c>
+      <c r="DG9" s="56">
         <v>1.7141203703703704E-2</v>
       </c>
       <c r="DH9" s="33">
         <f t="shared" si="25"/>
         <v>1.2511574074074074E-2</v>
       </c>
-      <c r="DI9" s="35"/>
+      <c r="DI9" s="31">
+        <v>3</v>
+      </c>
+      <c r="DJ9" s="56">
+        <v>4.6296296296296294E-3</v>
+      </c>
+      <c r="DK9" s="33">
+        <f t="shared" si="26"/>
+        <v>-8.6736173798840355E-19</v>
+      </c>
+      <c r="DL9" s="31">
+        <v>1</v>
+      </c>
+      <c r="DM9" s="56">
+        <v>1.9652777777777779E-2</v>
+      </c>
+      <c r="DN9" s="33">
+        <f t="shared" si="27"/>
+        <v>1.502314814814815E-2</v>
+      </c>
+      <c r="DO9" s="31">
+        <v>1</v>
+      </c>
+      <c r="DP9" s="56">
+        <v>2.4918981481481483E-2</v>
+      </c>
+      <c r="DQ9" s="33">
+        <f t="shared" si="28"/>
+        <v>2.0289351851851854E-2</v>
+      </c>
+      <c r="DR9" s="31"/>
+      <c r="DS9" s="56"/>
+      <c r="DT9" s="33" t="str">
+        <f t="shared" si="29"/>
+        <v>NA</v>
+      </c>
+      <c r="DU9" s="35"/>
     </row>
-    <row r="10" spans="1:113" x14ac:dyDescent="0.35">
-      <c r="A10" s="95" t="s">
+    <row r="10" spans="1:125" x14ac:dyDescent="0.35">
+      <c r="A10" s="88" t="s">
         <v>213</v>
       </c>
       <c r="B10" s="8" t="s">
@@ -3888,26 +4191,26 @@
       <c r="C10" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="D10" s="96" t="s">
+      <c r="D10" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="E10" s="96">
+      <c r="E10" s="5">
         <v>6</v>
       </c>
-      <c r="F10" s="76" t="str">
-        <f t="shared" si="26"/>
+      <c r="F10" s="74" t="str">
+        <f t="shared" si="30"/>
         <v>E6</v>
       </c>
-      <c r="G10" s="96">
+      <c r="G10" s="5">
         <v>3</v>
       </c>
-      <c r="H10" s="96">
+      <c r="H10" s="5">
         <v>12</v>
       </c>
-      <c r="I10" s="98">
+      <c r="I10" s="6">
         <v>0.4375</v>
       </c>
-      <c r="J10" s="98">
+      <c r="J10" s="6">
         <v>0.5131944444444444</v>
       </c>
       <c r="K10" s="7">
@@ -3918,35 +4221,35 @@
         <f>VLOOKUP(F10,LATLON!$A$2:$C$19,3)</f>
         <v>119.28802</v>
       </c>
-      <c r="M10" s="96">
+      <c r="M10" s="5">
         <v>40</v>
       </c>
-      <c r="N10" s="96">
+      <c r="N10" s="5">
         <v>37</v>
       </c>
-      <c r="O10" s="96" t="s">
+      <c r="O10" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="P10" s="96">
+      <c r="P10" s="5">
         <v>3</v>
       </c>
       <c r="Q10" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>7.5694444444444398E-2</v>
       </c>
-      <c r="R10" s="98" t="s">
+      <c r="R10" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="S10" s="96" t="s">
+      <c r="S10" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="T10" s="96">
+      <c r="T10" s="5">
         <v>0.23</v>
       </c>
-      <c r="U10" s="96" t="s">
+      <c r="U10" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="V10" s="96" t="s">
+      <c r="V10" s="5" t="s">
         <v>191</v>
       </c>
       <c r="W10" s="19"/>
@@ -3956,7 +4259,7 @@
       <c r="AA10" s="20"/>
       <c r="AB10" s="20"/>
       <c r="AC10" s="20">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="AD10" s="20"/>
@@ -4042,13 +4345,13 @@
         <f t="shared" si="12"/>
         <v>NA</v>
       </c>
-      <c r="BV10" s="41"/>
+      <c r="BV10" s="31"/>
       <c r="BW10" s="32"/>
       <c r="BX10" s="33" t="str">
         <f t="shared" si="13"/>
         <v>NA</v>
       </c>
-      <c r="BY10" s="41"/>
+      <c r="BY10" s="31"/>
       <c r="BZ10" s="32"/>
       <c r="CA10" s="33" t="str">
         <f t="shared" si="14"/>
@@ -4060,8 +4363,8 @@
         <f t="shared" si="15"/>
         <v>NA</v>
       </c>
-      <c r="CE10" s="41"/>
-      <c r="CF10" s="57"/>
+      <c r="CE10" s="31"/>
+      <c r="CF10" s="56"/>
       <c r="CG10" s="33" t="str">
         <f t="shared" si="16"/>
         <v>NA</v>
@@ -4120,10 +4423,34 @@
         <f t="shared" si="25"/>
         <v>NA</v>
       </c>
-      <c r="DI10" s="35"/>
+      <c r="DI10" s="31"/>
+      <c r="DJ10" s="34"/>
+      <c r="DK10" s="33" t="str">
+        <f t="shared" si="26"/>
+        <v>NA</v>
+      </c>
+      <c r="DL10" s="31"/>
+      <c r="DM10" s="34"/>
+      <c r="DN10" s="33" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DO10" s="31"/>
+      <c r="DP10" s="34"/>
+      <c r="DQ10" s="33" t="str">
+        <f t="shared" si="28"/>
+        <v>NA</v>
+      </c>
+      <c r="DR10" s="31"/>
+      <c r="DS10" s="34"/>
+      <c r="DT10" s="33" t="str">
+        <f t="shared" si="29"/>
+        <v>NA</v>
+      </c>
+      <c r="DU10" s="35"/>
     </row>
-    <row r="11" spans="1:113" x14ac:dyDescent="0.35">
-      <c r="A11" s="95" t="s">
+    <row r="11" spans="1:125" x14ac:dyDescent="0.35">
+      <c r="A11" s="88" t="s">
         <v>213</v>
       </c>
       <c r="B11" s="8" t="s">
@@ -4132,26 +4459,26 @@
       <c r="C11" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="D11" s="96" t="s">
+      <c r="D11" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="E11" s="96">
+      <c r="E11" s="5">
         <v>4</v>
       </c>
-      <c r="F11" s="76" t="str">
-        <f t="shared" si="26"/>
+      <c r="F11" s="74" t="str">
+        <f t="shared" si="30"/>
         <v>E4</v>
       </c>
-      <c r="G11" s="96">
+      <c r="G11" s="5">
         <v>4</v>
       </c>
-      <c r="H11" s="96" t="s">
+      <c r="H11" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="I11" s="98">
+      <c r="I11" s="6">
         <v>0.44166666666666665</v>
       </c>
-      <c r="J11" s="98">
+      <c r="J11" s="6">
         <v>0.51041666666666663</v>
       </c>
       <c r="K11" s="7">
@@ -4162,35 +4489,35 @@
         <f>VLOOKUP(F11,LATLON!$A$2:$C$19,3)</f>
         <v>119.287291</v>
       </c>
-      <c r="M11" s="96">
+      <c r="M11" s="5">
         <v>64</v>
       </c>
-      <c r="N11" s="96">
+      <c r="N11" s="5">
         <v>62</v>
       </c>
-      <c r="O11" s="96" t="s">
+      <c r="O11" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="P11" s="96">
+      <c r="P11" s="5">
         <v>4</v>
       </c>
       <c r="Q11" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>6.8749999999999978E-2</v>
       </c>
-      <c r="R11" s="98" t="s">
+      <c r="R11" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="S11" s="96" t="s">
+      <c r="S11" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="T11" s="96">
+      <c r="T11" s="5">
         <v>0.23</v>
       </c>
-      <c r="U11" s="96" t="s">
+      <c r="U11" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="V11" s="96"/>
+      <c r="V11" s="5"/>
       <c r="W11" s="19">
         <v>1.486111111111111E-2</v>
       </c>
@@ -4206,7 +4533,7 @@
       <c r="AA11" s="20"/>
       <c r="AB11" s="20"/>
       <c r="AC11" s="20">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>5.7280092592592591E-2</v>
       </c>
       <c r="AD11" s="20">
@@ -4227,7 +4554,7 @@
       </c>
       <c r="AI11" s="22"/>
       <c r="AJ11" s="29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AK11" s="30">
         <v>6</v>
@@ -4316,16 +4643,16 @@
         <f t="shared" si="12"/>
         <v>NA</v>
       </c>
-      <c r="BV11" s="41"/>
-      <c r="BW11" s="71"/>
+      <c r="BV11" s="31"/>
+      <c r="BW11" s="70"/>
       <c r="BX11" s="33" t="str">
         <f t="shared" si="13"/>
         <v>NA</v>
       </c>
-      <c r="BY11" s="41">
+      <c r="BY11" s="31">
         <v>1</v>
       </c>
-      <c r="BZ11" s="71">
+      <c r="BZ11" s="70">
         <v>4.3518518518518515E-3</v>
       </c>
       <c r="CA11" s="33">
@@ -4338,10 +4665,10 @@
         <f t="shared" si="15"/>
         <v>NA</v>
       </c>
-      <c r="CE11" s="41">
+      <c r="CE11" s="31">
         <v>1</v>
       </c>
-      <c r="CF11" s="57">
+      <c r="CF11" s="56">
         <v>4.3518518518518515E-3</v>
       </c>
       <c r="CG11" s="33">
@@ -4406,10 +4733,38 @@
         <f t="shared" si="25"/>
         <v>NA</v>
       </c>
-      <c r="DI11" s="35"/>
+      <c r="DI11" s="31"/>
+      <c r="DJ11" s="34"/>
+      <c r="DK11" s="33" t="str">
+        <f t="shared" si="26"/>
+        <v>NA</v>
+      </c>
+      <c r="DL11" s="31">
+        <v>1</v>
+      </c>
+      <c r="DM11" s="34">
+        <v>8.472222222222223E-3</v>
+      </c>
+      <c r="DN11" s="33">
+        <f t="shared" si="27"/>
+        <v>4.4907407407407413E-3</v>
+      </c>
+      <c r="DO11" s="31"/>
+      <c r="DP11" s="34"/>
+      <c r="DQ11" s="33" t="str">
+        <f t="shared" si="28"/>
+        <v>NA</v>
+      </c>
+      <c r="DR11" s="31"/>
+      <c r="DS11" s="34"/>
+      <c r="DT11" s="33" t="str">
+        <f t="shared" si="29"/>
+        <v>NA</v>
+      </c>
+      <c r="DU11" s="35"/>
     </row>
-    <row r="12" spans="1:113" x14ac:dyDescent="0.35">
-      <c r="A12" s="95" t="s">
+    <row r="12" spans="1:125" x14ac:dyDescent="0.35">
+      <c r="A12" s="88" t="s">
         <v>213</v>
       </c>
       <c r="B12" s="8" t="s">
@@ -4418,26 +4773,26 @@
       <c r="C12" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="D12" s="96" t="s">
+      <c r="D12" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="E12" s="96">
+      <c r="E12" s="5">
         <v>5</v>
       </c>
-      <c r="F12" s="76" t="str">
-        <f t="shared" si="26"/>
+      <c r="F12" s="74" t="str">
+        <f t="shared" si="30"/>
         <v>E5</v>
       </c>
-      <c r="G12" s="96">
+      <c r="G12" s="5">
         <v>5</v>
       </c>
-      <c r="H12" s="96">
+      <c r="H12" s="5">
         <v>5</v>
       </c>
-      <c r="I12" s="98">
+      <c r="I12" s="6">
         <v>0.4548611111111111</v>
       </c>
-      <c r="J12" s="98">
+      <c r="J12" s="6">
         <v>0.50347222222222221</v>
       </c>
       <c r="K12" s="7">
@@ -4448,35 +4803,35 @@
         <f>VLOOKUP(F12,LATLON!$A$2:$C$19,3)</f>
         <v>119.286874</v>
       </c>
-      <c r="M12" s="96">
+      <c r="M12" s="5">
         <v>52</v>
       </c>
-      <c r="N12" s="96">
+      <c r="N12" s="5">
         <v>52</v>
       </c>
-      <c r="O12" s="96" t="s">
+      <c r="O12" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="P12" s="96">
+      <c r="P12" s="5">
         <v>3</v>
       </c>
       <c r="Q12" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>4.8611111111111105E-2</v>
       </c>
-      <c r="R12" s="98" t="s">
+      <c r="R12" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="S12" s="96" t="s">
+      <c r="S12" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="T12" s="96">
+      <c r="T12" s="5">
         <v>0.25</v>
       </c>
-      <c r="U12" s="96" t="s">
+      <c r="U12" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="V12" s="96"/>
+      <c r="V12" s="5"/>
       <c r="W12" s="19">
         <v>1.7858796296296296E-2</v>
       </c>
@@ -4490,7 +4845,7 @@
       <c r="AA12" s="20"/>
       <c r="AB12" s="20"/>
       <c r="AC12" s="20">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>3.9143518518518522E-2</v>
       </c>
       <c r="AD12" s="20">
@@ -4594,13 +4949,13 @@
         <f t="shared" si="12"/>
         <v>NA</v>
       </c>
-      <c r="BV12" s="41"/>
+      <c r="BV12" s="31"/>
       <c r="BW12" s="32"/>
       <c r="BX12" s="33" t="str">
         <f t="shared" si="13"/>
         <v>NA</v>
       </c>
-      <c r="BY12" s="41"/>
+      <c r="BY12" s="31"/>
       <c r="BZ12" s="32"/>
       <c r="CA12" s="33" t="str">
         <f t="shared" si="14"/>
@@ -4612,26 +4967,26 @@
         <f t="shared" si="15"/>
         <v>NA</v>
       </c>
-      <c r="CE12" s="41"/>
-      <c r="CF12" s="57"/>
+      <c r="CE12" s="31"/>
+      <c r="CF12" s="56"/>
       <c r="CG12" s="33" t="str">
         <f t="shared" si="16"/>
         <v>NA</v>
       </c>
       <c r="CH12" s="31"/>
-      <c r="CI12" s="71"/>
+      <c r="CI12" s="70"/>
       <c r="CJ12" s="33" t="str">
         <f t="shared" si="17"/>
         <v>NA</v>
       </c>
       <c r="CK12" s="31"/>
-      <c r="CL12" s="71"/>
+      <c r="CL12" s="70"/>
       <c r="CM12" s="33" t="str">
         <f t="shared" si="18"/>
         <v>NA</v>
       </c>
       <c r="CN12" s="31"/>
-      <c r="CO12" s="71"/>
+      <c r="CO12" s="70"/>
       <c r="CP12" s="33" t="str">
         <f t="shared" si="19"/>
         <v>NA</v>
@@ -4647,25 +5002,25 @@
         <v>2.6087962962962966E-2</v>
       </c>
       <c r="CT12" s="31"/>
-      <c r="CU12" s="71"/>
+      <c r="CU12" s="70"/>
       <c r="CV12" s="33" t="str">
         <f t="shared" si="21"/>
         <v>NA</v>
       </c>
       <c r="CW12" s="31"/>
-      <c r="CX12" s="71"/>
+      <c r="CX12" s="70"/>
       <c r="CY12" s="33" t="str">
         <f t="shared" si="22"/>
         <v>NA</v>
       </c>
       <c r="CZ12" s="31"/>
-      <c r="DA12" s="71"/>
+      <c r="DA12" s="70"/>
       <c r="DB12" s="33" t="str">
         <f t="shared" si="23"/>
         <v>NA</v>
       </c>
       <c r="DC12" s="31"/>
-      <c r="DD12" s="71"/>
+      <c r="DD12" s="70"/>
       <c r="DE12" s="33" t="str">
         <f t="shared" si="24"/>
         <v>NA</v>
@@ -4673,17 +5028,49 @@
       <c r="DF12" s="31">
         <v>1</v>
       </c>
-      <c r="DG12" s="71">
+      <c r="DG12" s="70">
         <v>3.8657407407407408E-3</v>
       </c>
       <c r="DH12" s="33">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="DI12" s="35"/>
+      <c r="DI12" s="31"/>
+      <c r="DJ12" s="70"/>
+      <c r="DK12" s="33" t="str">
+        <f t="shared" si="26"/>
+        <v>NA</v>
+      </c>
+      <c r="DL12" s="31">
+        <v>1</v>
+      </c>
+      <c r="DM12" s="70">
+        <v>6.4351851851851853E-3</v>
+      </c>
+      <c r="DN12" s="33">
+        <f t="shared" si="27"/>
+        <v>2.5694444444444445E-3</v>
+      </c>
+      <c r="DO12" s="31">
+        <v>2</v>
+      </c>
+      <c r="DP12" s="70">
+        <v>1.5208333333333334E-2</v>
+      </c>
+      <c r="DQ12" s="33">
+        <f t="shared" si="28"/>
+        <v>1.1342592592592593E-2</v>
+      </c>
+      <c r="DR12" s="31"/>
+      <c r="DS12" s="70"/>
+      <c r="DT12" s="33" t="str">
+        <f t="shared" si="29"/>
+        <v>NA</v>
+      </c>
+      <c r="DU12" s="35"/>
     </row>
-    <row r="13" spans="1:113" x14ac:dyDescent="0.35">
-      <c r="A13" s="95" t="s">
+    <row r="13" spans="1:125" x14ac:dyDescent="0.35">
+      <c r="A13" s="88" t="s">
         <v>213</v>
       </c>
       <c r="B13" s="8" t="s">
@@ -4692,26 +5079,26 @@
       <c r="C13" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="D13" s="96" t="s">
+      <c r="D13" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="E13" s="96">
+      <c r="E13" s="5">
         <v>2</v>
       </c>
-      <c r="F13" s="76" t="str">
-        <f t="shared" si="26"/>
+      <c r="F13" s="74" t="str">
+        <f t="shared" si="30"/>
         <v>L2</v>
       </c>
-      <c r="G13" s="96">
+      <c r="G13" s="5">
         <v>1</v>
       </c>
-      <c r="H13" s="96">
+      <c r="H13" s="5">
         <v>1</v>
       </c>
-      <c r="I13" s="98">
+      <c r="I13" s="6">
         <v>0.40833333333333338</v>
       </c>
-      <c r="J13" s="98">
+      <c r="J13" s="6">
         <v>0.52638888888888891</v>
       </c>
       <c r="K13" s="7">
@@ -4722,35 +5109,35 @@
         <f>VLOOKUP(F13,LATLON!$A$2:$C$19,3)</f>
         <v>119.31211</v>
       </c>
-      <c r="M13" s="96">
+      <c r="M13" s="5">
         <v>59</v>
       </c>
-      <c r="N13" s="96">
+      <c r="N13" s="5">
         <v>50</v>
       </c>
-      <c r="O13" s="96" t="s">
+      <c r="O13" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="P13" s="96">
+      <c r="P13" s="5">
         <v>3</v>
       </c>
       <c r="Q13" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>0.11805555555555552</v>
       </c>
-      <c r="R13" s="98" t="s">
+      <c r="R13" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="S13" s="96" t="s">
+      <c r="S13" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="T13" s="96">
+      <c r="T13" s="5">
         <v>0.24</v>
       </c>
-      <c r="U13" s="96" t="s">
+      <c r="U13" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="V13" s="96"/>
+      <c r="V13" s="5"/>
       <c r="W13" s="19">
         <v>1.7858796296296296E-2</v>
       </c>
@@ -4764,7 +5151,7 @@
       <c r="AA13" s="20"/>
       <c r="AB13" s="20"/>
       <c r="AC13" s="20">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>4.4976851851851851E-2</v>
       </c>
       <c r="AD13" s="20">
@@ -4876,13 +5263,13 @@
         <f t="shared" si="12"/>
         <v>NA</v>
       </c>
-      <c r="BV13" s="41"/>
+      <c r="BV13" s="31"/>
       <c r="BW13" s="34"/>
       <c r="BX13" s="33" t="str">
         <f t="shared" si="13"/>
         <v>NA</v>
       </c>
-      <c r="BY13" s="41"/>
+      <c r="BY13" s="31"/>
       <c r="BZ13" s="34"/>
       <c r="CA13" s="33" t="str">
         <f t="shared" si="14"/>
@@ -4898,10 +5285,10 @@
         <f t="shared" si="15"/>
         <v>3.3333333333333331E-3</v>
       </c>
-      <c r="CE13" s="41">
+      <c r="CE13" s="31">
         <v>1</v>
       </c>
-      <c r="CF13" s="57">
+      <c r="CF13" s="56">
         <v>9.7916666666666655E-3</v>
       </c>
       <c r="CG13" s="33">
@@ -4957,7 +5344,7 @@
         <v>NA</v>
       </c>
       <c r="DF13" s="31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DG13" s="34">
         <v>5.6365740740740742E-3</v>
@@ -4966,10 +5353,34 @@
         <f t="shared" si="25"/>
         <v>8.1018518518518462E-5</v>
       </c>
-      <c r="DI13" s="35"/>
+      <c r="DI13" s="31"/>
+      <c r="DJ13" s="32"/>
+      <c r="DK13" s="33" t="str">
+        <f t="shared" si="26"/>
+        <v>NA</v>
+      </c>
+      <c r="DL13" s="31"/>
+      <c r="DM13" s="34"/>
+      <c r="DN13" s="33" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DO13" s="31"/>
+      <c r="DP13" s="34"/>
+      <c r="DQ13" s="33" t="str">
+        <f t="shared" si="28"/>
+        <v>NA</v>
+      </c>
+      <c r="DR13" s="31"/>
+      <c r="DS13" s="34"/>
+      <c r="DT13" s="33" t="str">
+        <f t="shared" si="29"/>
+        <v>NA</v>
+      </c>
+      <c r="DU13" s="35"/>
     </row>
-    <row r="14" spans="1:113" x14ac:dyDescent="0.35">
-      <c r="A14" s="95" t="s">
+    <row r="14" spans="1:125" x14ac:dyDescent="0.35">
+      <c r="A14" s="88" t="s">
         <v>213</v>
       </c>
       <c r="B14" s="8" t="s">
@@ -4978,26 +5389,26 @@
       <c r="C14" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="D14" s="96" t="s">
+      <c r="D14" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="E14" s="96">
+      <c r="E14" s="5">
         <v>1</v>
       </c>
-      <c r="F14" s="76" t="str">
-        <f t="shared" si="26"/>
+      <c r="F14" s="74" t="str">
+        <f t="shared" si="30"/>
         <v>L1</v>
       </c>
-      <c r="G14" s="96">
+      <c r="G14" s="5">
         <v>2</v>
       </c>
-      <c r="H14" s="96">
+      <c r="H14" s="5">
         <v>12</v>
       </c>
-      <c r="I14" s="98">
+      <c r="I14" s="6">
         <v>0.4152777777777778</v>
       </c>
-      <c r="J14" s="98">
+      <c r="J14" s="6">
         <v>0.53125</v>
       </c>
       <c r="K14" s="7">
@@ -5008,35 +5419,35 @@
         <f>VLOOKUP(F14,LATLON!$A$2:$C$19,3)</f>
         <v>119.31128099999999</v>
       </c>
-      <c r="M14" s="96">
+      <c r="M14" s="5">
         <v>58</v>
       </c>
-      <c r="N14" s="96">
+      <c r="N14" s="5">
         <v>61</v>
       </c>
-      <c r="O14" s="96" t="s">
+      <c r="O14" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="P14" s="96">
+      <c r="P14" s="5">
         <v>4</v>
       </c>
       <c r="Q14" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>0.1159722222222222</v>
       </c>
-      <c r="R14" s="98" t="s">
+      <c r="R14" s="6" t="s">
         <v>194</v>
       </c>
-      <c r="S14" s="96" t="s">
+      <c r="S14" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="T14" s="96">
+      <c r="T14" s="5">
         <v>0.24</v>
       </c>
-      <c r="U14" s="96" t="s">
+      <c r="U14" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="V14" s="96"/>
+      <c r="V14" s="5"/>
       <c r="W14" s="19">
         <v>2.0937499999999998E-2</v>
       </c>
@@ -5050,7 +5461,7 @@
       <c r="AA14" s="20"/>
       <c r="AB14" s="20"/>
       <c r="AC14" s="20">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>6.6909722222222218E-2</v>
       </c>
       <c r="AD14" s="20">
@@ -5060,7 +5471,7 @@
         <v>1.8831018518518518E-2</v>
       </c>
       <c r="AF14" s="20">
-        <f t="shared" ref="AF14:AF22" si="29">AC14-AD14-AE14</f>
+        <f t="shared" ref="AF14:AF22" si="33">AC14-AD14-AE14</f>
         <v>4.1828703703703701E-2</v>
       </c>
       <c r="AG14" s="21">
@@ -5083,25 +5494,25 @@
         <v>2.732638888888889E-2</v>
       </c>
       <c r="AN14" s="33">
-        <f t="shared" ref="AN14:AN22" si="30">IF(AL14=0,"NA",AM14-$AD14)</f>
+        <f t="shared" ref="AN14:AN22" si="34">IF(AL14=0,"NA",AM14-$AD14)</f>
         <v>2.1076388888888891E-2</v>
       </c>
       <c r="AO14" s="31"/>
       <c r="AP14" s="32"/>
       <c r="AQ14" s="33" t="str">
-        <f t="shared" ref="AQ14:AQ22" si="31">IF(AO14=0,"NA",AP14-$AD14)</f>
+        <f t="shared" ref="AQ14:AQ22" si="35">IF(AO14=0,"NA",AP14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="AR14" s="31"/>
       <c r="AS14" s="32"/>
       <c r="AT14" s="33" t="str">
-        <f t="shared" ref="AT14:AT22" si="32">IF(AR14=0,"NA",AS14-$AD14)</f>
+        <f t="shared" ref="AT14:AT22" si="36">IF(AR14=0,"NA",AS14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="AU14" s="31"/>
       <c r="AV14" s="32"/>
       <c r="AW14" s="33" t="str">
-        <f t="shared" ref="AW14:AW22" si="33">IF(AU14=0,"NA",AV14-$AD14)</f>
+        <f t="shared" ref="AW14:AW22" si="37">IF(AU14=0,"NA",AV14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="AX14" s="31"/>
@@ -5119,13 +5530,13 @@
       <c r="BD14" s="31"/>
       <c r="BE14" s="34"/>
       <c r="BF14" s="33" t="str">
-        <f t="shared" ref="BF14:BF22" si="34">IF(BD14=0,"NA",BE14-$AD14)</f>
+        <f t="shared" ref="BF14:BF22" si="38">IF(BD14=0,"NA",BE14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="BG14" s="31"/>
       <c r="BH14" s="32"/>
       <c r="BI14" s="33" t="str">
-        <f t="shared" ref="BI14:BI22" si="35">IF(BG14=0,"NA",BH14-$AD14)</f>
+        <f t="shared" ref="BI14:BI22" si="39">IF(BG14=0,"NA",BH14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="BJ14" s="31">
@@ -5135,7 +5546,7 @@
         <v>2.4201388888888887E-2</v>
       </c>
       <c r="BL14" s="33">
-        <f t="shared" ref="BL14:BL22" si="36">IF(BJ14=0,"NA",BK14-$AD14)</f>
+        <f t="shared" ref="BL14:BL22" si="40">IF(BJ14=0,"NA",BK14-$AD14)</f>
         <v>1.7951388888888888E-2</v>
       </c>
       <c r="BM14" s="31">
@@ -5145,31 +5556,31 @@
         <v>2.4131944444444445E-2</v>
       </c>
       <c r="BO14" s="33">
-        <f t="shared" ref="BO14:BO22" si="37">IF(BM14=0,"NA",BN14-$AD14)</f>
+        <f t="shared" ref="BO14:BO22" si="41">IF(BM14=0,"NA",BN14-$AD14)</f>
         <v>1.7881944444444447E-2</v>
       </c>
       <c r="BP14" s="31"/>
       <c r="BQ14" s="32"/>
       <c r="BR14" s="33" t="str">
-        <f t="shared" ref="BR14:BR22" si="38">IF(BP14=0,"NA",BQ14-$AD14)</f>
+        <f t="shared" ref="BR14:BR22" si="42">IF(BP14=0,"NA",BQ14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="BS14" s="31"/>
       <c r="BT14" s="32"/>
       <c r="BU14" s="33" t="str">
-        <f t="shared" ref="BU14:BU22" si="39">IF(BS14=0,"NA",BT14-$AD14)</f>
-        <v>NA</v>
-      </c>
-      <c r="BV14" s="41"/>
+        <f t="shared" ref="BU14:BU22" si="43">IF(BS14=0,"NA",BT14-$AD14)</f>
+        <v>NA</v>
+      </c>
+      <c r="BV14" s="31"/>
       <c r="BW14" s="34"/>
       <c r="BX14" s="33" t="str">
         <f t="shared" si="13"/>
         <v>NA</v>
       </c>
-      <c r="BY14" s="41"/>
+      <c r="BY14" s="31"/>
       <c r="BZ14" s="34"/>
       <c r="CA14" s="33" t="str">
-        <f t="shared" ref="CA14:CA22" si="40">IF(BY14=0,"NA",BZ14-$AD14)</f>
+        <f t="shared" ref="CA14:CA22" si="44">IF(BY14=0,"NA",BZ14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="CB14" s="31"/>
@@ -5178,8 +5589,8 @@
         <f t="shared" si="15"/>
         <v>NA</v>
       </c>
-      <c r="CE14" s="41"/>
-      <c r="CF14" s="57"/>
+      <c r="CE14" s="31"/>
+      <c r="CF14" s="56"/>
       <c r="CG14" s="33" t="str">
         <f t="shared" si="16"/>
         <v>NA</v>
@@ -5235,13 +5646,45 @@
       <c r="DF14" s="31"/>
       <c r="DG14" s="32"/>
       <c r="DH14" s="33" t="str">
-        <f t="shared" ref="DH14:DH22" si="41">IF(DF14=0,"NA",DG14-$AD14)</f>
-        <v>NA</v>
-      </c>
-      <c r="DI14" s="35"/>
+        <f t="shared" si="25"/>
+        <v>NA</v>
+      </c>
+      <c r="DI14" s="31">
+        <v>1</v>
+      </c>
+      <c r="DJ14" s="34">
+        <v>3.3831018518518517E-2</v>
+      </c>
+      <c r="DK14" s="33">
+        <f t="shared" si="26"/>
+        <v>2.7581018518518519E-2</v>
+      </c>
+      <c r="DL14" s="31">
+        <v>1</v>
+      </c>
+      <c r="DM14" s="34">
+        <v>1.3472222222222222E-2</v>
+      </c>
+      <c r="DN14" s="33">
+        <f t="shared" si="27"/>
+        <v>7.2222222222222228E-3</v>
+      </c>
+      <c r="DO14" s="31"/>
+      <c r="DP14" s="32"/>
+      <c r="DQ14" s="33" t="str">
+        <f t="shared" si="28"/>
+        <v>NA</v>
+      </c>
+      <c r="DR14" s="31"/>
+      <c r="DS14" s="32"/>
+      <c r="DT14" s="33" t="str">
+        <f t="shared" ref="DT14:DT22" si="45">IF(DR14=0,"NA",DS14-$AD14)</f>
+        <v>NA</v>
+      </c>
+      <c r="DU14" s="35"/>
     </row>
-    <row r="15" spans="1:113" x14ac:dyDescent="0.35">
-      <c r="A15" s="95" t="s">
+    <row r="15" spans="1:125" x14ac:dyDescent="0.35">
+      <c r="A15" s="88" t="s">
         <v>213</v>
       </c>
       <c r="B15" s="8" t="s">
@@ -5250,26 +5693,26 @@
       <c r="C15" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="D15" s="96" t="s">
+      <c r="D15" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="E15" s="96">
+      <c r="E15" s="5">
         <v>3</v>
       </c>
-      <c r="F15" s="76" t="str">
-        <f t="shared" si="26"/>
+      <c r="F15" s="74" t="str">
+        <f t="shared" si="30"/>
         <v>L3</v>
       </c>
-      <c r="G15" s="96">
+      <c r="G15" s="5">
         <v>3</v>
       </c>
-      <c r="H15" s="96">
+      <c r="H15" s="5">
         <v>11</v>
       </c>
-      <c r="I15" s="98">
+      <c r="I15" s="6">
         <v>0.42222222222222222</v>
       </c>
-      <c r="J15" s="98">
+      <c r="J15" s="6">
         <v>0.5180555555555556</v>
       </c>
       <c r="K15" s="7">
@@ -5280,35 +5723,35 @@
         <f>VLOOKUP(F15,LATLON!$A$2:$C$19,3)</f>
         <v>119.312033</v>
       </c>
-      <c r="M15" s="96">
+      <c r="M15" s="5">
         <v>52</v>
       </c>
-      <c r="N15" s="96">
+      <c r="N15" s="5">
         <v>70</v>
       </c>
-      <c r="O15" s="96" t="s">
+      <c r="O15" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="P15" s="96">
+      <c r="P15" s="5">
         <v>3</v>
       </c>
       <c r="Q15" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>9.5833333333333381E-2</v>
       </c>
-      <c r="R15" s="98" t="s">
+      <c r="R15" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="S15" s="96" t="s">
+      <c r="S15" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="T15" s="96">
+      <c r="T15" s="5">
         <v>0.24</v>
       </c>
-      <c r="U15" s="96" t="s">
+      <c r="U15" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="V15" s="96"/>
+      <c r="V15" s="5"/>
       <c r="W15" s="19">
         <v>2.1261574074074075E-2</v>
       </c>
@@ -5322,7 +5765,7 @@
       <c r="AA15" s="20"/>
       <c r="AB15" s="20"/>
       <c r="AC15" s="20">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>5.5925925925925928E-2</v>
       </c>
       <c r="AD15" s="20">
@@ -5332,10 +5775,10 @@
         <v>5.9027777777777776E-3</v>
       </c>
       <c r="AF15" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>4.5023148148148152E-2</v>
       </c>
-      <c r="AG15" s="100">
+      <c r="AG15" s="21">
         <v>80</v>
       </c>
       <c r="AH15" s="21">
@@ -5343,10 +5786,10 @@
       </c>
       <c r="AI15" s="22"/>
       <c r="AJ15" s="29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK15" s="30">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AL15" s="31">
         <v>1</v>
@@ -5355,29 +5798,29 @@
         <v>3.6354166666666667E-2</v>
       </c>
       <c r="AN15" s="33">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>3.1354166666666669E-2</v>
       </c>
       <c r="AO15" s="31">
         <v>3</v>
       </c>
       <c r="AP15" s="34">
-        <v>8.3912037037037045E-3</v>
+        <v>6.1921296296296299E-3</v>
       </c>
       <c r="AQ15" s="33">
-        <f t="shared" si="31"/>
-        <v>3.3912037037037044E-3</v>
+        <f t="shared" si="35"/>
+        <v>1.1921296296296298E-3</v>
       </c>
       <c r="AR15" s="31"/>
       <c r="AS15" s="32"/>
       <c r="AT15" s="33" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>NA</v>
       </c>
       <c r="AU15" s="31"/>
       <c r="AV15" s="32"/>
       <c r="AW15" s="33" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>NA</v>
       </c>
       <c r="AX15" s="31"/>
@@ -5395,79 +5838,79 @@
       <c r="BD15" s="31"/>
       <c r="BE15" s="32"/>
       <c r="BF15" s="33" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>NA</v>
       </c>
       <c r="BG15" s="31"/>
       <c r="BH15" s="32"/>
       <c r="BI15" s="33" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>NA</v>
       </c>
       <c r="BJ15" s="31"/>
       <c r="BK15" s="34"/>
       <c r="BL15" s="33" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>NA</v>
       </c>
       <c r="BM15" s="31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BN15" s="34">
-        <v>1.0300925925925927E-2</v>
+        <v>6.9675925925925929E-3</v>
       </c>
       <c r="BO15" s="33">
-        <f t="shared" si="37"/>
-        <v>5.3009259259259268E-3</v>
+        <f t="shared" si="41"/>
+        <v>1.9675925925925928E-3</v>
       </c>
       <c r="BP15" s="31"/>
       <c r="BQ15" s="32"/>
       <c r="BR15" s="33" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>NA</v>
       </c>
       <c r="BS15" s="31"/>
       <c r="BT15" s="32"/>
       <c r="BU15" s="33" t="str">
-        <f t="shared" si="39"/>
-        <v>NA</v>
-      </c>
-      <c r="BV15" s="41"/>
+        <f t="shared" si="43"/>
+        <v>NA</v>
+      </c>
+      <c r="BV15" s="31"/>
       <c r="BW15" s="34"/>
       <c r="BX15" s="33" t="str">
         <f t="shared" si="13"/>
         <v>NA</v>
       </c>
-      <c r="BY15" s="41">
+      <c r="BY15" s="31">
         <v>1</v>
       </c>
       <c r="BZ15" s="34">
         <v>3.8310185185185183E-2</v>
       </c>
       <c r="CA15" s="33">
-        <f t="shared" si="40"/>
+        <f t="shared" si="44"/>
         <v>3.3310185185185186E-2</v>
       </c>
       <c r="CB15" s="31"/>
-      <c r="CC15" s="71"/>
+      <c r="CC15" s="70"/>
       <c r="CD15" s="33" t="str">
         <f t="shared" si="15"/>
         <v>NA</v>
       </c>
-      <c r="CE15" s="41"/>
-      <c r="CF15" s="57"/>
+      <c r="CE15" s="31"/>
+      <c r="CF15" s="56"/>
       <c r="CG15" s="33" t="str">
         <f t="shared" si="16"/>
         <v>NA</v>
       </c>
       <c r="CH15" s="31"/>
-      <c r="CI15" s="71"/>
+      <c r="CI15" s="70"/>
       <c r="CJ15" s="33" t="str">
         <f t="shared" si="17"/>
         <v>NA</v>
       </c>
       <c r="CK15" s="31"/>
-      <c r="CL15" s="71"/>
+      <c r="CL15" s="70"/>
       <c r="CM15" s="33" t="str">
         <f t="shared" si="18"/>
         <v>NA</v>
@@ -5505,23 +5948,59 @@
       <c r="DC15" s="31">
         <v>2</v>
       </c>
-      <c r="DD15" s="71">
-        <v>8.0208333333333329E-3</v>
+      <c r="DD15" s="70">
+        <v>8.0555555555555554E-3</v>
       </c>
       <c r="DE15" s="33">
         <f t="shared" si="24"/>
-        <v>3.0208333333333328E-3</v>
-      </c>
-      <c r="DF15" s="31"/>
-      <c r="DG15" s="32"/>
-      <c r="DH15" s="33" t="str">
-        <f t="shared" si="41"/>
-        <v>NA</v>
-      </c>
-      <c r="DI15" s="35"/>
+        <v>3.0555555555555553E-3</v>
+      </c>
+      <c r="DF15" s="31">
+        <v>1</v>
+      </c>
+      <c r="DG15" s="34">
+        <v>5.9027777777777776E-3</v>
+      </c>
+      <c r="DH15" s="33">
+        <f t="shared" si="25"/>
+        <v>9.0277777777777752E-4</v>
+      </c>
+      <c r="DI15" s="31"/>
+      <c r="DJ15" s="70"/>
+      <c r="DK15" s="33" t="str">
+        <f t="shared" si="26"/>
+        <v>NA</v>
+      </c>
+      <c r="DL15" s="31"/>
+      <c r="DM15" s="32"/>
+      <c r="DN15" s="33" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DO15" s="31">
+        <v>1</v>
+      </c>
+      <c r="DP15" s="34">
+        <v>1.4907407407407407E-2</v>
+      </c>
+      <c r="DQ15" s="33">
+        <f t="shared" si="28"/>
+        <v>9.9074074074074064E-3</v>
+      </c>
+      <c r="DR15" s="31">
+        <v>1</v>
+      </c>
+      <c r="DS15" s="34">
+        <v>1.1030092592592593E-2</v>
+      </c>
+      <c r="DT15" s="33">
+        <f t="shared" si="45"/>
+        <v>6.030092592592593E-3</v>
+      </c>
+      <c r="DU15" s="35"/>
     </row>
-    <row r="16" spans="1:113" x14ac:dyDescent="0.35">
-      <c r="A16" s="95" t="s">
+    <row r="16" spans="1:125" x14ac:dyDescent="0.35">
+      <c r="A16" s="88" t="s">
         <v>213</v>
       </c>
       <c r="B16" s="8" t="s">
@@ -5530,26 +6009,26 @@
       <c r="C16" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="D16" s="96" t="s">
+      <c r="D16" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="E16" s="96">
+      <c r="E16" s="5">
         <v>1</v>
       </c>
-      <c r="F16" s="76" t="str">
-        <f t="shared" si="26"/>
+      <c r="F16" s="74" t="str">
+        <f t="shared" si="30"/>
         <v>D1</v>
       </c>
-      <c r="G16" s="96">
+      <c r="G16" s="5">
         <v>4</v>
       </c>
-      <c r="H16" s="96" t="s">
+      <c r="H16" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="I16" s="98">
+      <c r="I16" s="6">
         <v>0.42708333333333331</v>
       </c>
-      <c r="J16" s="98">
+      <c r="J16" s="6">
         <v>0.51597222222222217</v>
       </c>
       <c r="K16" s="7">
@@ -5560,35 +6039,35 @@
         <f>VLOOKUP(F16,LATLON!$A$2:$C$19,3)</f>
         <v>119.31157399999999</v>
       </c>
-      <c r="M16" s="96">
+      <c r="M16" s="5">
         <v>67</v>
       </c>
-      <c r="N16" s="96">
+      <c r="N16" s="5">
         <v>71</v>
       </c>
-      <c r="O16" s="96" t="s">
+      <c r="O16" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="P16" s="96">
+      <c r="P16" s="5">
         <v>6</v>
       </c>
       <c r="Q16" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>8.8888888888888851E-2</v>
       </c>
-      <c r="R16" s="98" t="s">
+      <c r="R16" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="S16" s="96" t="s">
+      <c r="S16" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="T16" s="96">
+      <c r="T16" s="5">
         <v>0.24</v>
       </c>
-      <c r="U16" s="96" t="s">
+      <c r="U16" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="V16" s="96"/>
+      <c r="V16" s="5"/>
       <c r="W16" s="19">
         <v>1.486111111111111E-2</v>
       </c>
@@ -5608,7 +6087,7 @@
         <v>1.486111111111111E-2</v>
       </c>
       <c r="AC16" s="20">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>8.9166666666666644E-2</v>
       </c>
       <c r="AD16" s="20">
@@ -5618,7 +6097,7 @@
         <v>4.1111111111111112E-2</v>
       </c>
       <c r="AF16" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>4.393518518518516E-2</v>
       </c>
       <c r="AG16" s="21">
@@ -5629,7 +6108,7 @@
       </c>
       <c r="AI16" s="22"/>
       <c r="AJ16" s="29">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AK16" s="30">
         <v>2</v>
@@ -5637,25 +6116,25 @@
       <c r="AL16" s="31"/>
       <c r="AM16" s="34"/>
       <c r="AN16" s="33" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>NA</v>
       </c>
       <c r="AO16" s="31"/>
       <c r="AP16" s="34"/>
       <c r="AQ16" s="33" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>NA</v>
       </c>
       <c r="AR16" s="31"/>
       <c r="AS16" s="34"/>
       <c r="AT16" s="33" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>NA</v>
       </c>
       <c r="AU16" s="31"/>
       <c r="AV16" s="34"/>
       <c r="AW16" s="33" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>NA</v>
       </c>
       <c r="AX16" s="31"/>
@@ -5673,35 +6152,35 @@
       <c r="BD16" s="31"/>
       <c r="BE16" s="34"/>
       <c r="BF16" s="33" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>NA</v>
       </c>
       <c r="BG16" s="31"/>
       <c r="BH16" s="34"/>
       <c r="BI16" s="33" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>NA</v>
       </c>
       <c r="BJ16" s="31"/>
       <c r="BK16" s="34"/>
-      <c r="BL16" s="57" t="str">
-        <f t="shared" si="36"/>
-        <v>NA</v>
-      </c>
-      <c r="BM16" s="41">
+      <c r="BL16" s="56" t="str">
+        <f t="shared" si="40"/>
+        <v>NA</v>
+      </c>
+      <c r="BM16" s="31">
         <v>10</v>
       </c>
       <c r="BN16" s="34">
         <v>4.2476851851851851E-3</v>
       </c>
       <c r="BO16" s="33">
-        <f t="shared" si="37"/>
+        <f t="shared" si="41"/>
         <v>1.2731481481481448E-4</v>
       </c>
       <c r="BP16" s="31"/>
       <c r="BQ16" s="32"/>
       <c r="BR16" s="33" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>NA</v>
       </c>
       <c r="BS16" s="31">
@@ -5711,19 +6190,19 @@
         <v>9.5486111111111101E-3</v>
       </c>
       <c r="BU16" s="33">
-        <f t="shared" si="39"/>
+        <f t="shared" si="43"/>
         <v>5.4282407407407396E-3</v>
       </c>
-      <c r="BV16" s="41"/>
-      <c r="BW16" s="57"/>
+      <c r="BV16" s="31"/>
+      <c r="BW16" s="56"/>
       <c r="BX16" s="33" t="str">
         <f t="shared" si="13"/>
         <v>NA</v>
       </c>
-      <c r="BY16" s="41"/>
-      <c r="BZ16" s="57"/>
+      <c r="BY16" s="31"/>
+      <c r="BZ16" s="56"/>
       <c r="CA16" s="33" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="44"/>
         <v>NA</v>
       </c>
       <c r="CB16" s="31"/>
@@ -5732,8 +6211,8 @@
         <f t="shared" si="15"/>
         <v>NA</v>
       </c>
-      <c r="CE16" s="41"/>
-      <c r="CF16" s="57"/>
+      <c r="CE16" s="31"/>
+      <c r="CF16" s="56"/>
       <c r="CG16" s="33" t="str">
         <f t="shared" si="16"/>
         <v>NA</v>
@@ -5789,13 +6268,45 @@
       <c r="DF16" s="31"/>
       <c r="DG16" s="34"/>
       <c r="DH16" s="33" t="str">
-        <f t="shared" si="41"/>
-        <v>NA</v>
-      </c>
-      <c r="DI16" s="35"/>
+        <f t="shared" si="25"/>
+        <v>NA</v>
+      </c>
+      <c r="DI16" s="31">
+        <v>1</v>
+      </c>
+      <c r="DJ16" s="34">
+        <v>6.2847222222222219E-3</v>
+      </c>
+      <c r="DK16" s="33">
+        <f t="shared" si="26"/>
+        <v>2.1643518518518513E-3</v>
+      </c>
+      <c r="DL16" s="31"/>
+      <c r="DM16" s="34"/>
+      <c r="DN16" s="33" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DO16" s="31">
+        <v>1</v>
+      </c>
+      <c r="DP16" s="34">
+        <v>4.4444444444444444E-3</v>
+      </c>
+      <c r="DQ16" s="33">
+        <f t="shared" si="28"/>
+        <v>3.2407407407407385E-4</v>
+      </c>
+      <c r="DR16" s="31"/>
+      <c r="DS16" s="34"/>
+      <c r="DT16" s="33" t="str">
+        <f t="shared" si="45"/>
+        <v>NA</v>
+      </c>
+      <c r="DU16" s="35"/>
     </row>
-    <row r="17" spans="1:113" x14ac:dyDescent="0.35">
-      <c r="A17" s="95" t="s">
+    <row r="17" spans="1:125" x14ac:dyDescent="0.35">
+      <c r="A17" s="88" t="s">
         <v>213</v>
       </c>
       <c r="B17" s="8" t="s">
@@ -5804,26 +6315,26 @@
       <c r="C17" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="D17" s="96" t="s">
+      <c r="D17" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="E17" s="96">
+      <c r="E17" s="5">
         <v>6</v>
       </c>
-      <c r="F17" s="76" t="str">
-        <f t="shared" si="26"/>
+      <c r="F17" s="74" t="str">
+        <f t="shared" si="30"/>
         <v>E6</v>
       </c>
-      <c r="G17" s="96">
+      <c r="G17" s="5">
         <v>5</v>
       </c>
-      <c r="H17" s="96">
+      <c r="H17" s="5">
         <v>14</v>
       </c>
-      <c r="I17" s="98">
+      <c r="I17" s="6">
         <v>0.44791666666666669</v>
       </c>
-      <c r="J17" s="98">
+      <c r="J17" s="6">
         <v>0.5</v>
       </c>
       <c r="K17" s="7">
@@ -5834,35 +6345,35 @@
         <f>VLOOKUP(F17,LATLON!$A$2:$C$19,3)</f>
         <v>119.28802</v>
       </c>
-      <c r="M17" s="96">
+      <c r="M17" s="5">
         <v>48</v>
       </c>
-      <c r="N17" s="96">
+      <c r="N17" s="5">
         <v>41</v>
       </c>
-      <c r="O17" s="96" t="s">
+      <c r="O17" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="P17" s="96">
+      <c r="P17" s="5">
         <v>3</v>
       </c>
       <c r="Q17" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>5.2083333333333315E-2</v>
       </c>
-      <c r="R17" s="98" t="s">
+      <c r="R17" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="S17" s="96" t="s">
+      <c r="S17" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="T17" s="96">
+      <c r="T17" s="5">
         <v>0.26</v>
       </c>
-      <c r="U17" s="96" t="s">
+      <c r="U17" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="V17" s="96" t="s">
+      <c r="V17" s="5" t="s">
         <v>196</v>
       </c>
       <c r="W17" s="19">
@@ -5878,7 +6389,7 @@
       <c r="AA17" s="20"/>
       <c r="AB17" s="20"/>
       <c r="AC17" s="20">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>4.4826388888888888E-2</v>
       </c>
       <c r="AD17" s="20">
@@ -5886,7 +6397,7 @@
       </c>
       <c r="AE17" s="20"/>
       <c r="AF17" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>4.1006944444444443E-2</v>
       </c>
       <c r="AG17" s="21">
@@ -5905,25 +6416,25 @@
       <c r="AL17" s="31"/>
       <c r="AM17" s="34"/>
       <c r="AN17" s="33" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>NA</v>
       </c>
       <c r="AO17" s="31"/>
       <c r="AP17" s="34"/>
       <c r="AQ17" s="33" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>NA</v>
       </c>
       <c r="AR17" s="31"/>
       <c r="AS17" s="34"/>
       <c r="AT17" s="33" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>NA</v>
       </c>
       <c r="AU17" s="31"/>
       <c r="AV17" s="34"/>
       <c r="AW17" s="33" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>NA</v>
       </c>
       <c r="AX17" s="31"/>
@@ -5945,53 +6456,53 @@
         <v>1.5416666666666667E-2</v>
       </c>
       <c r="BF17" s="33">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>1.1597222222222222E-2</v>
       </c>
       <c r="BG17" s="31"/>
       <c r="BH17" s="34"/>
       <c r="BI17" s="33" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>NA</v>
       </c>
       <c r="BJ17" s="31"/>
       <c r="BK17" s="34"/>
       <c r="BL17" s="33" t="str">
-        <f t="shared" si="36"/>
-        <v>NA</v>
-      </c>
-      <c r="BM17" s="41"/>
+        <f t="shared" si="40"/>
+        <v>NA</v>
+      </c>
+      <c r="BM17" s="31"/>
       <c r="BN17" s="34"/>
       <c r="BO17" s="33" t="str">
-        <f t="shared" si="37"/>
-        <v>NA</v>
-      </c>
-      <c r="BP17" s="41"/>
+        <f t="shared" si="41"/>
+        <v>NA</v>
+      </c>
+      <c r="BP17" s="31"/>
       <c r="BQ17" s="34"/>
       <c r="BR17" s="33" t="str">
-        <f t="shared" si="38"/>
-        <v>NA</v>
-      </c>
-      <c r="BS17" s="41"/>
+        <f t="shared" si="42"/>
+        <v>NA</v>
+      </c>
+      <c r="BS17" s="31"/>
       <c r="BT17" s="34"/>
       <c r="BU17" s="33" t="str">
-        <f t="shared" si="39"/>
-        <v>NA</v>
-      </c>
-      <c r="BV17" s="41"/>
+        <f t="shared" si="43"/>
+        <v>NA</v>
+      </c>
+      <c r="BV17" s="31"/>
       <c r="BW17" s="34"/>
       <c r="BX17" s="33" t="str">
         <f t="shared" si="13"/>
         <v>NA</v>
       </c>
-      <c r="BY17" s="41">
+      <c r="BY17" s="31">
         <v>6</v>
       </c>
       <c r="BZ17" s="34">
         <v>4.0509259259259257E-3</v>
       </c>
       <c r="CA17" s="33">
-        <f t="shared" si="40"/>
+        <f t="shared" si="44"/>
         <v>2.3148148148148138E-4</v>
       </c>
       <c r="CB17" s="31"/>
@@ -6000,8 +6511,8 @@
         <f t="shared" si="15"/>
         <v>NA</v>
       </c>
-      <c r="CE17" s="41"/>
-      <c r="CF17" s="57"/>
+      <c r="CE17" s="31"/>
+      <c r="CF17" s="56"/>
       <c r="CG17" s="33" t="str">
         <f t="shared" si="16"/>
         <v>NA</v>
@@ -6061,13 +6572,41 @@
       <c r="DF17" s="31"/>
       <c r="DG17" s="34"/>
       <c r="DH17" s="33" t="str">
-        <f t="shared" si="41"/>
-        <v>NA</v>
-      </c>
-      <c r="DI17" s="35"/>
+        <f t="shared" si="25"/>
+        <v>NA</v>
+      </c>
+      <c r="DI17" s="31"/>
+      <c r="DJ17" s="34"/>
+      <c r="DK17" s="33" t="str">
+        <f t="shared" si="26"/>
+        <v>NA</v>
+      </c>
+      <c r="DL17" s="31">
+        <v>1</v>
+      </c>
+      <c r="DM17" s="34">
+        <v>4.178240740740741E-3</v>
+      </c>
+      <c r="DN17" s="33">
+        <f t="shared" si="27"/>
+        <v>3.5879629629629673E-4</v>
+      </c>
+      <c r="DO17" s="31"/>
+      <c r="DP17" s="34"/>
+      <c r="DQ17" s="33" t="str">
+        <f t="shared" si="28"/>
+        <v>NA</v>
+      </c>
+      <c r="DR17" s="31"/>
+      <c r="DS17" s="34"/>
+      <c r="DT17" s="33" t="str">
+        <f t="shared" si="45"/>
+        <v>NA</v>
+      </c>
+      <c r="DU17" s="35"/>
     </row>
-    <row r="18" spans="1:113" x14ac:dyDescent="0.35">
-      <c r="A18" s="95" t="s">
+    <row r="18" spans="1:125" x14ac:dyDescent="0.35">
+      <c r="A18" s="88" t="s">
         <v>213</v>
       </c>
       <c r="B18" s="8" t="s">
@@ -6076,26 +6615,26 @@
       <c r="C18" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="D18" s="96" t="s">
+      <c r="D18" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="E18" s="96">
+      <c r="E18" s="5">
         <v>2</v>
       </c>
-      <c r="F18" s="76" t="str">
-        <f t="shared" si="26"/>
+      <c r="F18" s="74" t="str">
+        <f t="shared" si="30"/>
         <v>D2</v>
       </c>
-      <c r="G18" s="96">
+      <c r="G18" s="5">
         <v>1</v>
       </c>
-      <c r="H18" s="96">
+      <c r="H18" s="5">
         <v>1</v>
       </c>
-      <c r="I18" s="98">
+      <c r="I18" s="6">
         <v>0.51250000000000007</v>
       </c>
-      <c r="J18" s="98">
+      <c r="J18" s="6">
         <v>0.62777777777777777</v>
       </c>
       <c r="K18" s="7">
@@ -6106,35 +6645,35 @@
         <f>VLOOKUP(F18,LATLON!$A$2:$C$19,3)</f>
         <v>119.31312699999999</v>
       </c>
-      <c r="M18" s="96">
+      <c r="M18" s="5">
         <v>45</v>
       </c>
-      <c r="N18" s="96">
+      <c r="N18" s="5">
         <v>41</v>
       </c>
-      <c r="O18" s="96" t="s">
+      <c r="O18" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="P18" s="96">
+      <c r="P18" s="5">
         <v>3</v>
       </c>
       <c r="Q18" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>0.1152777777777777</v>
       </c>
-      <c r="R18" s="98" t="s">
+      <c r="R18" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="S18" s="96" t="s">
+      <c r="S18" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="T18" s="96">
+      <c r="T18" s="5">
         <v>0.32</v>
       </c>
-      <c r="U18" s="96" t="s">
+      <c r="U18" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="V18" s="96"/>
+      <c r="V18" s="5"/>
       <c r="W18" s="19">
         <v>2.3321759259259261E-2</v>
       </c>
@@ -6148,7 +6687,7 @@
       <c r="AA18" s="20"/>
       <c r="AB18" s="20"/>
       <c r="AC18" s="20">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>4.4664351851851851E-2</v>
       </c>
       <c r="AD18" s="20">
@@ -6156,7 +6695,7 @@
       </c>
       <c r="AE18" s="20"/>
       <c r="AF18" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>4.0497685185185185E-2</v>
       </c>
       <c r="AG18" s="21">
@@ -6175,7 +6714,7 @@
       <c r="AL18" s="31"/>
       <c r="AM18" s="34"/>
       <c r="AN18" s="33" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>NA</v>
       </c>
       <c r="AO18" s="31">
@@ -6185,19 +6724,19 @@
         <v>2.3252314814814812E-2</v>
       </c>
       <c r="AQ18" s="33">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>1.9085648148148147E-2</v>
       </c>
       <c r="AR18" s="31"/>
       <c r="AS18" s="34"/>
       <c r="AT18" s="33" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>NA</v>
       </c>
       <c r="AU18" s="31"/>
       <c r="AV18" s="34"/>
       <c r="AW18" s="33" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>NA</v>
       </c>
       <c r="AX18" s="31"/>
@@ -6219,19 +6758,19 @@
         <v>3.1828703703703706E-2</v>
       </c>
       <c r="BF18" s="33">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>2.7662037037037041E-2</v>
       </c>
       <c r="BG18" s="31"/>
       <c r="BH18" s="34"/>
       <c r="BI18" s="33" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>NA</v>
       </c>
       <c r="BJ18" s="31"/>
       <c r="BK18" s="34"/>
       <c r="BL18" s="33" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>NA</v>
       </c>
       <c r="BM18" s="31">
@@ -6241,22 +6780,22 @@
         <v>2.6643518518518521E-2</v>
       </c>
       <c r="BO18" s="33">
-        <f t="shared" si="37"/>
+        <f t="shared" si="41"/>
         <v>2.2476851851851855E-2</v>
       </c>
       <c r="BP18" s="31"/>
       <c r="BQ18" s="34"/>
       <c r="BR18" s="33" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>NA</v>
       </c>
       <c r="BS18" s="31"/>
       <c r="BT18" s="34"/>
       <c r="BU18" s="33" t="str">
-        <f t="shared" si="39"/>
-        <v>NA</v>
-      </c>
-      <c r="BV18" s="41">
+        <f t="shared" si="43"/>
+        <v>NA</v>
+      </c>
+      <c r="BV18" s="31">
         <v>1</v>
       </c>
       <c r="BW18" s="34">
@@ -6266,14 +6805,14 @@
         <f t="shared" si="13"/>
         <v>2.1122685185185185E-2</v>
       </c>
-      <c r="BY18" s="41">
+      <c r="BY18" s="31">
         <v>1</v>
       </c>
       <c r="BZ18" s="34">
         <v>3.5891203703703703E-2</v>
       </c>
       <c r="CA18" s="33">
-        <f t="shared" si="40"/>
+        <f t="shared" si="44"/>
         <v>3.1724537037037037E-2</v>
       </c>
       <c r="CB18" s="31"/>
@@ -6282,8 +6821,8 @@
         <f t="shared" si="15"/>
         <v>NA</v>
       </c>
-      <c r="CE18" s="41"/>
-      <c r="CF18" s="57"/>
+      <c r="CE18" s="31"/>
+      <c r="CF18" s="56"/>
       <c r="CG18" s="33" t="str">
         <f t="shared" si="16"/>
         <v>NA</v>
@@ -6351,13 +6890,37 @@
         <v>1.3587962962962963E-2</v>
       </c>
       <c r="DH18" s="33">
-        <f t="shared" si="41"/>
+        <f t="shared" si="25"/>
         <v>9.4212962962962957E-3</v>
       </c>
-      <c r="DI18" s="35"/>
+      <c r="DI18" s="31"/>
+      <c r="DJ18" s="34"/>
+      <c r="DK18" s="33" t="str">
+        <f t="shared" si="26"/>
+        <v>NA</v>
+      </c>
+      <c r="DL18" s="31"/>
+      <c r="DM18" s="34"/>
+      <c r="DN18" s="33" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DO18" s="31"/>
+      <c r="DP18" s="34"/>
+      <c r="DQ18" s="33" t="str">
+        <f t="shared" si="28"/>
+        <v>NA</v>
+      </c>
+      <c r="DR18" s="31"/>
+      <c r="DS18" s="34"/>
+      <c r="DT18" s="33" t="str">
+        <f t="shared" si="45"/>
+        <v>NA</v>
+      </c>
+      <c r="DU18" s="35"/>
     </row>
-    <row r="19" spans="1:113" x14ac:dyDescent="0.35">
-      <c r="A19" s="95" t="s">
+    <row r="19" spans="1:125" x14ac:dyDescent="0.35">
+      <c r="A19" s="88" t="s">
         <v>213</v>
       </c>
       <c r="B19" s="8" t="s">
@@ -6366,26 +6929,26 @@
       <c r="C19" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="D19" s="96" t="s">
+      <c r="D19" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="E19" s="96">
+      <c r="E19" s="5">
         <v>3</v>
       </c>
-      <c r="F19" s="76" t="str">
-        <f t="shared" si="26"/>
+      <c r="F19" s="74" t="str">
+        <f t="shared" si="30"/>
         <v>D3</v>
       </c>
-      <c r="G19" s="96">
+      <c r="G19" s="5">
         <v>2</v>
       </c>
-      <c r="H19" s="96">
+      <c r="H19" s="5">
         <v>12</v>
       </c>
-      <c r="I19" s="98">
+      <c r="I19" s="6">
         <v>0.52361111111111114</v>
       </c>
-      <c r="J19" s="98">
+      <c r="J19" s="6">
         <v>0.62361111111111112</v>
       </c>
       <c r="K19" s="7">
@@ -6396,35 +6959,35 @@
         <f>VLOOKUP(F19,LATLON!$A$2:$C$19,3)</f>
         <v>119.309448</v>
       </c>
-      <c r="M19" s="96">
+      <c r="M19" s="5">
         <v>32</v>
       </c>
-      <c r="N19" s="96">
+      <c r="N19" s="5">
         <v>53</v>
       </c>
-      <c r="O19" s="96" t="s">
+      <c r="O19" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="P19" s="96">
+      <c r="P19" s="5">
         <v>3</v>
       </c>
       <c r="Q19" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>9.9999999999999978E-2</v>
       </c>
-      <c r="R19" s="98" t="s">
+      <c r="R19" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="S19" s="96" t="s">
+      <c r="S19" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="T19" s="96">
+      <c r="T19" s="5">
         <v>0.32</v>
       </c>
-      <c r="U19" s="96" t="s">
+      <c r="U19" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="V19" s="96"/>
+      <c r="V19" s="5"/>
       <c r="W19" s="19">
         <v>1.9571759259259257E-2</v>
       </c>
@@ -6438,7 +7001,7 @@
       <c r="AA19" s="20"/>
       <c r="AB19" s="20"/>
       <c r="AC19" s="20">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>4.5949074074074073E-2</v>
       </c>
       <c r="AD19" s="20">
@@ -6446,7 +7009,7 @@
       </c>
       <c r="AE19" s="20"/>
       <c r="AF19" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>4.1840277777777775E-2</v>
       </c>
       <c r="AG19" s="21">
@@ -6465,7 +7028,7 @@
       <c r="AL19" s="31"/>
       <c r="AM19" s="34"/>
       <c r="AN19" s="33" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>NA</v>
       </c>
       <c r="AO19" s="31">
@@ -6475,19 +7038,19 @@
         <v>9.6064814814814815E-3</v>
       </c>
       <c r="AQ19" s="33">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>5.4976851851851844E-3</v>
       </c>
       <c r="AR19" s="31"/>
       <c r="AS19" s="34"/>
       <c r="AT19" s="33" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>NA</v>
       </c>
       <c r="AU19" s="31"/>
       <c r="AV19" s="34"/>
       <c r="AW19" s="33" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>NA</v>
       </c>
       <c r="AX19" s="31"/>
@@ -6505,19 +7068,19 @@
       <c r="BD19" s="31"/>
       <c r="BE19" s="34"/>
       <c r="BF19" s="33" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>NA</v>
       </c>
       <c r="BG19" s="31"/>
       <c r="BH19" s="34"/>
       <c r="BI19" s="33" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>NA</v>
       </c>
       <c r="BJ19" s="31"/>
       <c r="BK19" s="34"/>
       <c r="BL19" s="33" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>NA</v>
       </c>
       <c r="BM19" s="31">
@@ -6527,35 +7090,35 @@
         <v>5.0925925925925921E-3</v>
       </c>
       <c r="BO19" s="33">
-        <f t="shared" si="37"/>
+        <f t="shared" si="41"/>
         <v>9.8379629629629511E-4</v>
       </c>
       <c r="BP19" s="31"/>
       <c r="BQ19" s="34"/>
       <c r="BR19" s="33" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>NA</v>
       </c>
       <c r="BS19" s="31"/>
       <c r="BT19" s="34"/>
       <c r="BU19" s="33" t="str">
-        <f t="shared" si="39"/>
-        <v>NA</v>
-      </c>
-      <c r="BV19" s="41"/>
+        <f t="shared" si="43"/>
+        <v>NA</v>
+      </c>
+      <c r="BV19" s="31"/>
       <c r="BW19" s="34"/>
       <c r="BX19" s="33" t="str">
         <f t="shared" si="13"/>
         <v>NA</v>
       </c>
-      <c r="BY19" s="41">
+      <c r="BY19" s="31">
         <v>1</v>
       </c>
       <c r="BZ19" s="34">
         <v>1.0231481481481482E-2</v>
       </c>
       <c r="CA19" s="33">
-        <f t="shared" si="40"/>
+        <f t="shared" si="44"/>
         <v>6.122685185185185E-3</v>
       </c>
       <c r="CB19" s="31"/>
@@ -6564,8 +7127,8 @@
         <f t="shared" si="15"/>
         <v>NA</v>
       </c>
-      <c r="CE19" s="41"/>
-      <c r="CF19" s="57"/>
+      <c r="CE19" s="31"/>
+      <c r="CF19" s="56"/>
       <c r="CG19" s="33" t="str">
         <f t="shared" si="16"/>
         <v>NA</v>
@@ -6625,13 +7188,45 @@
       <c r="DF19" s="31"/>
       <c r="DG19" s="34"/>
       <c r="DH19" s="33" t="str">
-        <f t="shared" si="41"/>
-        <v>NA</v>
-      </c>
-      <c r="DI19" s="35"/>
+        <f t="shared" si="25"/>
+        <v>NA</v>
+      </c>
+      <c r="DI19" s="31"/>
+      <c r="DJ19" s="34"/>
+      <c r="DK19" s="33" t="str">
+        <f t="shared" si="26"/>
+        <v>NA</v>
+      </c>
+      <c r="DL19" s="31">
+        <v>1</v>
+      </c>
+      <c r="DM19" s="34">
+        <v>6.7939814814814816E-3</v>
+      </c>
+      <c r="DN19" s="33">
+        <f t="shared" si="27"/>
+        <v>2.6851851851851846E-3</v>
+      </c>
+      <c r="DO19" s="31">
+        <v>1</v>
+      </c>
+      <c r="DP19" s="34">
+        <v>5.092592592592593E-3</v>
+      </c>
+      <c r="DQ19" s="33">
+        <f t="shared" si="28"/>
+        <v>9.8379629629629598E-4</v>
+      </c>
+      <c r="DR19" s="31"/>
+      <c r="DS19" s="34"/>
+      <c r="DT19" s="33" t="str">
+        <f t="shared" si="45"/>
+        <v>NA</v>
+      </c>
+      <c r="DU19" s="35"/>
     </row>
-    <row r="20" spans="1:113" x14ac:dyDescent="0.35">
-      <c r="A20" s="95" t="s">
+    <row r="20" spans="1:125" x14ac:dyDescent="0.35">
+      <c r="A20" s="88" t="s">
         <v>213</v>
       </c>
       <c r="B20" s="8" t="s">
@@ -6640,26 +7235,26 @@
       <c r="C20" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="D20" s="96" t="s">
+      <c r="D20" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="E20" s="96">
+      <c r="E20" s="5">
         <v>2</v>
       </c>
-      <c r="F20" s="76" t="str">
-        <f t="shared" si="26"/>
+      <c r="F20" s="74" t="str">
+        <f t="shared" si="30"/>
         <v>E2</v>
       </c>
-      <c r="G20" s="96">
+      <c r="G20" s="5">
         <v>3</v>
       </c>
-      <c r="H20" s="96">
+      <c r="H20" s="5">
         <v>11</v>
       </c>
-      <c r="I20" s="98">
+      <c r="I20" s="6">
         <v>0.54097222222222219</v>
       </c>
-      <c r="J20" s="98">
+      <c r="J20" s="6">
         <v>0.61458333333333337</v>
       </c>
       <c r="K20" s="7">
@@ -6670,35 +7265,35 @@
         <f>VLOOKUP(F20,LATLON!$A$2:$C$19,3)</f>
         <v>119.312573</v>
       </c>
-      <c r="M20" s="96">
+      <c r="M20" s="5">
         <v>73</v>
       </c>
-      <c r="N20" s="96">
+      <c r="N20" s="5">
         <v>73</v>
       </c>
-      <c r="O20" s="96" t="s">
+      <c r="O20" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="P20" s="96">
+      <c r="P20" s="5">
         <v>3</v>
       </c>
       <c r="Q20" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>7.3611111111111183E-2</v>
       </c>
-      <c r="R20" s="98" t="s">
+      <c r="R20" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="S20" s="96" t="s">
+      <c r="S20" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="T20" s="96">
+      <c r="T20" s="5">
         <v>0.34</v>
       </c>
-      <c r="U20" s="96" t="s">
+      <c r="U20" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="V20" s="96"/>
+      <c r="V20" s="5"/>
       <c r="W20" s="19">
         <v>1.7858796296296296E-2</v>
       </c>
@@ -6712,7 +7307,7 @@
       <c r="AA20" s="20"/>
       <c r="AB20" s="20"/>
       <c r="AC20" s="20">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>5.3576388888888889E-2</v>
       </c>
       <c r="AD20" s="20">
@@ -6722,7 +7317,7 @@
         <v>6.9444444444444441E-3</v>
       </c>
       <c r="AF20" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>4.2638888888888893E-2</v>
       </c>
       <c r="AG20" s="21">
@@ -6741,7 +7336,7 @@
       <c r="AL20" s="31"/>
       <c r="AM20" s="34"/>
       <c r="AN20" s="33" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>NA</v>
       </c>
       <c r="AO20" s="31">
@@ -6751,19 +7346,19 @@
         <v>2.344907407407407E-2</v>
       </c>
       <c r="AQ20" s="33">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>1.9456018518518515E-2</v>
       </c>
       <c r="AR20" s="31"/>
       <c r="AS20" s="34"/>
       <c r="AT20" s="33" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>NA</v>
       </c>
       <c r="AU20" s="31"/>
       <c r="AV20" s="34"/>
       <c r="AW20" s="33" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>NA</v>
       </c>
       <c r="AX20" s="31"/>
@@ -6781,19 +7376,19 @@
       <c r="BD20" s="31"/>
       <c r="BE20" s="34"/>
       <c r="BF20" s="33" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>NA</v>
       </c>
       <c r="BG20" s="31"/>
       <c r="BH20" s="34"/>
       <c r="BI20" s="33" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>NA</v>
       </c>
       <c r="BJ20" s="31"/>
       <c r="BK20" s="34"/>
       <c r="BL20" s="33" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>NA</v>
       </c>
       <c r="BM20" s="31">
@@ -6803,31 +7398,31 @@
         <v>3.9930555555555561E-3</v>
       </c>
       <c r="BO20" s="33">
-        <f t="shared" si="37"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="BP20" s="31"/>
       <c r="BQ20" s="34"/>
       <c r="BR20" s="33" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>NA</v>
       </c>
       <c r="BS20" s="31"/>
       <c r="BT20" s="34"/>
       <c r="BU20" s="33" t="str">
-        <f t="shared" si="39"/>
-        <v>NA</v>
-      </c>
-      <c r="BV20" s="41"/>
+        <f t="shared" si="43"/>
+        <v>NA</v>
+      </c>
+      <c r="BV20" s="31"/>
       <c r="BW20" s="34"/>
       <c r="BX20" s="33" t="str">
         <f t="shared" si="13"/>
         <v>NA</v>
       </c>
-      <c r="BY20" s="41"/>
+      <c r="BY20" s="31"/>
       <c r="BZ20" s="34"/>
       <c r="CA20" s="33" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="44"/>
         <v>NA</v>
       </c>
       <c r="CB20" s="31"/>
@@ -6836,8 +7431,8 @@
         <f t="shared" si="15"/>
         <v>NA</v>
       </c>
-      <c r="CE20" s="41"/>
-      <c r="CF20" s="57"/>
+      <c r="CE20" s="31"/>
+      <c r="CF20" s="56"/>
       <c r="CG20" s="33" t="str">
         <f t="shared" si="16"/>
         <v>NA</v>
@@ -6897,13 +7492,49 @@
       <c r="DF20" s="31"/>
       <c r="DG20" s="34"/>
       <c r="DH20" s="33" t="str">
-        <f t="shared" si="41"/>
-        <v>NA</v>
-      </c>
-      <c r="DI20" s="35"/>
+        <f t="shared" si="25"/>
+        <v>NA</v>
+      </c>
+      <c r="DI20" s="31">
+        <v>3</v>
+      </c>
+      <c r="DJ20" s="34">
+        <v>9.4444444444444445E-3</v>
+      </c>
+      <c r="DK20" s="33">
+        <f t="shared" si="26"/>
+        <v>5.4513888888888884E-3</v>
+      </c>
+      <c r="DL20" s="31"/>
+      <c r="DM20" s="34"/>
+      <c r="DN20" s="33" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DO20" s="31">
+        <v>1</v>
+      </c>
+      <c r="DP20" s="34">
+        <v>2.3090277777777779E-2</v>
+      </c>
+      <c r="DQ20" s="33">
+        <f t="shared" si="28"/>
+        <v>1.9097222222222224E-2</v>
+      </c>
+      <c r="DR20" s="31">
+        <v>1</v>
+      </c>
+      <c r="DS20" s="34">
+        <v>6.9791666666666665E-3</v>
+      </c>
+      <c r="DT20" s="33">
+        <f t="shared" si="45"/>
+        <v>2.9861111111111104E-3</v>
+      </c>
+      <c r="DU20" s="35"/>
     </row>
-    <row r="21" spans="1:113" x14ac:dyDescent="0.35">
-      <c r="A21" s="95" t="s">
+    <row r="21" spans="1:125" x14ac:dyDescent="0.35">
+      <c r="A21" s="88" t="s">
         <v>213</v>
       </c>
       <c r="B21" s="8" t="s">
@@ -6912,26 +7543,26 @@
       <c r="C21" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="D21" s="96" t="s">
+      <c r="D21" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="E21" s="96">
+      <c r="E21" s="5">
         <v>3</v>
       </c>
-      <c r="F21" s="76" t="str">
-        <f t="shared" si="26"/>
+      <c r="F21" s="74" t="str">
+        <f t="shared" si="30"/>
         <v>E3</v>
       </c>
-      <c r="G21" s="96">
+      <c r="G21" s="5">
         <v>4</v>
       </c>
-      <c r="H21" s="96" t="s">
+      <c r="H21" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="I21" s="98">
+      <c r="I21" s="6">
         <v>0.54652777777777783</v>
       </c>
-      <c r="J21" s="98">
+      <c r="J21" s="6">
         <v>0.61458333333333337</v>
       </c>
       <c r="K21" s="7">
@@ -6942,57 +7573,57 @@
         <f>VLOOKUP(F21,LATLON!$A$2:$C$19,3)</f>
         <v>119.31198000000001</v>
       </c>
-      <c r="M21" s="96">
+      <c r="M21" s="5">
         <v>58</v>
       </c>
-      <c r="N21" s="96">
+      <c r="N21" s="5">
         <v>62</v>
       </c>
-      <c r="O21" s="96" t="s">
+      <c r="O21" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="P21" s="96">
+      <c r="P21" s="5">
         <v>3</v>
       </c>
       <c r="Q21" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>6.8055555555555536E-2</v>
       </c>
-      <c r="R21" s="98" t="s">
+      <c r="R21" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="S21" s="96" t="s">
+      <c r="S21" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="T21" s="96">
+      <c r="T21" s="5">
         <v>0.34</v>
       </c>
-      <c r="U21" s="96" t="s">
+      <c r="U21" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="V21" s="96"/>
-      <c r="W21" s="78">
+      <c r="V21" s="5"/>
+      <c r="W21" s="76">
         <v>1.5891203703703703E-2</v>
       </c>
-      <c r="X21" s="79">
+      <c r="X21" s="77">
         <v>1.486111111111111E-2</v>
       </c>
-      <c r="Y21" s="79">
+      <c r="Y21" s="77">
         <v>3.1134259259259257E-3</v>
       </c>
-      <c r="Z21" s="79"/>
-      <c r="AA21" s="79"/>
-      <c r="AB21" s="79"/>
+      <c r="Z21" s="77"/>
+      <c r="AA21" s="77"/>
+      <c r="AB21" s="77"/>
       <c r="AC21" s="20">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>3.3865740740740738E-2</v>
       </c>
-      <c r="AD21" s="80">
+      <c r="AD21" s="78">
         <v>4.1666666666666666E-3</v>
       </c>
-      <c r="AE21" s="80"/>
+      <c r="AE21" s="78"/>
       <c r="AF21" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>2.9699074074074072E-2</v>
       </c>
       <c r="AG21" s="21">
@@ -7013,25 +7644,25 @@
       <c r="AL21" s="31"/>
       <c r="AM21" s="32"/>
       <c r="AN21" s="33" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>NA</v>
       </c>
       <c r="AO21" s="31"/>
       <c r="AP21" s="32"/>
       <c r="AQ21" s="33" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>NA</v>
       </c>
       <c r="AR21" s="31"/>
       <c r="AS21" s="32"/>
       <c r="AT21" s="33" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>NA</v>
       </c>
       <c r="AU21" s="31"/>
       <c r="AV21" s="32"/>
       <c r="AW21" s="33" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>NA</v>
       </c>
       <c r="AX21" s="31"/>
@@ -7049,57 +7680,57 @@
       <c r="BD21" s="31"/>
       <c r="BE21" s="34"/>
       <c r="BF21" s="33" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>NA</v>
       </c>
       <c r="BG21" s="31"/>
       <c r="BH21" s="32"/>
       <c r="BI21" s="33" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>NA</v>
       </c>
       <c r="BJ21" s="31"/>
       <c r="BK21" s="32"/>
       <c r="BL21" s="33" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>NA</v>
       </c>
       <c r="BM21" s="31">
         <v>1</v>
       </c>
-      <c r="BN21" s="57">
+      <c r="BN21" s="56">
         <v>3.2858796296296296E-2</v>
       </c>
       <c r="BO21" s="33">
-        <f t="shared" si="37"/>
+        <f t="shared" si="41"/>
         <v>2.869212962962963E-2</v>
       </c>
       <c r="BP21" s="31"/>
       <c r="BQ21" s="32"/>
       <c r="BR21" s="33" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>NA</v>
       </c>
       <c r="BS21" s="31"/>
       <c r="BT21" s="32"/>
       <c r="BU21" s="33" t="str">
-        <f t="shared" si="39"/>
-        <v>NA</v>
-      </c>
-      <c r="BV21" s="41"/>
+        <f t="shared" si="43"/>
+        <v>NA</v>
+      </c>
+      <c r="BV21" s="31"/>
       <c r="BW21" s="34"/>
       <c r="BX21" s="33" t="str">
         <f t="shared" si="13"/>
         <v>NA</v>
       </c>
-      <c r="BY21" s="41">
+      <c r="BY21" s="31">
         <v>1</v>
       </c>
       <c r="BZ21" s="34">
         <v>2.1956018518518517E-2</v>
       </c>
       <c r="CA21" s="33">
-        <f t="shared" si="40"/>
+        <f t="shared" si="44"/>
         <v>1.7789351851851851E-2</v>
       </c>
       <c r="CB21" s="31"/>
@@ -7108,7 +7739,7 @@
         <f t="shared" si="15"/>
         <v>NA</v>
       </c>
-      <c r="CE21" s="41"/>
+      <c r="CE21" s="31"/>
       <c r="CF21" s="34"/>
       <c r="CG21" s="33" t="str">
         <f t="shared" si="16"/>
@@ -7161,21 +7792,49 @@
         <v>NA</v>
       </c>
       <c r="DC21" s="31"/>
-      <c r="DD21" s="57"/>
+      <c r="DD21" s="56"/>
       <c r="DE21" s="33" t="str">
         <f t="shared" si="24"/>
         <v>NA</v>
       </c>
       <c r="DF21" s="31"/>
-      <c r="DG21" s="57"/>
+      <c r="DG21" s="56"/>
       <c r="DH21" s="33" t="str">
-        <f t="shared" si="41"/>
-        <v>NA</v>
-      </c>
-      <c r="DI21" s="35"/>
+        <f t="shared" si="25"/>
+        <v>NA</v>
+      </c>
+      <c r="DI21" s="31"/>
+      <c r="DJ21" s="56"/>
+      <c r="DK21" s="33" t="str">
+        <f t="shared" si="26"/>
+        <v>NA</v>
+      </c>
+      <c r="DL21" s="31">
+        <v>1</v>
+      </c>
+      <c r="DM21" s="56">
+        <v>1.6805555555555556E-2</v>
+      </c>
+      <c r="DN21" s="33">
+        <f t="shared" si="27"/>
+        <v>1.263888888888889E-2</v>
+      </c>
+      <c r="DO21" s="31"/>
+      <c r="DP21" s="56"/>
+      <c r="DQ21" s="33" t="str">
+        <f t="shared" si="28"/>
+        <v>NA</v>
+      </c>
+      <c r="DR21" s="31"/>
+      <c r="DS21" s="56"/>
+      <c r="DT21" s="33" t="str">
+        <f t="shared" si="45"/>
+        <v>NA</v>
+      </c>
+      <c r="DU21" s="35"/>
     </row>
-    <row r="22" spans="1:113" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="106" t="s">
+    <row r="22" spans="1:125" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="94" t="s">
         <v>213</v>
       </c>
       <c r="B22" s="14" t="s">
@@ -7190,8 +7849,8 @@
       <c r="E22" s="11">
         <v>1</v>
       </c>
-      <c r="F22" s="77" t="str">
-        <f t="shared" si="26"/>
+      <c r="F22" s="75" t="str">
+        <f t="shared" si="30"/>
         <v>E1</v>
       </c>
       <c r="G22" s="11">
@@ -7227,7 +7886,7 @@
         <v>3</v>
       </c>
       <c r="Q22" s="12">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>5.2083333333333259E-2</v>
       </c>
       <c r="R22" s="12" t="s">
@@ -7243,30 +7902,30 @@
         <v>186</v>
       </c>
       <c r="V22" s="11"/>
-      <c r="W22" s="81">
+      <c r="W22" s="79">
         <v>1.7858796296296296E-2</v>
       </c>
-      <c r="X22" s="70">
+      <c r="X22" s="69">
         <v>1.7858796296296296E-2</v>
       </c>
-      <c r="Y22" s="70">
+      <c r="Y22" s="69">
         <v>1.7175925925925924E-2</v>
       </c>
-      <c r="Z22" s="70"/>
-      <c r="AA22" s="70"/>
-      <c r="AB22" s="70"/>
+      <c r="Z22" s="69"/>
+      <c r="AA22" s="69"/>
+      <c r="AB22" s="69"/>
       <c r="AC22" s="23">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>5.289351851851852E-2</v>
       </c>
-      <c r="AD22" s="82">
+      <c r="AD22" s="80">
         <v>5.3240740740740748E-3</v>
       </c>
-      <c r="AE22" s="82">
+      <c r="AE22" s="80">
         <v>1.1388888888888888E-2</v>
       </c>
       <c r="AF22" s="23">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>3.6180555555555556E-2</v>
       </c>
       <c r="AG22" s="24">
@@ -7277,61 +7936,61 @@
       </c>
       <c r="AI22" s="25"/>
       <c r="AJ22" s="36">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AK22" s="37">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AL22" s="38"/>
       <c r="AM22" s="40"/>
-      <c r="AN22" s="42" t="str">
-        <f t="shared" si="30"/>
+      <c r="AN22" s="41" t="str">
+        <f t="shared" si="34"/>
         <v>NA</v>
       </c>
       <c r="AO22" s="38"/>
       <c r="AP22" s="40"/>
-      <c r="AQ22" s="42" t="str">
-        <f t="shared" si="31"/>
+      <c r="AQ22" s="41" t="str">
+        <f t="shared" si="35"/>
         <v>NA</v>
       </c>
       <c r="AR22" s="38"/>
-      <c r="AS22" s="85"/>
-      <c r="AT22" s="42" t="str">
-        <f t="shared" si="32"/>
+      <c r="AS22" s="82"/>
+      <c r="AT22" s="41" t="str">
+        <f t="shared" si="36"/>
         <v>NA</v>
       </c>
       <c r="AU22" s="38"/>
-      <c r="AV22" s="85"/>
-      <c r="AW22" s="42" t="str">
-        <f t="shared" si="33"/>
+      <c r="AV22" s="82"/>
+      <c r="AW22" s="41" t="str">
+        <f t="shared" si="37"/>
         <v>NA</v>
       </c>
       <c r="AX22" s="38"/>
-      <c r="AY22" s="85"/>
-      <c r="AZ22" s="42" t="str">
+      <c r="AY22" s="82"/>
+      <c r="AZ22" s="41" t="str">
         <f t="shared" si="5"/>
         <v>NA</v>
       </c>
       <c r="BA22" s="38">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="BB22" s="40">
         <v>1.5740740740740743E-2</v>
       </c>
-      <c r="BC22" s="42">
+      <c r="BC22" s="41">
         <f t="shared" si="6"/>
         <v>1.0416666666666668E-2</v>
       </c>
       <c r="BD22" s="38"/>
       <c r="BE22" s="40"/>
-      <c r="BF22" s="42" t="str">
-        <f t="shared" si="34"/>
+      <c r="BF22" s="41" t="str">
+        <f t="shared" si="38"/>
         <v>NA</v>
       </c>
       <c r="BG22" s="38"/>
-      <c r="BH22" s="85"/>
-      <c r="BI22" s="42" t="str">
-        <f t="shared" si="35"/>
+      <c r="BH22" s="82"/>
+      <c r="BI22" s="41" t="str">
+        <f t="shared" si="39"/>
         <v>NA</v>
       </c>
       <c r="BJ22" s="38">
@@ -7340,8 +7999,8 @@
       <c r="BK22" s="40">
         <v>8.1018518518518514E-3</v>
       </c>
-      <c r="BL22" s="42">
-        <f t="shared" si="36"/>
+      <c r="BL22" s="41">
+        <f t="shared" si="40"/>
         <v>2.7777777777777766E-3</v>
       </c>
       <c r="BM22" s="38">
@@ -7350,47 +8009,47 @@
       <c r="BN22" s="40">
         <v>5.37037037037037E-3</v>
       </c>
-      <c r="BO22" s="42">
-        <f t="shared" si="37"/>
+      <c r="BO22" s="41">
+        <f t="shared" si="41"/>
         <v>4.6296296296295149E-5</v>
       </c>
       <c r="BP22" s="38"/>
-      <c r="BQ22" s="85"/>
-      <c r="BR22" s="42" t="str">
-        <f t="shared" si="38"/>
+      <c r="BQ22" s="82"/>
+      <c r="BR22" s="41" t="str">
+        <f t="shared" si="42"/>
         <v>NA</v>
       </c>
       <c r="BS22" s="38"/>
-      <c r="BT22" s="85"/>
-      <c r="BU22" s="42" t="str">
-        <f t="shared" si="39"/>
-        <v>NA</v>
-      </c>
-      <c r="BV22" s="86"/>
+      <c r="BT22" s="82"/>
+      <c r="BU22" s="41" t="str">
+        <f t="shared" si="43"/>
+        <v>NA</v>
+      </c>
+      <c r="BV22" s="38"/>
       <c r="BW22" s="40"/>
-      <c r="BX22" s="42" t="str">
+      <c r="BX22" s="41" t="str">
         <f t="shared" si="13"/>
         <v>NA</v>
       </c>
-      <c r="BY22" s="86">
+      <c r="BY22" s="38">
         <v>1</v>
       </c>
       <c r="BZ22" s="40">
         <v>3.0173611111111113E-2</v>
       </c>
-      <c r="CA22" s="42">
-        <f t="shared" si="40"/>
+      <c r="CA22" s="41">
+        <f t="shared" si="44"/>
         <v>2.4849537037037038E-2</v>
       </c>
       <c r="CB22" s="38"/>
-      <c r="CC22" s="85"/>
-      <c r="CD22" s="42" t="str">
+      <c r="CC22" s="82"/>
+      <c r="CD22" s="41" t="str">
         <f t="shared" si="15"/>
         <v>NA</v>
       </c>
-      <c r="CE22" s="86"/>
-      <c r="CF22" s="85"/>
-      <c r="CG22" s="42" t="str">
+      <c r="CE22" s="38"/>
+      <c r="CF22" s="82"/>
+      <c r="CG22" s="41" t="str">
         <f t="shared" si="16"/>
         <v>NA</v>
       </c>
@@ -7400,13 +8059,13 @@
       <c r="CI22" s="40">
         <v>5.3240740740740748E-3</v>
       </c>
-      <c r="CJ22" s="42">
+      <c r="CJ22" s="41">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="CK22" s="38"/>
-      <c r="CL22" s="85"/>
-      <c r="CM22" s="42" t="str">
+      <c r="CL22" s="82"/>
+      <c r="CM22" s="41" t="str">
         <f t="shared" si="18"/>
         <v>NA</v>
       </c>
@@ -7416,47 +8075,83 @@
       <c r="CO22" s="40">
         <v>2.1331018518518517E-2</v>
       </c>
-      <c r="CP22" s="42">
+      <c r="CP22" s="41">
         <f t="shared" si="19"/>
         <v>1.6006944444444442E-2</v>
       </c>
       <c r="CQ22" s="38"/>
       <c r="CR22" s="40"/>
-      <c r="CS22" s="42" t="str">
+      <c r="CS22" s="41" t="str">
         <f t="shared" si="20"/>
         <v>NA</v>
       </c>
       <c r="CT22" s="38"/>
-      <c r="CU22" s="85"/>
-      <c r="CV22" s="42" t="str">
+      <c r="CU22" s="82"/>
+      <c r="CV22" s="41" t="str">
         <f t="shared" si="21"/>
         <v>NA</v>
       </c>
       <c r="CW22" s="38"/>
-      <c r="CX22" s="85"/>
-      <c r="CY22" s="42" t="str">
+      <c r="CX22" s="82"/>
+      <c r="CY22" s="41" t="str">
         <f t="shared" si="22"/>
         <v>NA</v>
       </c>
       <c r="CZ22" s="38"/>
       <c r="DA22" s="40"/>
-      <c r="DB22" s="42" t="str">
+      <c r="DB22" s="41" t="str">
         <f t="shared" si="23"/>
         <v>NA</v>
       </c>
       <c r="DC22" s="38"/>
       <c r="DD22" s="40"/>
-      <c r="DE22" s="42" t="str">
+      <c r="DE22" s="41" t="str">
         <f t="shared" si="24"/>
         <v>NA</v>
       </c>
       <c r="DF22" s="38"/>
       <c r="DG22" s="40"/>
-      <c r="DH22" s="42" t="str">
-        <f t="shared" si="41"/>
-        <v>NA</v>
-      </c>
-      <c r="DI22" s="39"/>
+      <c r="DH22" s="41" t="str">
+        <f t="shared" si="25"/>
+        <v>NA</v>
+      </c>
+      <c r="DI22" s="38">
+        <v>1</v>
+      </c>
+      <c r="DJ22" s="40">
+        <v>2.042824074074074E-2</v>
+      </c>
+      <c r="DK22" s="41">
+        <f t="shared" si="26"/>
+        <v>1.5104166666666665E-2</v>
+      </c>
+      <c r="DL22" s="38">
+        <v>3</v>
+      </c>
+      <c r="DM22" s="40">
+        <v>5.324074074074074E-3</v>
+      </c>
+      <c r="DN22" s="41">
+        <f t="shared" si="27"/>
+        <v>-8.6736173798840355E-19</v>
+      </c>
+      <c r="DO22" s="38">
+        <v>1</v>
+      </c>
+      <c r="DP22" s="40">
+        <v>3.259259259259259E-2</v>
+      </c>
+      <c r="DQ22" s="41">
+        <f t="shared" si="28"/>
+        <v>2.7268518518518515E-2</v>
+      </c>
+      <c r="DR22" s="38"/>
+      <c r="DS22" s="40"/>
+      <c r="DT22" s="41" t="str">
+        <f t="shared" si="45"/>
+        <v>NA</v>
+      </c>
+      <c r="DU22" s="39"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -7497,7 +8192,7 @@
       <c r="C2" t="s">
         <v>146</v>
       </c>
-      <c r="D2" s="56">
+      <c r="D2" s="55">
         <v>0.56111111111111112</v>
       </c>
     </row>
@@ -7511,7 +8206,7 @@
       <c r="C3" t="s">
         <v>146</v>
       </c>
-      <c r="D3" s="56">
+      <c r="D3" s="55">
         <v>0.55555555555555558</v>
       </c>
     </row>
@@ -7525,7 +8220,7 @@
       <c r="C4" t="s">
         <v>150</v>
       </c>
-      <c r="D4" s="56">
+      <c r="D4" s="55">
         <v>0.45069444444444445</v>
       </c>
     </row>
@@ -7536,7 +8231,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F89D226-4FD3-43E7-AD2C-117D056F41E4}">
-  <dimension ref="A1:CW22"/>
+  <dimension ref="A1:CU22"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.453125" bestFit="1" customWidth="1"/>
@@ -7545,30 +8240,17 @@
     <col min="22" max="28" width="8.7265625" style="1"/>
     <col min="36" max="36" width="14.90625" bestFit="1" customWidth="1"/>
     <col min="39" max="39" width="14.08984375" bestFit="1" customWidth="1"/>
-    <col min="40" max="41" width="8.7265625" style="88"/>
-    <col min="42" max="42" width="14.453125" style="88" bestFit="1" customWidth="1"/>
-    <col min="43" max="44" width="8.7265625" style="88"/>
-    <col min="45" max="45" width="10.7265625" style="88" bestFit="1" customWidth="1"/>
-    <col min="46" max="47" width="8.7265625" style="88"/>
-    <col min="48" max="48" width="10.6328125" style="88" bestFit="1" customWidth="1"/>
-    <col min="49" max="50" width="8.7265625" style="88"/>
-    <col min="51" max="51" width="10.6328125" style="88" bestFit="1" customWidth="1"/>
-    <col min="52" max="53" width="8.7265625" style="88"/>
-    <col min="54" max="54" width="12.81640625" style="88" bestFit="1" customWidth="1"/>
-    <col min="55" max="56" width="8.7265625" style="88"/>
-    <col min="57" max="57" width="8.90625" style="88" bestFit="1" customWidth="1"/>
-    <col min="58" max="75" width="8.7265625" style="88"/>
-    <col min="76" max="76" width="8.7265625" style="89"/>
-    <col min="77" max="77" width="8.7265625" style="88"/>
-    <col min="78" max="78" width="9.36328125" style="88" bestFit="1" customWidth="1"/>
-    <col min="79" max="83" width="8.7265625" style="88"/>
-    <col min="84" max="84" width="18.36328125" style="88" bestFit="1" customWidth="1"/>
-    <col min="85" max="95" width="8.7265625" style="88"/>
-    <col min="96" max="96" width="11.1796875" style="88" bestFit="1" customWidth="1"/>
-    <col min="97" max="98" width="8.7265625" style="88"/>
-    <col min="99" max="99" width="11.1796875" style="88" bestFit="1" customWidth="1"/>
-    <col min="100" max="100" width="13.90625" style="88" bestFit="1" customWidth="1"/>
-    <col min="101" max="101" width="8.7265625" style="88"/>
+    <col min="42" max="42" width="14.453125" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="10.7265625" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="10.6328125" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="10.6328125" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="8.90625" bestFit="1" customWidth="1"/>
+    <col min="78" max="78" width="9.36328125" bestFit="1" customWidth="1"/>
+    <col min="84" max="84" width="18.36328125" bestFit="1" customWidth="1"/>
+    <col min="96" max="96" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="99" max="99" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="100" max="100" width="13.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:99" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -7584,7 +8266,7 @@
       <c r="D1" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E1" s="75" t="s">
+      <c r="E1" s="73" t="s">
         <v>98</v>
       </c>
       <c r="F1" s="3" t="s">
@@ -7677,7 +8359,7 @@
       <c r="AI1" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="AJ1" s="60" t="s">
+      <c r="AJ1" s="59" t="s">
         <v>11</v>
       </c>
       <c r="AK1" s="26" t="s">
@@ -7691,29 +8373,29 @@
       </c>
     </row>
     <row r="2" spans="1:99" ht="145" x14ac:dyDescent="0.35">
-      <c r="A2" s="43" t="s">
+      <c r="A2" s="42" t="s">
         <v>68</v>
       </c>
-      <c r="B2" s="44" t="s">
+      <c r="B2" s="43" t="s">
         <v>69</v>
       </c>
-      <c r="C2" s="45" t="s">
+      <c r="C2" s="44" t="s">
         <v>70</v>
       </c>
-      <c r="D2" s="46" t="s">
+      <c r="D2" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="E2" s="76" t="s">
+      <c r="E2" s="74" t="s">
         <v>144</v>
       </c>
-      <c r="F2" s="45" t="s">
+      <c r="F2" s="44" t="s">
         <v>72</v>
       </c>
-      <c r="G2" s="45"/>
-      <c r="H2" s="47" t="s">
+      <c r="G2" s="44"/>
+      <c r="H2" s="46" t="s">
         <v>73</v>
       </c>
-      <c r="I2" s="45" t="s">
+      <c r="I2" s="44" t="s">
         <v>74</v>
       </c>
       <c r="J2" s="7" t="s">
@@ -7722,124 +8404,124 @@
       <c r="K2" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="L2" s="45" t="s">
+      <c r="L2" s="44" t="s">
         <v>89</v>
       </c>
-      <c r="M2" s="45" t="s">
+      <c r="M2" s="44" t="s">
         <v>89</v>
       </c>
-      <c r="N2" s="45" t="s">
+      <c r="N2" s="44" t="s">
         <v>76</v>
       </c>
-      <c r="O2" s="45" t="s">
+      <c r="O2" s="44" t="s">
         <v>75</v>
       </c>
       <c r="P2" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="Q2" s="47" t="s">
+      <c r="Q2" s="46" t="s">
         <v>145</v>
       </c>
-      <c r="R2" s="45" t="s">
+      <c r="R2" s="44" t="s">
         <v>90</v>
       </c>
-      <c r="S2" s="45" t="s">
+      <c r="S2" s="44" t="s">
         <v>77</v>
       </c>
-      <c r="T2" s="45" t="s">
+      <c r="T2" s="44" t="s">
         <v>77</v>
       </c>
-      <c r="U2" s="48"/>
-      <c r="V2" s="49" t="s">
+      <c r="U2" s="47"/>
+      <c r="V2" s="48" t="s">
         <v>78</v>
       </c>
-      <c r="W2" s="50" t="s">
+      <c r="W2" s="49" t="s">
         <v>78</v>
       </c>
-      <c r="X2" s="50" t="s">
+      <c r="X2" s="49" t="s">
         <v>78</v>
       </c>
-      <c r="Y2" s="50" t="s">
+      <c r="Y2" s="49" t="s">
         <v>78</v>
       </c>
-      <c r="Z2" s="50" t="s">
+      <c r="Z2" s="49" t="s">
         <v>78</v>
       </c>
-      <c r="AA2" s="50" t="s">
+      <c r="AA2" s="49" t="s">
         <v>78</v>
       </c>
       <c r="AB2" s="20" t="s">
         <v>144</v>
       </c>
-      <c r="AC2" s="50" t="s">
+      <c r="AC2" s="49" t="s">
         <v>79</v>
       </c>
-      <c r="AD2" s="50" t="s">
+      <c r="AD2" s="49" t="s">
         <v>80</v>
       </c>
       <c r="AE2" s="20" t="e">
         <f t="shared" ref="AE2:AE22" si="0">AB2-AC2-AD2</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AF2" s="51" t="s">
+      <c r="AF2" s="50" t="s">
         <v>82</v>
       </c>
-      <c r="AG2" s="51" t="s">
+      <c r="AG2" s="50" t="s">
         <v>81</v>
       </c>
       <c r="AH2" s="22"/>
-      <c r="AI2" s="52" t="s">
+      <c r="AI2" s="51" t="s">
         <v>83</v>
       </c>
-      <c r="AJ2" s="53" t="s">
+      <c r="AJ2" s="52" t="s">
         <v>83</v>
       </c>
-      <c r="AK2" s="54" t="s">
+      <c r="AK2" s="53" t="s">
         <v>84</v>
       </c>
-      <c r="AL2" s="55" t="s">
+      <c r="AL2" s="54" t="s">
         <v>85</v>
       </c>
-      <c r="AM2" s="57" t="s">
+      <c r="AM2" s="56" t="s">
         <v>144</v>
       </c>
-      <c r="AO2" s="90"/>
-      <c r="AP2" s="90"/>
-      <c r="AS2" s="90"/>
-      <c r="AV2" s="90"/>
-      <c r="AY2" s="90"/>
-      <c r="BB2" s="90"/>
-      <c r="BE2" s="90"/>
-      <c r="BH2" s="90"/>
-      <c r="BK2" s="90"/>
-      <c r="BN2" s="90"/>
-      <c r="BQ2" s="90"/>
-      <c r="BS2" s="91"/>
-      <c r="BT2" s="90"/>
-      <c r="BW2" s="90"/>
-      <c r="BY2" s="90"/>
-      <c r="BZ2" s="90"/>
-      <c r="CB2" s="92"/>
-      <c r="CC2" s="90"/>
-      <c r="CE2" s="92"/>
-      <c r="CF2" s="90"/>
-      <c r="CH2" s="92"/>
-      <c r="CI2" s="90"/>
-      <c r="CK2" s="92"/>
-      <c r="CL2" s="90"/>
-      <c r="CN2" s="92"/>
-      <c r="CO2" s="90"/>
-      <c r="CQ2" s="92"/>
-      <c r="CR2" s="90"/>
-      <c r="CT2" s="92"/>
-      <c r="CU2" s="90"/>
+      <c r="AO2" s="84"/>
+      <c r="AP2" s="84"/>
+      <c r="AS2" s="84"/>
+      <c r="AV2" s="84"/>
+      <c r="AY2" s="84"/>
+      <c r="BB2" s="84"/>
+      <c r="BE2" s="84"/>
+      <c r="BH2" s="84"/>
+      <c r="BK2" s="84"/>
+      <c r="BN2" s="84"/>
+      <c r="BQ2" s="84"/>
+      <c r="BS2" s="55"/>
+      <c r="BT2" s="84"/>
+      <c r="BW2" s="84"/>
+      <c r="BY2" s="84"/>
+      <c r="BZ2" s="84"/>
+      <c r="CB2" s="85"/>
+      <c r="CC2" s="84"/>
+      <c r="CE2" s="85"/>
+      <c r="CF2" s="84"/>
+      <c r="CH2" s="85"/>
+      <c r="CI2" s="84"/>
+      <c r="CK2" s="85"/>
+      <c r="CL2" s="84"/>
+      <c r="CN2" s="85"/>
+      <c r="CO2" s="84"/>
+      <c r="CQ2" s="85"/>
+      <c r="CR2" s="84"/>
+      <c r="CT2" s="85"/>
+      <c r="CU2" s="84"/>
     </row>
     <row r="3" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A3" s="9"/>
       <c r="B3" s="9"/>
       <c r="C3" s="5"/>
       <c r="D3" s="5"/>
-      <c r="E3" s="76" t="str">
+      <c r="E3" s="74" t="str">
         <f t="shared" ref="E3:E22" si="1">C3&amp;""&amp;D3</f>
         <v/>
       </c>
@@ -7891,38 +8573,38 @@
       <c r="AJ3" s="30"/>
       <c r="AK3" s="31"/>
       <c r="AL3" s="34"/>
-      <c r="AM3" s="57" t="str">
+      <c r="AM3" s="56" t="str">
         <f t="shared" ref="AM3:AM22" si="4">IF(AK3=0,"NA",AL3-$AC3)</f>
         <v>NA</v>
       </c>
-      <c r="AP3" s="90"/>
-      <c r="AS3" s="90"/>
-      <c r="AV3" s="90"/>
-      <c r="AY3" s="90"/>
-      <c r="BB3" s="90"/>
-      <c r="BE3" s="90"/>
-      <c r="BH3" s="90"/>
-      <c r="BK3" s="90"/>
-      <c r="BN3" s="90"/>
-      <c r="BQ3" s="90"/>
-      <c r="BT3" s="90"/>
-      <c r="BW3" s="90"/>
-      <c r="BY3" s="90"/>
-      <c r="BZ3" s="90"/>
-      <c r="CC3" s="90"/>
-      <c r="CF3" s="90"/>
-      <c r="CI3" s="90"/>
-      <c r="CL3" s="90"/>
-      <c r="CO3" s="90"/>
-      <c r="CR3" s="90"/>
-      <c r="CU3" s="90"/>
+      <c r="AP3" s="84"/>
+      <c r="AS3" s="84"/>
+      <c r="AV3" s="84"/>
+      <c r="AY3" s="84"/>
+      <c r="BB3" s="84"/>
+      <c r="BE3" s="84"/>
+      <c r="BH3" s="84"/>
+      <c r="BK3" s="84"/>
+      <c r="BN3" s="84"/>
+      <c r="BQ3" s="84"/>
+      <c r="BT3" s="84"/>
+      <c r="BW3" s="84"/>
+      <c r="BY3" s="84"/>
+      <c r="BZ3" s="84"/>
+      <c r="CC3" s="84"/>
+      <c r="CF3" s="84"/>
+      <c r="CI3" s="84"/>
+      <c r="CL3" s="84"/>
+      <c r="CO3" s="84"/>
+      <c r="CR3" s="84"/>
+      <c r="CU3" s="84"/>
     </row>
     <row r="4" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A4" s="9"/>
       <c r="B4" s="9"/>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
-      <c r="E4" s="76" t="str">
+      <c r="E4" s="74" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -7974,47 +8656,47 @@
       <c r="AJ4" s="30"/>
       <c r="AK4" s="31"/>
       <c r="AL4" s="34"/>
-      <c r="AM4" s="57" t="str">
+      <c r="AM4" s="56" t="str">
         <f t="shared" si="4"/>
         <v>NA</v>
       </c>
-      <c r="AP4" s="90"/>
-      <c r="AS4" s="90"/>
-      <c r="AV4" s="90"/>
-      <c r="AY4" s="90"/>
-      <c r="BB4" s="90"/>
-      <c r="BE4" s="90"/>
-      <c r="BG4" s="92"/>
-      <c r="BH4" s="90"/>
-      <c r="BJ4" s="92"/>
-      <c r="BK4" s="90"/>
-      <c r="BN4" s="90"/>
-      <c r="BQ4" s="90"/>
-      <c r="BT4" s="90"/>
-      <c r="BW4" s="90"/>
-      <c r="BY4" s="90"/>
-      <c r="BZ4" s="90"/>
-      <c r="CB4" s="92"/>
-      <c r="CC4" s="90"/>
-      <c r="CE4" s="92"/>
-      <c r="CF4" s="90"/>
-      <c r="CH4" s="92"/>
-      <c r="CI4" s="90"/>
-      <c r="CK4" s="92"/>
-      <c r="CL4" s="90"/>
-      <c r="CN4" s="92"/>
-      <c r="CO4" s="90"/>
-      <c r="CQ4" s="92"/>
-      <c r="CR4" s="90"/>
-      <c r="CT4" s="92"/>
-      <c r="CU4" s="90"/>
+      <c r="AP4" s="84"/>
+      <c r="AS4" s="84"/>
+      <c r="AV4" s="84"/>
+      <c r="AY4" s="84"/>
+      <c r="BB4" s="84"/>
+      <c r="BE4" s="84"/>
+      <c r="BG4" s="85"/>
+      <c r="BH4" s="84"/>
+      <c r="BJ4" s="85"/>
+      <c r="BK4" s="84"/>
+      <c r="BN4" s="84"/>
+      <c r="BQ4" s="84"/>
+      <c r="BT4" s="84"/>
+      <c r="BW4" s="84"/>
+      <c r="BY4" s="84"/>
+      <c r="BZ4" s="84"/>
+      <c r="CB4" s="85"/>
+      <c r="CC4" s="84"/>
+      <c r="CE4" s="85"/>
+      <c r="CF4" s="84"/>
+      <c r="CH4" s="85"/>
+      <c r="CI4" s="84"/>
+      <c r="CK4" s="85"/>
+      <c r="CL4" s="84"/>
+      <c r="CN4" s="85"/>
+      <c r="CO4" s="84"/>
+      <c r="CQ4" s="85"/>
+      <c r="CR4" s="84"/>
+      <c r="CT4" s="85"/>
+      <c r="CU4" s="84"/>
     </row>
     <row r="5" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A5" s="9"/>
       <c r="B5" s="9"/>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
-      <c r="E5" s="76" t="str">
+      <c r="E5" s="74" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -8066,38 +8748,38 @@
       <c r="AJ5" s="30"/>
       <c r="AK5" s="31"/>
       <c r="AL5" s="34"/>
-      <c r="AM5" s="57" t="str">
+      <c r="AM5" s="56" t="str">
         <f t="shared" si="4"/>
         <v>NA</v>
       </c>
-      <c r="AP5" s="90"/>
-      <c r="AS5" s="90"/>
-      <c r="AV5" s="90"/>
-      <c r="AY5" s="90"/>
-      <c r="BB5" s="90"/>
-      <c r="BE5" s="90"/>
-      <c r="BH5" s="90"/>
-      <c r="BK5" s="90"/>
-      <c r="BN5" s="90"/>
-      <c r="BQ5" s="90"/>
-      <c r="BT5" s="90"/>
-      <c r="BW5" s="90"/>
-      <c r="BY5" s="90"/>
-      <c r="BZ5" s="90"/>
-      <c r="CC5" s="90"/>
-      <c r="CF5" s="90"/>
-      <c r="CI5" s="90"/>
-      <c r="CL5" s="90"/>
-      <c r="CO5" s="90"/>
-      <c r="CR5" s="90"/>
-      <c r="CU5" s="90"/>
+      <c r="AP5" s="84"/>
+      <c r="AS5" s="84"/>
+      <c r="AV5" s="84"/>
+      <c r="AY5" s="84"/>
+      <c r="BB5" s="84"/>
+      <c r="BE5" s="84"/>
+      <c r="BH5" s="84"/>
+      <c r="BK5" s="84"/>
+      <c r="BN5" s="84"/>
+      <c r="BQ5" s="84"/>
+      <c r="BT5" s="84"/>
+      <c r="BW5" s="84"/>
+      <c r="BY5" s="84"/>
+      <c r="BZ5" s="84"/>
+      <c r="CC5" s="84"/>
+      <c r="CF5" s="84"/>
+      <c r="CI5" s="84"/>
+      <c r="CL5" s="84"/>
+      <c r="CO5" s="84"/>
+      <c r="CR5" s="84"/>
+      <c r="CU5" s="84"/>
     </row>
     <row r="6" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A6" s="9"/>
       <c r="B6" s="9"/>
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
-      <c r="E6" s="76" t="str">
+      <c r="E6" s="74" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -8149,38 +8831,38 @@
       <c r="AJ6" s="30"/>
       <c r="AK6" s="31"/>
       <c r="AL6" s="34"/>
-      <c r="AM6" s="57" t="str">
+      <c r="AM6" s="56" t="str">
         <f t="shared" si="4"/>
         <v>NA</v>
       </c>
-      <c r="AP6" s="90"/>
-      <c r="AS6" s="90"/>
-      <c r="AV6" s="90"/>
-      <c r="AY6" s="90"/>
-      <c r="BB6" s="90"/>
-      <c r="BE6" s="90"/>
-      <c r="BH6" s="90"/>
-      <c r="BK6" s="90"/>
-      <c r="BN6" s="90"/>
-      <c r="BQ6" s="90"/>
-      <c r="BT6" s="90"/>
-      <c r="BW6" s="90"/>
-      <c r="BY6" s="90"/>
-      <c r="BZ6" s="90"/>
-      <c r="CC6" s="90"/>
-      <c r="CF6" s="90"/>
-      <c r="CI6" s="90"/>
-      <c r="CL6" s="90"/>
-      <c r="CO6" s="90"/>
-      <c r="CR6" s="90"/>
-      <c r="CU6" s="90"/>
+      <c r="AP6" s="84"/>
+      <c r="AS6" s="84"/>
+      <c r="AV6" s="84"/>
+      <c r="AY6" s="84"/>
+      <c r="BB6" s="84"/>
+      <c r="BE6" s="84"/>
+      <c r="BH6" s="84"/>
+      <c r="BK6" s="84"/>
+      <c r="BN6" s="84"/>
+      <c r="BQ6" s="84"/>
+      <c r="BT6" s="84"/>
+      <c r="BW6" s="84"/>
+      <c r="BY6" s="84"/>
+      <c r="BZ6" s="84"/>
+      <c r="CC6" s="84"/>
+      <c r="CF6" s="84"/>
+      <c r="CI6" s="84"/>
+      <c r="CL6" s="84"/>
+      <c r="CO6" s="84"/>
+      <c r="CR6" s="84"/>
+      <c r="CU6" s="84"/>
     </row>
     <row r="7" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A7" s="9"/>
       <c r="B7" s="9"/>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
-      <c r="E7" s="76" t="str">
+      <c r="E7" s="74" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -8232,38 +8914,38 @@
       <c r="AJ7" s="30"/>
       <c r="AK7" s="31"/>
       <c r="AL7" s="34"/>
-      <c r="AM7" s="57" t="str">
+      <c r="AM7" s="56" t="str">
         <f t="shared" si="4"/>
         <v>NA</v>
       </c>
-      <c r="AP7" s="90"/>
-      <c r="AS7" s="90"/>
-      <c r="AV7" s="90"/>
-      <c r="AY7" s="90"/>
-      <c r="BB7" s="90"/>
-      <c r="BE7" s="90"/>
-      <c r="BH7" s="90"/>
-      <c r="BK7" s="90"/>
-      <c r="BN7" s="90"/>
-      <c r="BQ7" s="90"/>
-      <c r="BT7" s="90"/>
-      <c r="BW7" s="90"/>
-      <c r="BY7" s="90"/>
-      <c r="BZ7" s="90"/>
-      <c r="CC7" s="90"/>
-      <c r="CF7" s="90"/>
-      <c r="CI7" s="90"/>
-      <c r="CL7" s="90"/>
-      <c r="CO7" s="90"/>
-      <c r="CR7" s="90"/>
-      <c r="CU7" s="90"/>
+      <c r="AP7" s="84"/>
+      <c r="AS7" s="84"/>
+      <c r="AV7" s="84"/>
+      <c r="AY7" s="84"/>
+      <c r="BB7" s="84"/>
+      <c r="BE7" s="84"/>
+      <c r="BH7" s="84"/>
+      <c r="BK7" s="84"/>
+      <c r="BN7" s="84"/>
+      <c r="BQ7" s="84"/>
+      <c r="BT7" s="84"/>
+      <c r="BW7" s="84"/>
+      <c r="BY7" s="84"/>
+      <c r="BZ7" s="84"/>
+      <c r="CC7" s="84"/>
+      <c r="CF7" s="84"/>
+      <c r="CI7" s="84"/>
+      <c r="CL7" s="84"/>
+      <c r="CO7" s="84"/>
+      <c r="CR7" s="84"/>
+      <c r="CU7" s="84"/>
     </row>
     <row r="8" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A8" s="9"/>
       <c r="B8" s="9"/>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
-      <c r="E8" s="76" t="str">
+      <c r="E8" s="74" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -8315,41 +8997,41 @@
       <c r="AJ8" s="30"/>
       <c r="AK8" s="31"/>
       <c r="AL8" s="34"/>
-      <c r="AM8" s="57" t="str">
+      <c r="AM8" s="56" t="str">
         <f t="shared" si="4"/>
         <v>NA</v>
       </c>
-      <c r="AO8" s="91"/>
-      <c r="AP8" s="90"/>
-      <c r="AS8" s="90"/>
-      <c r="AV8" s="90"/>
-      <c r="AY8" s="90"/>
-      <c r="BB8" s="90"/>
-      <c r="BE8" s="90"/>
-      <c r="BH8" s="90"/>
-      <c r="BK8" s="90"/>
-      <c r="BN8" s="90"/>
-      <c r="BQ8" s="90"/>
-      <c r="BT8" s="90"/>
-      <c r="BW8" s="90"/>
-      <c r="BY8" s="90"/>
-      <c r="BZ8" s="90"/>
-      <c r="CC8" s="90"/>
-      <c r="CF8" s="90"/>
-      <c r="CI8" s="90"/>
-      <c r="CL8" s="90"/>
-      <c r="CO8" s="90"/>
-      <c r="CQ8" s="91"/>
-      <c r="CR8" s="90"/>
-      <c r="CT8" s="91"/>
-      <c r="CU8" s="90"/>
+      <c r="AO8" s="55"/>
+      <c r="AP8" s="84"/>
+      <c r="AS8" s="84"/>
+      <c r="AV8" s="84"/>
+      <c r="AY8" s="84"/>
+      <c r="BB8" s="84"/>
+      <c r="BE8" s="84"/>
+      <c r="BH8" s="84"/>
+      <c r="BK8" s="84"/>
+      <c r="BN8" s="84"/>
+      <c r="BQ8" s="84"/>
+      <c r="BT8" s="84"/>
+      <c r="BW8" s="84"/>
+      <c r="BY8" s="84"/>
+      <c r="BZ8" s="84"/>
+      <c r="CC8" s="84"/>
+      <c r="CF8" s="84"/>
+      <c r="CI8" s="84"/>
+      <c r="CL8" s="84"/>
+      <c r="CO8" s="84"/>
+      <c r="CQ8" s="55"/>
+      <c r="CR8" s="84"/>
+      <c r="CT8" s="55"/>
+      <c r="CU8" s="84"/>
     </row>
     <row r="9" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A9" s="9"/>
       <c r="B9" s="9"/>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
-      <c r="E9" s="76" t="str">
+      <c r="E9" s="74" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -8401,41 +9083,41 @@
       <c r="AJ9" s="30"/>
       <c r="AK9" s="31"/>
       <c r="AL9" s="34"/>
-      <c r="AM9" s="57" t="str">
+      <c r="AM9" s="56" t="str">
         <f t="shared" si="4"/>
         <v>NA</v>
       </c>
-      <c r="AP9" s="90"/>
-      <c r="AS9" s="90"/>
-      <c r="AV9" s="90"/>
-      <c r="AY9" s="90"/>
-      <c r="BB9" s="90"/>
-      <c r="BE9" s="90"/>
-      <c r="BH9" s="90"/>
-      <c r="BJ9" s="92"/>
-      <c r="BK9" s="90"/>
-      <c r="BN9" s="90"/>
-      <c r="BQ9" s="90"/>
-      <c r="BT9" s="90"/>
-      <c r="BW9" s="90"/>
-      <c r="BY9" s="90"/>
-      <c r="BZ9" s="90"/>
-      <c r="CC9" s="90"/>
-      <c r="CF9" s="90"/>
-      <c r="CI9" s="90"/>
-      <c r="CL9" s="90"/>
-      <c r="CO9" s="90"/>
-      <c r="CQ9" s="90"/>
-      <c r="CR9" s="90"/>
-      <c r="CT9" s="90"/>
-      <c r="CU9" s="90"/>
+      <c r="AP9" s="84"/>
+      <c r="AS9" s="84"/>
+      <c r="AV9" s="84"/>
+      <c r="AY9" s="84"/>
+      <c r="BB9" s="84"/>
+      <c r="BE9" s="84"/>
+      <c r="BH9" s="84"/>
+      <c r="BJ9" s="85"/>
+      <c r="BK9" s="84"/>
+      <c r="BN9" s="84"/>
+      <c r="BQ9" s="84"/>
+      <c r="BT9" s="84"/>
+      <c r="BW9" s="84"/>
+      <c r="BY9" s="84"/>
+      <c r="BZ9" s="84"/>
+      <c r="CC9" s="84"/>
+      <c r="CF9" s="84"/>
+      <c r="CI9" s="84"/>
+      <c r="CL9" s="84"/>
+      <c r="CO9" s="84"/>
+      <c r="CQ9" s="84"/>
+      <c r="CR9" s="84"/>
+      <c r="CT9" s="84"/>
+      <c r="CU9" s="84"/>
     </row>
     <row r="10" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A10" s="9"/>
       <c r="B10" s="9"/>
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
-      <c r="E10" s="76" t="str">
+      <c r="E10" s="74" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -8487,46 +9169,46 @@
       <c r="AJ10" s="30"/>
       <c r="AK10" s="31"/>
       <c r="AL10" s="34"/>
-      <c r="AM10" s="57" t="str">
+      <c r="AM10" s="56" t="str">
         <f t="shared" si="4"/>
         <v>NA</v>
       </c>
-      <c r="AO10" s="92"/>
-      <c r="AP10" s="90"/>
-      <c r="AS10" s="90"/>
-      <c r="AV10" s="90"/>
-      <c r="AY10" s="90"/>
-      <c r="BB10" s="90"/>
-      <c r="BE10" s="90"/>
-      <c r="BH10" s="90"/>
-      <c r="BK10" s="90"/>
-      <c r="BN10" s="90"/>
-      <c r="BQ10" s="90"/>
-      <c r="BT10" s="90"/>
-      <c r="BW10" s="90"/>
-      <c r="BY10" s="90"/>
-      <c r="BZ10" s="90"/>
-      <c r="CB10" s="92"/>
-      <c r="CC10" s="90"/>
-      <c r="CE10" s="92"/>
-      <c r="CF10" s="90"/>
-      <c r="CH10" s="92"/>
-      <c r="CI10" s="90"/>
-      <c r="CK10" s="92"/>
-      <c r="CL10" s="90"/>
-      <c r="CN10" s="92"/>
-      <c r="CO10" s="90"/>
-      <c r="CQ10" s="92"/>
-      <c r="CR10" s="90"/>
-      <c r="CT10" s="92"/>
-      <c r="CU10" s="90"/>
+      <c r="AO10" s="85"/>
+      <c r="AP10" s="84"/>
+      <c r="AS10" s="84"/>
+      <c r="AV10" s="84"/>
+      <c r="AY10" s="84"/>
+      <c r="BB10" s="84"/>
+      <c r="BE10" s="84"/>
+      <c r="BH10" s="84"/>
+      <c r="BK10" s="84"/>
+      <c r="BN10" s="84"/>
+      <c r="BQ10" s="84"/>
+      <c r="BT10" s="84"/>
+      <c r="BW10" s="84"/>
+      <c r="BY10" s="84"/>
+      <c r="BZ10" s="84"/>
+      <c r="CB10" s="85"/>
+      <c r="CC10" s="84"/>
+      <c r="CE10" s="85"/>
+      <c r="CF10" s="84"/>
+      <c r="CH10" s="85"/>
+      <c r="CI10" s="84"/>
+      <c r="CK10" s="85"/>
+      <c r="CL10" s="84"/>
+      <c r="CN10" s="85"/>
+      <c r="CO10" s="84"/>
+      <c r="CQ10" s="85"/>
+      <c r="CR10" s="84"/>
+      <c r="CT10" s="85"/>
+      <c r="CU10" s="84"/>
     </row>
     <row r="11" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A11" s="9"/>
       <c r="B11" s="9"/>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
-      <c r="E11" s="76" t="str">
+      <c r="E11" s="74" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -8578,50 +9260,50 @@
       <c r="AJ11" s="30"/>
       <c r="AK11" s="31"/>
       <c r="AL11" s="34"/>
-      <c r="AM11" s="57" t="str">
+      <c r="AM11" s="56" t="str">
         <f t="shared" si="4"/>
         <v>NA</v>
       </c>
-      <c r="AO11" s="92"/>
-      <c r="AP11" s="90"/>
-      <c r="AS11" s="90"/>
-      <c r="AV11" s="90"/>
-      <c r="AX11" s="92"/>
-      <c r="AY11" s="90"/>
-      <c r="BA11" s="92"/>
-      <c r="BB11" s="90"/>
-      <c r="BE11" s="90"/>
-      <c r="BG11" s="92"/>
-      <c r="BH11" s="90"/>
-      <c r="BK11" s="90"/>
-      <c r="BM11" s="92"/>
-      <c r="BN11" s="90"/>
-      <c r="BQ11" s="90"/>
-      <c r="BT11" s="90"/>
-      <c r="BW11" s="90"/>
-      <c r="BY11" s="90"/>
-      <c r="BZ11" s="90"/>
-      <c r="CB11" s="92"/>
-      <c r="CC11" s="90"/>
-      <c r="CE11" s="92"/>
-      <c r="CF11" s="90"/>
-      <c r="CH11" s="92"/>
-      <c r="CI11" s="90"/>
-      <c r="CK11" s="92"/>
-      <c r="CL11" s="90"/>
-      <c r="CN11" s="92"/>
-      <c r="CO11" s="90"/>
-      <c r="CQ11" s="92"/>
-      <c r="CR11" s="90"/>
-      <c r="CT11" s="92"/>
-      <c r="CU11" s="90"/>
+      <c r="AO11" s="85"/>
+      <c r="AP11" s="84"/>
+      <c r="AS11" s="84"/>
+      <c r="AV11" s="84"/>
+      <c r="AX11" s="85"/>
+      <c r="AY11" s="84"/>
+      <c r="BA11" s="85"/>
+      <c r="BB11" s="84"/>
+      <c r="BE11" s="84"/>
+      <c r="BG11" s="85"/>
+      <c r="BH11" s="84"/>
+      <c r="BK11" s="84"/>
+      <c r="BM11" s="85"/>
+      <c r="BN11" s="84"/>
+      <c r="BQ11" s="84"/>
+      <c r="BT11" s="84"/>
+      <c r="BW11" s="84"/>
+      <c r="BY11" s="84"/>
+      <c r="BZ11" s="84"/>
+      <c r="CB11" s="85"/>
+      <c r="CC11" s="84"/>
+      <c r="CE11" s="85"/>
+      <c r="CF11" s="84"/>
+      <c r="CH11" s="85"/>
+      <c r="CI11" s="84"/>
+      <c r="CK11" s="85"/>
+      <c r="CL11" s="84"/>
+      <c r="CN11" s="85"/>
+      <c r="CO11" s="84"/>
+      <c r="CQ11" s="85"/>
+      <c r="CR11" s="84"/>
+      <c r="CT11" s="85"/>
+      <c r="CU11" s="84"/>
     </row>
     <row r="12" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A12" s="9"/>
       <c r="B12" s="9"/>
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
-      <c r="E12" s="76" t="str">
+      <c r="E12" s="74" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -8673,45 +9355,45 @@
       <c r="AJ12" s="30"/>
       <c r="AK12" s="31"/>
       <c r="AL12" s="34"/>
-      <c r="AM12" s="57" t="str">
+      <c r="AM12" s="56" t="str">
         <f t="shared" si="4"/>
         <v>NA</v>
       </c>
-      <c r="AP12" s="90"/>
-      <c r="AS12" s="90"/>
-      <c r="AV12" s="90"/>
-      <c r="AY12" s="90"/>
-      <c r="BB12" s="90"/>
-      <c r="BE12" s="90"/>
-      <c r="BH12" s="90"/>
-      <c r="BK12" s="90"/>
-      <c r="BN12" s="90"/>
-      <c r="BQ12" s="90"/>
-      <c r="BT12" s="90"/>
-      <c r="BW12" s="90"/>
-      <c r="BY12" s="90"/>
-      <c r="BZ12" s="90"/>
-      <c r="CB12" s="91"/>
-      <c r="CC12" s="90"/>
-      <c r="CE12" s="91"/>
-      <c r="CF12" s="90"/>
-      <c r="CH12" s="91"/>
-      <c r="CI12" s="90"/>
-      <c r="CK12" s="91"/>
-      <c r="CL12" s="90"/>
-      <c r="CN12" s="91"/>
-      <c r="CO12" s="90"/>
-      <c r="CQ12" s="91"/>
-      <c r="CR12" s="90"/>
-      <c r="CT12" s="91"/>
-      <c r="CU12" s="90"/>
+      <c r="AP12" s="84"/>
+      <c r="AS12" s="84"/>
+      <c r="AV12" s="84"/>
+      <c r="AY12" s="84"/>
+      <c r="BB12" s="84"/>
+      <c r="BE12" s="84"/>
+      <c r="BH12" s="84"/>
+      <c r="BK12" s="84"/>
+      <c r="BN12" s="84"/>
+      <c r="BQ12" s="84"/>
+      <c r="BT12" s="84"/>
+      <c r="BW12" s="84"/>
+      <c r="BY12" s="84"/>
+      <c r="BZ12" s="84"/>
+      <c r="CB12" s="55"/>
+      <c r="CC12" s="84"/>
+      <c r="CE12" s="55"/>
+      <c r="CF12" s="84"/>
+      <c r="CH12" s="55"/>
+      <c r="CI12" s="84"/>
+      <c r="CK12" s="55"/>
+      <c r="CL12" s="84"/>
+      <c r="CN12" s="55"/>
+      <c r="CO12" s="84"/>
+      <c r="CQ12" s="55"/>
+      <c r="CR12" s="84"/>
+      <c r="CT12" s="55"/>
+      <c r="CU12" s="84"/>
     </row>
     <row r="13" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A13" s="9"/>
       <c r="B13" s="9"/>
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
-      <c r="E13" s="76" t="str">
+      <c r="E13" s="74" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -8763,42 +9445,42 @@
       <c r="AJ13" s="30"/>
       <c r="AK13" s="31"/>
       <c r="AL13" s="34"/>
-      <c r="AM13" s="57" t="str">
+      <c r="AM13" s="56" t="str">
         <f t="shared" si="4"/>
         <v>NA</v>
       </c>
-      <c r="AP13" s="90"/>
-      <c r="AS13" s="90"/>
-      <c r="AV13" s="90"/>
-      <c r="AY13" s="90"/>
-      <c r="BB13" s="90"/>
-      <c r="BE13" s="90"/>
-      <c r="BG13" s="92"/>
-      <c r="BH13" s="90"/>
-      <c r="BK13" s="90"/>
-      <c r="BN13" s="90"/>
-      <c r="BQ13" s="90"/>
-      <c r="BS13" s="92"/>
-      <c r="BT13" s="90"/>
-      <c r="BW13" s="90"/>
-      <c r="BY13" s="90"/>
-      <c r="BZ13" s="90"/>
-      <c r="CC13" s="90"/>
-      <c r="CF13" s="90"/>
-      <c r="CI13" s="90"/>
-      <c r="CK13" s="92"/>
-      <c r="CL13" s="90"/>
-      <c r="CN13" s="92"/>
-      <c r="CO13" s="90"/>
-      <c r="CR13" s="90"/>
-      <c r="CU13" s="90"/>
+      <c r="AP13" s="84"/>
+      <c r="AS13" s="84"/>
+      <c r="AV13" s="84"/>
+      <c r="AY13" s="84"/>
+      <c r="BB13" s="84"/>
+      <c r="BE13" s="84"/>
+      <c r="BG13" s="85"/>
+      <c r="BH13" s="84"/>
+      <c r="BK13" s="84"/>
+      <c r="BN13" s="84"/>
+      <c r="BQ13" s="84"/>
+      <c r="BS13" s="85"/>
+      <c r="BT13" s="84"/>
+      <c r="BW13" s="84"/>
+      <c r="BY13" s="84"/>
+      <c r="BZ13" s="84"/>
+      <c r="CC13" s="84"/>
+      <c r="CF13" s="84"/>
+      <c r="CI13" s="84"/>
+      <c r="CK13" s="85"/>
+      <c r="CL13" s="84"/>
+      <c r="CN13" s="85"/>
+      <c r="CO13" s="84"/>
+      <c r="CR13" s="84"/>
+      <c r="CU13" s="84"/>
     </row>
     <row r="14" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A14" s="9"/>
       <c r="B14" s="9"/>
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
-      <c r="E14" s="76" t="str">
+      <c r="E14" s="74" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -8850,44 +9532,44 @@
       <c r="AJ14" s="30"/>
       <c r="AK14" s="31"/>
       <c r="AL14" s="32"/>
-      <c r="AM14" s="57" t="str">
+      <c r="AM14" s="56" t="str">
         <f t="shared" si="4"/>
         <v>NA</v>
       </c>
-      <c r="AP14" s="90"/>
-      <c r="AS14" s="90"/>
-      <c r="AV14" s="90"/>
-      <c r="AX14" s="92"/>
-      <c r="AY14" s="90"/>
-      <c r="BA14" s="92"/>
-      <c r="BB14" s="90"/>
-      <c r="BE14" s="90"/>
-      <c r="BG14" s="92"/>
-      <c r="BH14" s="90"/>
-      <c r="BJ14" s="92"/>
-      <c r="BK14" s="90"/>
-      <c r="BN14" s="90"/>
-      <c r="BQ14" s="90"/>
-      <c r="BS14" s="92"/>
-      <c r="BT14" s="90"/>
-      <c r="BV14" s="92"/>
-      <c r="BW14" s="90"/>
-      <c r="BY14" s="90"/>
-      <c r="BZ14" s="90"/>
-      <c r="CC14" s="90"/>
-      <c r="CF14" s="90"/>
-      <c r="CI14" s="90"/>
-      <c r="CL14" s="90"/>
-      <c r="CO14" s="90"/>
-      <c r="CR14" s="90"/>
-      <c r="CU14" s="90"/>
+      <c r="AP14" s="84"/>
+      <c r="AS14" s="84"/>
+      <c r="AV14" s="84"/>
+      <c r="AX14" s="85"/>
+      <c r="AY14" s="84"/>
+      <c r="BA14" s="85"/>
+      <c r="BB14" s="84"/>
+      <c r="BE14" s="84"/>
+      <c r="BG14" s="85"/>
+      <c r="BH14" s="84"/>
+      <c r="BJ14" s="85"/>
+      <c r="BK14" s="84"/>
+      <c r="BN14" s="84"/>
+      <c r="BQ14" s="84"/>
+      <c r="BS14" s="85"/>
+      <c r="BT14" s="84"/>
+      <c r="BV14" s="85"/>
+      <c r="BW14" s="84"/>
+      <c r="BY14" s="84"/>
+      <c r="BZ14" s="84"/>
+      <c r="CC14" s="84"/>
+      <c r="CF14" s="84"/>
+      <c r="CI14" s="84"/>
+      <c r="CL14" s="84"/>
+      <c r="CO14" s="84"/>
+      <c r="CR14" s="84"/>
+      <c r="CU14" s="84"/>
     </row>
     <row r="15" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A15" s="9"/>
       <c r="B15" s="9"/>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
-      <c r="E15" s="76" t="str">
+      <c r="E15" s="74" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -8939,43 +9621,43 @@
       <c r="AJ15" s="30"/>
       <c r="AK15" s="31"/>
       <c r="AL15" s="34"/>
-      <c r="AM15" s="57" t="str">
+      <c r="AM15" s="56" t="str">
         <f t="shared" si="4"/>
         <v>NA</v>
       </c>
-      <c r="AP15" s="90"/>
-      <c r="AS15" s="90"/>
-      <c r="AV15" s="90"/>
-      <c r="AY15" s="90"/>
-      <c r="BB15" s="90"/>
-      <c r="BE15" s="90"/>
-      <c r="BG15" s="92"/>
-      <c r="BH15" s="90"/>
-      <c r="BK15" s="90"/>
-      <c r="BN15" s="90"/>
-      <c r="BQ15" s="90"/>
-      <c r="BS15" s="92"/>
-      <c r="BT15" s="90"/>
-      <c r="BV15" s="91"/>
-      <c r="BW15" s="90"/>
-      <c r="BY15" s="90"/>
-      <c r="BZ15" s="90"/>
-      <c r="CB15" s="91"/>
-      <c r="CC15" s="90"/>
-      <c r="CE15" s="91"/>
-      <c r="CF15" s="90"/>
-      <c r="CI15" s="90"/>
-      <c r="CL15" s="90"/>
-      <c r="CO15" s="90"/>
-      <c r="CR15" s="90"/>
-      <c r="CU15" s="90"/>
+      <c r="AP15" s="84"/>
+      <c r="AS15" s="84"/>
+      <c r="AV15" s="84"/>
+      <c r="AY15" s="84"/>
+      <c r="BB15" s="84"/>
+      <c r="BE15" s="84"/>
+      <c r="BG15" s="85"/>
+      <c r="BH15" s="84"/>
+      <c r="BK15" s="84"/>
+      <c r="BN15" s="84"/>
+      <c r="BQ15" s="84"/>
+      <c r="BS15" s="85"/>
+      <c r="BT15" s="84"/>
+      <c r="BV15" s="55"/>
+      <c r="BW15" s="84"/>
+      <c r="BY15" s="84"/>
+      <c r="BZ15" s="84"/>
+      <c r="CB15" s="55"/>
+      <c r="CC15" s="84"/>
+      <c r="CE15" s="55"/>
+      <c r="CF15" s="84"/>
+      <c r="CI15" s="84"/>
+      <c r="CL15" s="84"/>
+      <c r="CO15" s="84"/>
+      <c r="CR15" s="84"/>
+      <c r="CU15" s="84"/>
     </row>
     <row r="16" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A16" s="9"/>
       <c r="B16" s="9"/>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
-      <c r="E16" s="76" t="str">
+      <c r="E16" s="74" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -9027,55 +9709,54 @@
       <c r="AJ16" s="30"/>
       <c r="AK16" s="31"/>
       <c r="AL16" s="34"/>
-      <c r="AM16" s="57" t="str">
+      <c r="AM16" s="56" t="str">
         <f t="shared" si="4"/>
         <v>NA</v>
       </c>
-      <c r="AO16" s="92"/>
-      <c r="AP16" s="90"/>
-      <c r="AR16" s="92"/>
-      <c r="AS16" s="90"/>
-      <c r="AU16" s="92"/>
-      <c r="AV16" s="90"/>
-      <c r="AX16" s="92"/>
-      <c r="AY16" s="90"/>
-      <c r="BA16" s="92"/>
-      <c r="BB16" s="90"/>
-      <c r="BD16" s="92"/>
-      <c r="BE16" s="90"/>
-      <c r="BG16" s="92"/>
-      <c r="BH16" s="90"/>
-      <c r="BI16" s="89"/>
-      <c r="BJ16" s="92"/>
-      <c r="BK16" s="90"/>
-      <c r="BN16" s="90"/>
-      <c r="BQ16" s="90"/>
-      <c r="BS16" s="90"/>
-      <c r="BT16" s="90"/>
-      <c r="BW16" s="90"/>
-      <c r="BY16" s="90"/>
-      <c r="BZ16" s="90"/>
-      <c r="CB16" s="92"/>
-      <c r="CC16" s="90"/>
-      <c r="CE16" s="92"/>
-      <c r="CF16" s="90"/>
-      <c r="CH16" s="92"/>
-      <c r="CI16" s="90"/>
-      <c r="CK16" s="92"/>
-      <c r="CL16" s="90"/>
-      <c r="CN16" s="92"/>
-      <c r="CO16" s="90"/>
-      <c r="CQ16" s="92"/>
-      <c r="CR16" s="90"/>
-      <c r="CT16" s="92"/>
-      <c r="CU16" s="90"/>
+      <c r="AO16" s="85"/>
+      <c r="AP16" s="84"/>
+      <c r="AR16" s="85"/>
+      <c r="AS16" s="84"/>
+      <c r="AU16" s="85"/>
+      <c r="AV16" s="84"/>
+      <c r="AX16" s="85"/>
+      <c r="AY16" s="84"/>
+      <c r="BA16" s="85"/>
+      <c r="BB16" s="84"/>
+      <c r="BD16" s="85"/>
+      <c r="BE16" s="84"/>
+      <c r="BG16" s="85"/>
+      <c r="BH16" s="84"/>
+      <c r="BJ16" s="85"/>
+      <c r="BK16" s="84"/>
+      <c r="BN16" s="84"/>
+      <c r="BQ16" s="84"/>
+      <c r="BS16" s="84"/>
+      <c r="BT16" s="84"/>
+      <c r="BW16" s="84"/>
+      <c r="BY16" s="84"/>
+      <c r="BZ16" s="84"/>
+      <c r="CB16" s="85"/>
+      <c r="CC16" s="84"/>
+      <c r="CE16" s="85"/>
+      <c r="CF16" s="84"/>
+      <c r="CH16" s="85"/>
+      <c r="CI16" s="84"/>
+      <c r="CK16" s="85"/>
+      <c r="CL16" s="84"/>
+      <c r="CN16" s="85"/>
+      <c r="CO16" s="84"/>
+      <c r="CQ16" s="85"/>
+      <c r="CR16" s="84"/>
+      <c r="CT16" s="85"/>
+      <c r="CU16" s="84"/>
     </row>
     <row r="17" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A17" s="9"/>
       <c r="B17" s="9"/>
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
-      <c r="E17" s="76" t="str">
+      <c r="E17" s="74" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -9127,58 +9808,55 @@
       <c r="AJ17" s="30"/>
       <c r="AK17" s="31"/>
       <c r="AL17" s="34"/>
-      <c r="AM17" s="57" t="str">
+      <c r="AM17" s="56" t="str">
         <f t="shared" si="4"/>
         <v>NA</v>
       </c>
-      <c r="AO17" s="92"/>
-      <c r="AP17" s="90"/>
-      <c r="AR17" s="92"/>
-      <c r="AS17" s="90"/>
-      <c r="AU17" s="92"/>
-      <c r="AV17" s="90"/>
-      <c r="AX17" s="92"/>
-      <c r="AY17" s="90"/>
-      <c r="BA17" s="92"/>
-      <c r="BB17" s="90"/>
-      <c r="BD17" s="92"/>
-      <c r="BE17" s="90"/>
-      <c r="BG17" s="92"/>
-      <c r="BH17" s="90"/>
-      <c r="BI17" s="89"/>
-      <c r="BJ17" s="92"/>
-      <c r="BK17" s="90"/>
-      <c r="BL17" s="89"/>
-      <c r="BM17" s="92"/>
-      <c r="BN17" s="90"/>
-      <c r="BO17" s="89"/>
-      <c r="BP17" s="92"/>
-      <c r="BQ17" s="90"/>
-      <c r="BT17" s="90"/>
-      <c r="BW17" s="90"/>
-      <c r="BY17" s="90"/>
-      <c r="BZ17" s="90"/>
-      <c r="CB17" s="92"/>
-      <c r="CC17" s="90"/>
-      <c r="CE17" s="92"/>
-      <c r="CF17" s="90"/>
-      <c r="CH17" s="92"/>
-      <c r="CI17" s="90"/>
-      <c r="CK17" s="92"/>
-      <c r="CL17" s="90"/>
-      <c r="CN17" s="92"/>
-      <c r="CO17" s="90"/>
-      <c r="CQ17" s="92"/>
-      <c r="CR17" s="90"/>
-      <c r="CT17" s="92"/>
-      <c r="CU17" s="90"/>
+      <c r="AO17" s="85"/>
+      <c r="AP17" s="84"/>
+      <c r="AR17" s="85"/>
+      <c r="AS17" s="84"/>
+      <c r="AU17" s="85"/>
+      <c r="AV17" s="84"/>
+      <c r="AX17" s="85"/>
+      <c r="AY17" s="84"/>
+      <c r="BA17" s="85"/>
+      <c r="BB17" s="84"/>
+      <c r="BD17" s="85"/>
+      <c r="BE17" s="84"/>
+      <c r="BG17" s="85"/>
+      <c r="BH17" s="84"/>
+      <c r="BJ17" s="85"/>
+      <c r="BK17" s="84"/>
+      <c r="BM17" s="85"/>
+      <c r="BN17" s="84"/>
+      <c r="BP17" s="85"/>
+      <c r="BQ17" s="84"/>
+      <c r="BT17" s="84"/>
+      <c r="BW17" s="84"/>
+      <c r="BY17" s="84"/>
+      <c r="BZ17" s="84"/>
+      <c r="CB17" s="85"/>
+      <c r="CC17" s="84"/>
+      <c r="CE17" s="85"/>
+      <c r="CF17" s="84"/>
+      <c r="CH17" s="85"/>
+      <c r="CI17" s="84"/>
+      <c r="CK17" s="85"/>
+      <c r="CL17" s="84"/>
+      <c r="CN17" s="85"/>
+      <c r="CO17" s="84"/>
+      <c r="CQ17" s="85"/>
+      <c r="CR17" s="84"/>
+      <c r="CT17" s="85"/>
+      <c r="CU17" s="84"/>
     </row>
     <row r="18" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A18" s="9"/>
       <c r="B18" s="9"/>
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
-      <c r="E18" s="76" t="str">
+      <c r="E18" s="74" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -9230,55 +9908,55 @@
       <c r="AJ18" s="30"/>
       <c r="AK18" s="31"/>
       <c r="AL18" s="34"/>
-      <c r="AM18" s="57" t="str">
+      <c r="AM18" s="56" t="str">
         <f t="shared" si="4"/>
         <v>NA</v>
       </c>
-      <c r="AO18" s="92"/>
-      <c r="AP18" s="90"/>
-      <c r="AR18" s="92"/>
-      <c r="AS18" s="90"/>
-      <c r="AU18" s="92"/>
-      <c r="AV18" s="90"/>
-      <c r="AX18" s="92"/>
-      <c r="AY18" s="90"/>
-      <c r="BA18" s="92"/>
-      <c r="BB18" s="90"/>
-      <c r="BD18" s="92"/>
-      <c r="BE18" s="90"/>
-      <c r="BG18" s="92"/>
-      <c r="BH18" s="90"/>
-      <c r="BJ18" s="92"/>
-      <c r="BK18" s="90"/>
-      <c r="BM18" s="92"/>
-      <c r="BN18" s="90"/>
-      <c r="BP18" s="92"/>
-      <c r="BQ18" s="90"/>
-      <c r="BT18" s="90"/>
-      <c r="BW18" s="90"/>
-      <c r="BY18" s="90"/>
-      <c r="BZ18" s="90"/>
-      <c r="CB18" s="92"/>
-      <c r="CC18" s="90"/>
-      <c r="CE18" s="92"/>
-      <c r="CF18" s="90"/>
-      <c r="CH18" s="92"/>
-      <c r="CI18" s="90"/>
-      <c r="CK18" s="92"/>
-      <c r="CL18" s="90"/>
-      <c r="CN18" s="92"/>
-      <c r="CO18" s="90"/>
-      <c r="CQ18" s="92"/>
-      <c r="CR18" s="90"/>
-      <c r="CT18" s="92"/>
-      <c r="CU18" s="90"/>
+      <c r="AO18" s="85"/>
+      <c r="AP18" s="84"/>
+      <c r="AR18" s="85"/>
+      <c r="AS18" s="84"/>
+      <c r="AU18" s="85"/>
+      <c r="AV18" s="84"/>
+      <c r="AX18" s="85"/>
+      <c r="AY18" s="84"/>
+      <c r="BA18" s="85"/>
+      <c r="BB18" s="84"/>
+      <c r="BD18" s="85"/>
+      <c r="BE18" s="84"/>
+      <c r="BG18" s="85"/>
+      <c r="BH18" s="84"/>
+      <c r="BJ18" s="85"/>
+      <c r="BK18" s="84"/>
+      <c r="BM18" s="85"/>
+      <c r="BN18" s="84"/>
+      <c r="BP18" s="85"/>
+      <c r="BQ18" s="84"/>
+      <c r="BT18" s="84"/>
+      <c r="BW18" s="84"/>
+      <c r="BY18" s="84"/>
+      <c r="BZ18" s="84"/>
+      <c r="CB18" s="85"/>
+      <c r="CC18" s="84"/>
+      <c r="CE18" s="85"/>
+      <c r="CF18" s="84"/>
+      <c r="CH18" s="85"/>
+      <c r="CI18" s="84"/>
+      <c r="CK18" s="85"/>
+      <c r="CL18" s="84"/>
+      <c r="CN18" s="85"/>
+      <c r="CO18" s="84"/>
+      <c r="CQ18" s="85"/>
+      <c r="CR18" s="84"/>
+      <c r="CT18" s="85"/>
+      <c r="CU18" s="84"/>
     </row>
     <row r="19" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A19" s="9"/>
       <c r="B19" s="9"/>
       <c r="C19" s="5"/>
       <c r="D19" s="5"/>
-      <c r="E19" s="76" t="str">
+      <c r="E19" s="74" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -9330,55 +10008,55 @@
       <c r="AJ19" s="30"/>
       <c r="AK19" s="31"/>
       <c r="AL19" s="34"/>
-      <c r="AM19" s="57" t="str">
+      <c r="AM19" s="56" t="str">
         <f t="shared" si="4"/>
         <v>NA</v>
       </c>
-      <c r="AO19" s="92"/>
-      <c r="AP19" s="90"/>
-      <c r="AR19" s="92"/>
-      <c r="AS19" s="90"/>
-      <c r="AU19" s="92"/>
-      <c r="AV19" s="90"/>
-      <c r="AX19" s="92"/>
-      <c r="AY19" s="90"/>
-      <c r="BA19" s="92"/>
-      <c r="BB19" s="90"/>
-      <c r="BD19" s="92"/>
-      <c r="BE19" s="90"/>
-      <c r="BG19" s="92"/>
-      <c r="BH19" s="90"/>
-      <c r="BJ19" s="92"/>
-      <c r="BK19" s="90"/>
-      <c r="BM19" s="92"/>
-      <c r="BN19" s="90"/>
-      <c r="BP19" s="92"/>
-      <c r="BQ19" s="90"/>
-      <c r="BT19" s="90"/>
-      <c r="BW19" s="90"/>
-      <c r="BY19" s="90"/>
-      <c r="BZ19" s="90"/>
-      <c r="CB19" s="92"/>
-      <c r="CC19" s="90"/>
-      <c r="CE19" s="92"/>
-      <c r="CF19" s="90"/>
-      <c r="CH19" s="92"/>
-      <c r="CI19" s="90"/>
-      <c r="CK19" s="92"/>
-      <c r="CL19" s="90"/>
-      <c r="CN19" s="92"/>
-      <c r="CO19" s="90"/>
-      <c r="CQ19" s="92"/>
-      <c r="CR19" s="90"/>
-      <c r="CT19" s="92"/>
-      <c r="CU19" s="90"/>
+      <c r="AO19" s="85"/>
+      <c r="AP19" s="84"/>
+      <c r="AR19" s="85"/>
+      <c r="AS19" s="84"/>
+      <c r="AU19" s="85"/>
+      <c r="AV19" s="84"/>
+      <c r="AX19" s="85"/>
+      <c r="AY19" s="84"/>
+      <c r="BA19" s="85"/>
+      <c r="BB19" s="84"/>
+      <c r="BD19" s="85"/>
+      <c r="BE19" s="84"/>
+      <c r="BG19" s="85"/>
+      <c r="BH19" s="84"/>
+      <c r="BJ19" s="85"/>
+      <c r="BK19" s="84"/>
+      <c r="BM19" s="85"/>
+      <c r="BN19" s="84"/>
+      <c r="BP19" s="85"/>
+      <c r="BQ19" s="84"/>
+      <c r="BT19" s="84"/>
+      <c r="BW19" s="84"/>
+      <c r="BY19" s="84"/>
+      <c r="BZ19" s="84"/>
+      <c r="CB19" s="85"/>
+      <c r="CC19" s="84"/>
+      <c r="CE19" s="85"/>
+      <c r="CF19" s="84"/>
+      <c r="CH19" s="85"/>
+      <c r="CI19" s="84"/>
+      <c r="CK19" s="85"/>
+      <c r="CL19" s="84"/>
+      <c r="CN19" s="85"/>
+      <c r="CO19" s="84"/>
+      <c r="CQ19" s="85"/>
+      <c r="CR19" s="84"/>
+      <c r="CT19" s="85"/>
+      <c r="CU19" s="84"/>
     </row>
     <row r="20" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A20" s="9"/>
       <c r="B20" s="9"/>
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
-      <c r="E20" s="76" t="str">
+      <c r="E20" s="74" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -9430,57 +10108,57 @@
       <c r="AJ20" s="30"/>
       <c r="AK20" s="31"/>
       <c r="AL20" s="34"/>
-      <c r="AM20" s="57" t="str">
+      <c r="AM20" s="56" t="str">
         <f t="shared" si="4"/>
         <v>NA</v>
       </c>
-      <c r="AO20" s="92"/>
-      <c r="AP20" s="90"/>
-      <c r="AR20" s="92"/>
-      <c r="AS20" s="90"/>
-      <c r="AU20" s="92"/>
-      <c r="AV20" s="90"/>
-      <c r="AX20" s="92"/>
-      <c r="AY20" s="90"/>
-      <c r="BA20" s="92"/>
-      <c r="BB20" s="90"/>
-      <c r="BD20" s="92"/>
-      <c r="BE20" s="90"/>
-      <c r="BG20" s="92"/>
-      <c r="BH20" s="90"/>
-      <c r="BJ20" s="92"/>
-      <c r="BK20" s="90"/>
-      <c r="BM20" s="92"/>
-      <c r="BN20" s="90"/>
-      <c r="BP20" s="92"/>
-      <c r="BQ20" s="90"/>
-      <c r="BS20" s="92"/>
-      <c r="BT20" s="90"/>
-      <c r="BV20" s="92"/>
-      <c r="BW20" s="90"/>
-      <c r="BY20" s="90"/>
-      <c r="BZ20" s="90"/>
-      <c r="CB20" s="92"/>
-      <c r="CC20" s="90"/>
-      <c r="CE20" s="92"/>
-      <c r="CF20" s="90"/>
-      <c r="CH20" s="92"/>
-      <c r="CI20" s="90"/>
-      <c r="CK20" s="92"/>
-      <c r="CL20" s="90"/>
-      <c r="CN20" s="92"/>
-      <c r="CO20" s="90"/>
-      <c r="CQ20" s="92"/>
-      <c r="CR20" s="90"/>
-      <c r="CT20" s="92"/>
-      <c r="CU20" s="90"/>
+      <c r="AO20" s="85"/>
+      <c r="AP20" s="84"/>
+      <c r="AR20" s="85"/>
+      <c r="AS20" s="84"/>
+      <c r="AU20" s="85"/>
+      <c r="AV20" s="84"/>
+      <c r="AX20" s="85"/>
+      <c r="AY20" s="84"/>
+      <c r="BA20" s="85"/>
+      <c r="BB20" s="84"/>
+      <c r="BD20" s="85"/>
+      <c r="BE20" s="84"/>
+      <c r="BG20" s="85"/>
+      <c r="BH20" s="84"/>
+      <c r="BJ20" s="85"/>
+      <c r="BK20" s="84"/>
+      <c r="BM20" s="85"/>
+      <c r="BN20" s="84"/>
+      <c r="BP20" s="85"/>
+      <c r="BQ20" s="84"/>
+      <c r="BS20" s="85"/>
+      <c r="BT20" s="84"/>
+      <c r="BV20" s="85"/>
+      <c r="BW20" s="84"/>
+      <c r="BY20" s="84"/>
+      <c r="BZ20" s="84"/>
+      <c r="CB20" s="85"/>
+      <c r="CC20" s="84"/>
+      <c r="CE20" s="85"/>
+      <c r="CF20" s="84"/>
+      <c r="CH20" s="85"/>
+      <c r="CI20" s="84"/>
+      <c r="CK20" s="85"/>
+      <c r="CL20" s="84"/>
+      <c r="CN20" s="85"/>
+      <c r="CO20" s="84"/>
+      <c r="CQ20" s="85"/>
+      <c r="CR20" s="84"/>
+      <c r="CT20" s="85"/>
+      <c r="CU20" s="84"/>
     </row>
     <row r="21" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A21" s="9"/>
       <c r="B21" s="9"/>
       <c r="C21" s="5"/>
       <c r="D21" s="5"/>
-      <c r="E21" s="76" t="str">
+      <c r="E21" s="74" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -9509,18 +10187,18 @@
       <c r="S21" s="5"/>
       <c r="T21" s="5"/>
       <c r="U21" s="8"/>
-      <c r="V21" s="78"/>
-      <c r="W21" s="79"/>
-      <c r="X21" s="79"/>
-      <c r="Y21" s="79"/>
-      <c r="Z21" s="79"/>
-      <c r="AA21" s="79"/>
+      <c r="V21" s="76"/>
+      <c r="W21" s="77"/>
+      <c r="X21" s="77"/>
+      <c r="Y21" s="77"/>
+      <c r="Z21" s="77"/>
+      <c r="AA21" s="77"/>
       <c r="AB21" s="20">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AC21" s="80"/>
-      <c r="AD21" s="80"/>
+      <c r="AC21" s="78"/>
+      <c r="AD21" s="78"/>
       <c r="AE21" s="20">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -9532,41 +10210,41 @@
       <c r="AJ21" s="30"/>
       <c r="AK21" s="31"/>
       <c r="AL21" s="32"/>
-      <c r="AM21" s="57" t="str">
+      <c r="AM21" s="56" t="str">
         <f t="shared" si="4"/>
         <v>NA</v>
       </c>
-      <c r="AP21" s="90"/>
-      <c r="AS21" s="90"/>
-      <c r="AV21" s="90"/>
-      <c r="AY21" s="90"/>
-      <c r="BA21" s="92"/>
-      <c r="BB21" s="90"/>
-      <c r="BE21" s="90"/>
-      <c r="BH21" s="90"/>
-      <c r="BJ21" s="90"/>
-      <c r="BK21" s="90"/>
-      <c r="BN21" s="90"/>
-      <c r="BQ21" s="90"/>
-      <c r="BT21" s="90"/>
-      <c r="BW21" s="90"/>
-      <c r="BY21" s="92"/>
-      <c r="BZ21" s="90"/>
-      <c r="CC21" s="90"/>
-      <c r="CF21" s="90"/>
-      <c r="CI21" s="90"/>
-      <c r="CL21" s="90"/>
-      <c r="CO21" s="90"/>
-      <c r="CR21" s="90"/>
-      <c r="CT21" s="90"/>
-      <c r="CU21" s="90"/>
+      <c r="AP21" s="84"/>
+      <c r="AS21" s="84"/>
+      <c r="AV21" s="84"/>
+      <c r="AY21" s="84"/>
+      <c r="BA21" s="85"/>
+      <c r="BB21" s="84"/>
+      <c r="BE21" s="84"/>
+      <c r="BH21" s="84"/>
+      <c r="BJ21" s="84"/>
+      <c r="BK21" s="84"/>
+      <c r="BN21" s="84"/>
+      <c r="BQ21" s="84"/>
+      <c r="BT21" s="84"/>
+      <c r="BW21" s="84"/>
+      <c r="BY21" s="85"/>
+      <c r="BZ21" s="84"/>
+      <c r="CC21" s="84"/>
+      <c r="CF21" s="84"/>
+      <c r="CI21" s="84"/>
+      <c r="CL21" s="84"/>
+      <c r="CO21" s="84"/>
+      <c r="CR21" s="84"/>
+      <c r="CT21" s="84"/>
+      <c r="CU21" s="84"/>
     </row>
     <row r="22" spans="1:99" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A22" s="10"/>
       <c r="B22" s="10"/>
       <c r="C22" s="11"/>
       <c r="D22" s="11"/>
-      <c r="E22" s="77" t="str">
+      <c r="E22" s="75" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -9595,18 +10273,18 @@
       <c r="S22" s="11"/>
       <c r="T22" s="11"/>
       <c r="U22" s="14"/>
-      <c r="V22" s="81"/>
-      <c r="W22" s="70"/>
-      <c r="X22" s="70"/>
-      <c r="Y22" s="70"/>
-      <c r="Z22" s="70"/>
-      <c r="AA22" s="70"/>
+      <c r="V22" s="79"/>
+      <c r="W22" s="69"/>
+      <c r="X22" s="69"/>
+      <c r="Y22" s="69"/>
+      <c r="Z22" s="69"/>
+      <c r="AA22" s="69"/>
       <c r="AB22" s="23">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AC22" s="82"/>
-      <c r="AD22" s="82"/>
+      <c r="AC22" s="80"/>
+      <c r="AD22" s="80"/>
       <c r="AE22" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -9618,35 +10296,35 @@
       <c r="AJ22" s="37"/>
       <c r="AK22" s="38"/>
       <c r="AL22" s="40"/>
-      <c r="AM22" s="87" t="str">
+      <c r="AM22" s="83" t="str">
         <f t="shared" si="4"/>
         <v>NA</v>
       </c>
-      <c r="AO22" s="92"/>
-      <c r="AP22" s="90"/>
-      <c r="AS22" s="90"/>
-      <c r="AV22" s="90"/>
-      <c r="AY22" s="90"/>
-      <c r="BA22" s="92"/>
-      <c r="BB22" s="90"/>
-      <c r="BE22" s="90"/>
-      <c r="BH22" s="90"/>
-      <c r="BJ22" s="92"/>
-      <c r="BK22" s="90"/>
-      <c r="BN22" s="90"/>
-      <c r="BQ22" s="90"/>
-      <c r="BT22" s="90"/>
-      <c r="BW22" s="90"/>
-      <c r="BZ22" s="90"/>
-      <c r="CC22" s="90"/>
-      <c r="CF22" s="90"/>
-      <c r="CI22" s="90"/>
-      <c r="CL22" s="90"/>
-      <c r="CO22" s="90"/>
-      <c r="CQ22" s="92"/>
-      <c r="CR22" s="90"/>
-      <c r="CT22" s="92"/>
-      <c r="CU22" s="90"/>
+      <c r="AO22" s="85"/>
+      <c r="AP22" s="84"/>
+      <c r="AS22" s="84"/>
+      <c r="AV22" s="84"/>
+      <c r="AY22" s="84"/>
+      <c r="BA22" s="85"/>
+      <c r="BB22" s="84"/>
+      <c r="BE22" s="84"/>
+      <c r="BH22" s="84"/>
+      <c r="BJ22" s="85"/>
+      <c r="BK22" s="84"/>
+      <c r="BN22" s="84"/>
+      <c r="BQ22" s="84"/>
+      <c r="BT22" s="84"/>
+      <c r="BW22" s="84"/>
+      <c r="BZ22" s="84"/>
+      <c r="CC22" s="84"/>
+      <c r="CF22" s="84"/>
+      <c r="CI22" s="84"/>
+      <c r="CL22" s="84"/>
+      <c r="CO22" s="84"/>
+      <c r="CQ22" s="85"/>
+      <c r="CR22" s="84"/>
+      <c r="CT22" s="85"/>
+      <c r="CU22" s="84"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9659,234 +10337,234 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="61" t="s">
+      <c r="A1" s="60" t="s">
         <v>98</v>
       </c>
-      <c r="B1" s="62" t="s">
+      <c r="B1" s="61" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="62" t="s">
+      <c r="C1" s="61" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="63" t="s">
+      <c r="D1" s="62" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="64" t="s">
+      <c r="A2" s="63" t="s">
         <v>99</v>
       </c>
-      <c r="B2" s="65">
+      <c r="B2" s="64">
         <v>-5.4793240000000001</v>
       </c>
-      <c r="C2" s="65">
+      <c r="C2" s="64">
         <v>119.31157399999999</v>
       </c>
-      <c r="D2" s="66"/>
+      <c r="D2" s="65"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="64" t="s">
+      <c r="A3" s="63" t="s">
         <v>100</v>
       </c>
-      <c r="B3" s="65">
+      <c r="B3" s="64">
         <v>-5.4880659999999999</v>
       </c>
-      <c r="C3" s="65">
+      <c r="C3" s="64">
         <v>119.31312699999999</v>
       </c>
-      <c r="D3" s="66"/>
+      <c r="D3" s="65"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="64" t="s">
+      <c r="A4" s="63" t="s">
         <v>101</v>
       </c>
-      <c r="B4" s="65">
+      <c r="B4" s="64">
         <v>-5.4889159999999997</v>
       </c>
-      <c r="C4" s="65">
+      <c r="C4" s="64">
         <v>119.309448</v>
       </c>
-      <c r="D4" s="66"/>
+      <c r="D4" s="65"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="64" t="s">
+      <c r="A5" s="63" t="s">
         <v>102</v>
       </c>
-      <c r="B5" s="65">
+      <c r="B5" s="64">
         <v>-5.468826</v>
       </c>
-      <c r="C5" s="65">
+      <c r="C5" s="64">
         <v>119.300459</v>
       </c>
-      <c r="D5" s="66"/>
+      <c r="D5" s="65"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="64" t="s">
+      <c r="A6" s="63" t="s">
         <v>103</v>
       </c>
-      <c r="B6" s="65">
+      <c r="B6" s="64">
         <v>-5.4682649999999997</v>
       </c>
-      <c r="C6" s="65">
+      <c r="C6" s="64">
         <v>119.30207900000001</v>
       </c>
-      <c r="D6" s="66"/>
+      <c r="D6" s="65"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="64" t="s">
+      <c r="A7" s="63" t="s">
         <v>96</v>
       </c>
-      <c r="B7" s="65">
+      <c r="B7" s="64">
         <v>-5.4671349999999999</v>
       </c>
-      <c r="C7" s="65">
+      <c r="C7" s="64">
         <v>119.302812</v>
       </c>
-      <c r="D7" s="66"/>
+      <c r="D7" s="65"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" s="64" t="s">
+      <c r="A8" s="63" t="s">
         <v>104</v>
       </c>
-      <c r="B8" s="65">
+      <c r="B8" s="64">
         <v>-5.4901910000000003</v>
       </c>
-      <c r="C8" s="65">
+      <c r="C8" s="64">
         <v>119.311859</v>
       </c>
-      <c r="D8" s="66"/>
+      <c r="D8" s="65"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="64" t="s">
+      <c r="A9" s="63" t="s">
         <v>105</v>
       </c>
-      <c r="B9" s="65">
+      <c r="B9" s="64">
         <v>-5.491987</v>
       </c>
-      <c r="C9" s="65">
+      <c r="C9" s="64">
         <v>119.312573</v>
       </c>
-      <c r="D9" s="66"/>
+      <c r="D9" s="65"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="64" t="s">
+      <c r="A10" s="63" t="s">
         <v>106</v>
       </c>
-      <c r="B10" s="65">
+      <c r="B10" s="64">
         <v>-5.49282</v>
       </c>
-      <c r="C10" s="65">
+      <c r="C10" s="64">
         <v>119.31198000000001</v>
       </c>
-      <c r="D10" s="66"/>
+      <c r="D10" s="65"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" s="64" t="s">
+      <c r="A11" s="63" t="s">
         <v>107</v>
       </c>
-      <c r="B11" s="65">
+      <c r="B11" s="64">
         <v>-5.4639509999999998</v>
       </c>
-      <c r="C11" s="65">
+      <c r="C11" s="64">
         <v>119.287291</v>
       </c>
-      <c r="D11" s="66"/>
+      <c r="D11" s="65"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="64" t="s">
+      <c r="A12" s="63" t="s">
         <v>94</v>
       </c>
-      <c r="B12" s="65">
+      <c r="B12" s="64">
         <v>-5.4620889999999997</v>
       </c>
-      <c r="C12" s="65">
+      <c r="C12" s="64">
         <v>119.286874</v>
       </c>
-      <c r="D12" s="66"/>
+      <c r="D12" s="65"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" s="64" t="s">
+      <c r="A13" s="63" t="s">
         <v>108</v>
       </c>
-      <c r="B13" s="65">
+      <c r="B13" s="64">
         <v>-5.463902</v>
       </c>
-      <c r="C13" s="65">
+      <c r="C13" s="64">
         <v>119.28802</v>
       </c>
-      <c r="D13" s="66"/>
+      <c r="D13" s="65"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" s="64" t="s">
+      <c r="A14" s="63" t="s">
         <v>109</v>
       </c>
-      <c r="B14" s="65">
+      <c r="B14" s="64">
         <v>-5.4810160000000003</v>
       </c>
-      <c r="C14" s="65">
+      <c r="C14" s="64">
         <v>119.31128099999999</v>
       </c>
-      <c r="D14" s="66"/>
+      <c r="D14" s="65"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" s="64" t="s">
+      <c r="A15" s="63" t="s">
         <v>110</v>
       </c>
-      <c r="B15" s="65">
+      <c r="B15" s="64">
         <v>-5.4811319999999997</v>
       </c>
-      <c r="C15" s="65">
+      <c r="C15" s="64">
         <v>119.31211</v>
       </c>
-      <c r="D15" s="66"/>
+      <c r="D15" s="65"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" s="64" t="s">
+      <c r="A16" s="63" t="s">
         <v>111</v>
       </c>
-      <c r="B16" s="65">
+      <c r="B16" s="64">
         <v>-5.4793599999999998</v>
       </c>
-      <c r="C16" s="65">
+      <c r="C16" s="64">
         <v>119.312033</v>
       </c>
-      <c r="D16" s="66"/>
+      <c r="D16" s="65"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" s="64" t="s">
+      <c r="A17" s="63" t="s">
         <v>112</v>
       </c>
-      <c r="B17" s="65">
+      <c r="B17" s="64">
         <v>-5.4663769999999996</v>
       </c>
-      <c r="C17" s="65">
+      <c r="C17" s="64">
         <v>119.30229</v>
       </c>
-      <c r="D17" s="66"/>
+      <c r="D17" s="65"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" s="64" t="s">
+      <c r="A18" s="63" t="s">
         <v>113</v>
       </c>
-      <c r="B18" s="65">
+      <c r="B18" s="64">
         <v>-5.4682510000000004</v>
       </c>
-      <c r="C18" s="65">
+      <c r="C18" s="64">
         <v>119.301957</v>
       </c>
-      <c r="D18" s="66"/>
+      <c r="D18" s="65"/>
     </row>
     <row r="19" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="67" t="s">
+      <c r="A19" s="66" t="s">
         <v>97</v>
       </c>
-      <c r="B19" s="68">
+      <c r="B19" s="67">
         <v>-5.4686510000000004</v>
       </c>
-      <c r="C19" s="68">
+      <c r="C19" s="67">
         <v>119.300428</v>
       </c>
-      <c r="D19" s="69"/>
+      <c r="D19" s="68"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/URUVS/Datasheets/URUV/04.2024/April_RecordingData.xlsx
+++ b/URUVS/Datasheets/URUV/04.2024/April_RecordingData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\swulfing\Documents\GitHub\TanakekeProject\URUVS\Datasheets\URUV\04.2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AFD1C74-50CF-4846-A3E0-26E533A9FB95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D71F8297-70A8-412A-804D-281A7AAE8AF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-3840" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="43095" yWindow="-9285" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RecordingData_04.2024" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="230">
   <si>
     <t>DATE</t>
   </si>
@@ -720,6 +720,15 @@
   </si>
   <si>
     <t>T1_SHRIMP</t>
+  </si>
+  <si>
+    <t>MAXN_FISHO</t>
+  </si>
+  <si>
+    <t>TIME_1STFISHO</t>
+  </si>
+  <si>
+    <t>T1_FISHO</t>
   </si>
 </sst>
 </file>
@@ -1423,7 +1432,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAF2D75B-3330-44BB-BF8B-27BF0F133624}">
-  <dimension ref="A1:DU22"/>
+  <dimension ref="A1:DX22"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="10.453125" bestFit="1" customWidth="1"/>
@@ -1442,19 +1451,19 @@
     <col min="61" max="61" width="8.90625" bestFit="1" customWidth="1"/>
     <col min="62" max="62" width="12" bestFit="1" customWidth="1"/>
     <col min="85" max="85" width="9.36328125" bestFit="1" customWidth="1"/>
-    <col min="91" max="91" width="18.36328125" bestFit="1" customWidth="1"/>
-    <col min="96" max="96" width="8.7265625" style="85"/>
-    <col min="106" max="106" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="94" max="94" width="18.36328125" bestFit="1" customWidth="1"/>
+    <col min="99" max="99" width="8.7265625" style="85"/>
     <col min="109" max="109" width="11.1796875" bestFit="1" customWidth="1"/>
     <col min="112" max="112" width="11.1796875" bestFit="1" customWidth="1"/>
     <col min="115" max="115" width="11.1796875" bestFit="1" customWidth="1"/>
     <col min="118" max="118" width="11.1796875" bestFit="1" customWidth="1"/>
     <col min="121" max="121" width="11.1796875" bestFit="1" customWidth="1"/>
     <col min="124" max="124" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="125" max="125" width="13.90625" bestFit="1" customWidth="1"/>
+    <col min="127" max="127" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="128" max="128" width="13.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:125" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:128" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="93" t="s">
         <v>212</v>
       </c>
@@ -1720,118 +1729,127 @@
         <v>140</v>
       </c>
       <c r="CK1" s="81" t="s">
+        <v>227</v>
+      </c>
+      <c r="CL1" s="27" t="s">
+        <v>228</v>
+      </c>
+      <c r="CM1" s="59" t="s">
+        <v>229</v>
+      </c>
+      <c r="CN1" s="81" t="s">
         <v>123</v>
       </c>
-      <c r="CL1" s="27" t="s">
+      <c r="CO1" s="27" t="s">
         <v>124</v>
       </c>
-      <c r="CM1" s="59" t="s">
+      <c r="CP1" s="59" t="s">
         <v>125</v>
       </c>
-      <c r="CN1" s="81" t="s">
+      <c r="CQ1" s="81" t="s">
         <v>208</v>
       </c>
-      <c r="CO1" s="27" t="s">
+      <c r="CR1" s="27" t="s">
         <v>209</v>
       </c>
-      <c r="CP1" s="59" t="s">
+      <c r="CS1" s="59" t="s">
         <v>210</v>
       </c>
-      <c r="CQ1" s="81" t="s">
+      <c r="CT1" s="81" t="s">
         <v>201</v>
       </c>
-      <c r="CR1" s="90" t="s">
+      <c r="CU1" s="90" t="s">
         <v>202</v>
       </c>
-      <c r="CS1" s="59" t="s">
+      <c r="CV1" s="59" t="s">
         <v>203</v>
       </c>
-      <c r="CT1" s="81" t="s">
+      <c r="CW1" s="81" t="s">
         <v>132</v>
       </c>
-      <c r="CU1" s="27" t="s">
+      <c r="CX1" s="27" t="s">
         <v>133</v>
       </c>
-      <c r="CV1" s="59" t="s">
+      <c r="CY1" s="59" t="s">
         <v>134</v>
       </c>
-      <c r="CW1" s="81" t="s">
+      <c r="CZ1" s="81" t="s">
         <v>135</v>
       </c>
-      <c r="CX1" s="27" t="s">
+      <c r="DA1" s="27" t="s">
         <v>136</v>
       </c>
-      <c r="CY1" s="59" t="s">
+      <c r="DB1" s="59" t="s">
         <v>137</v>
       </c>
-      <c r="CZ1" s="81" t="s">
+      <c r="DC1" s="81" t="s">
         <v>141</v>
       </c>
-      <c r="DA1" s="27" t="s">
+      <c r="DD1" s="27" t="s">
         <v>142</v>
       </c>
-      <c r="DB1" s="59" t="s">
+      <c r="DE1" s="59" t="s">
         <v>143</v>
       </c>
-      <c r="DC1" s="81" t="s">
+      <c r="DF1" s="81" t="s">
         <v>200</v>
       </c>
-      <c r="DD1" s="27" t="s">
+      <c r="DG1" s="27" t="s">
         <v>198</v>
       </c>
-      <c r="DE1" s="59" t="s">
+      <c r="DH1" s="59" t="s">
         <v>199</v>
       </c>
-      <c r="DF1" s="81" t="s">
+      <c r="DI1" s="81" t="s">
         <v>12</v>
       </c>
-      <c r="DG1" s="27" t="s">
+      <c r="DJ1" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="DH1" s="59" t="s">
+      <c r="DK1" s="59" t="s">
         <v>33</v>
       </c>
-      <c r="DI1" s="81" t="s">
+      <c r="DL1" s="81" t="s">
         <v>215</v>
       </c>
-      <c r="DJ1" s="27" t="s">
+      <c r="DM1" s="27" t="s">
         <v>216</v>
       </c>
-      <c r="DK1" s="59" t="s">
+      <c r="DN1" s="59" t="s">
         <v>217</v>
       </c>
-      <c r="DL1" s="81" t="s">
+      <c r="DO1" s="81" t="s">
         <v>218</v>
       </c>
-      <c r="DM1" s="27" t="s">
+      <c r="DP1" s="27" t="s">
         <v>219</v>
       </c>
-      <c r="DN1" s="59" t="s">
+      <c r="DQ1" s="59" t="s">
         <v>220</v>
       </c>
-      <c r="DO1" s="81" t="s">
+      <c r="DR1" s="81" t="s">
         <v>224</v>
       </c>
-      <c r="DP1" s="27" t="s">
+      <c r="DS1" s="27" t="s">
         <v>225</v>
       </c>
-      <c r="DQ1" s="59" t="s">
+      <c r="DT1" s="59" t="s">
         <v>226</v>
       </c>
-      <c r="DR1" s="81" t="s">
+      <c r="DU1" s="81" t="s">
         <v>221</v>
       </c>
-      <c r="DS1" s="27" t="s">
+      <c r="DV1" s="27" t="s">
         <v>222</v>
       </c>
-      <c r="DT1" s="59" t="s">
+      <c r="DW1" s="59" t="s">
         <v>223</v>
       </c>
-      <c r="DU1" s="28" t="s">
+      <c r="DX1" s="28" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:125" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:128" x14ac:dyDescent="0.35">
       <c r="A2" s="88" t="s">
         <v>213</v>
       </c>
@@ -2093,51 +2111,57 @@
         <f t="shared" ref="DE2:DE22" si="24">IF(DC2=0,"NA",DD2-$AD2)</f>
         <v>NA</v>
       </c>
-      <c r="DF2" s="58">
+      <c r="DF2" s="58"/>
+      <c r="DG2" s="71"/>
+      <c r="DH2" s="33" t="str">
+        <f t="shared" ref="DH2:DH22" si="25">IF(DF2=0,"NA",DG2-$AD2)</f>
+        <v>NA</v>
+      </c>
+      <c r="DI2" s="58">
         <v>3</v>
       </c>
-      <c r="DG2" s="71">
+      <c r="DJ2" s="71">
         <v>3.8541666666666668E-3</v>
-      </c>
-      <c r="DH2" s="33">
-        <f t="shared" ref="DH2:DH22" si="25">IF(DF2=0,"NA",DG2-$AD2)</f>
-        <v>5.7870370370370454E-5</v>
-      </c>
-      <c r="DI2" s="58">
-        <v>1</v>
-      </c>
-      <c r="DJ2" s="71">
-        <v>1.8194444444444444E-2</v>
       </c>
       <c r="DK2" s="33">
         <f t="shared" ref="DK2:DK22" si="26">IF(DI2=0,"NA",DJ2-$AD2)</f>
-        <v>1.4398148148148148E-2</v>
+        <v>5.7870370370370454E-5</v>
       </c>
       <c r="DL2" s="58">
         <v>1</v>
       </c>
       <c r="DM2" s="71">
-        <v>6.851851851851852E-3</v>
+        <v>1.8194444444444444E-2</v>
       </c>
       <c r="DN2" s="33">
         <f t="shared" ref="DN2:DN22" si="27">IF(DL2=0,"NA",DM2-$AD2)</f>
+        <v>1.4398148148148148E-2</v>
+      </c>
+      <c r="DO2" s="58">
+        <v>1</v>
+      </c>
+      <c r="DP2" s="71">
+        <v>6.851851851851852E-3</v>
+      </c>
+      <c r="DQ2" s="33">
+        <f t="shared" ref="DQ2:DQ22" si="28">IF(DO2=0,"NA",DP2-$AD2)</f>
         <v>3.0555555555555557E-3</v>
-      </c>
-      <c r="DO2" s="58"/>
-      <c r="DP2" s="71"/>
-      <c r="DQ2" s="33" t="str">
-        <f t="shared" ref="DQ2:DQ22" si="28">IF(DO2=0,"NA",DP2-$AD2)</f>
-        <v>NA</v>
       </c>
       <c r="DR2" s="58"/>
       <c r="DS2" s="71"/>
       <c r="DT2" s="33" t="str">
-        <f t="shared" ref="DT2:DT13" si="29">IF(DR2=0,"NA",DS2-$AD2)</f>
-        <v>NA</v>
-      </c>
-      <c r="DU2" s="35"/>
+        <f t="shared" ref="DT2:DT22" si="29">IF(DR2=0,"NA",DS2-$AD2)</f>
+        <v>NA</v>
+      </c>
+      <c r="DU2" s="58"/>
+      <c r="DV2" s="71"/>
+      <c r="DW2" s="33" t="str">
+        <f t="shared" ref="DW2:DW13" si="30">IF(DU2=0,"NA",DV2-$AD2)</f>
+        <v>NA</v>
+      </c>
+      <c r="DX2" s="35"/>
     </row>
-    <row r="3" spans="1:125" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:128" x14ac:dyDescent="0.35">
       <c r="A3" s="88" t="s">
         <v>213</v>
       </c>
@@ -2154,7 +2178,7 @@
         <v>6</v>
       </c>
       <c r="F3" s="74" t="str">
-        <f t="shared" ref="F3:F22" si="30">D3&amp;""&amp;E3</f>
+        <f t="shared" ref="F3:F22" si="31">D3&amp;""&amp;E3</f>
         <v>L6</v>
       </c>
       <c r="G3" s="5">
@@ -2190,7 +2214,7 @@
         <v>4</v>
       </c>
       <c r="Q3" s="6">
-        <f t="shared" ref="Q3:Q22" si="31">J3-I3</f>
+        <f t="shared" ref="Q3:Q22" si="32">J3-I3</f>
         <v>9.5833333333333326E-2</v>
       </c>
       <c r="R3" s="6" t="s">
@@ -2219,7 +2243,7 @@
       <c r="AA3" s="20"/>
       <c r="AB3" s="20"/>
       <c r="AC3" s="20">
-        <f t="shared" ref="AC3:AC22" si="32">SUM(W3:AB3)</f>
+        <f t="shared" ref="AC3:AC22" si="33">SUM(W3:AB3)</f>
         <v>6.008101851851852E-2</v>
       </c>
       <c r="AD3" s="20">
@@ -2368,13 +2392,13 @@
         <v>NA</v>
       </c>
       <c r="CQ3" s="31"/>
-      <c r="CR3" s="34"/>
+      <c r="CR3" s="32"/>
       <c r="CS3" s="33" t="str">
         <f t="shared" si="20"/>
         <v>NA</v>
       </c>
       <c r="CT3" s="31"/>
-      <c r="CU3" s="32"/>
+      <c r="CU3" s="34"/>
       <c r="CV3" s="33" t="str">
         <f t="shared" si="21"/>
         <v>NA</v>
@@ -2391,31 +2415,31 @@
         <f t="shared" si="23"/>
         <v>NA</v>
       </c>
-      <c r="DC3" s="31">
+      <c r="DC3" s="31"/>
+      <c r="DD3" s="32"/>
+      <c r="DE3" s="33" t="str">
+        <f t="shared" si="24"/>
+        <v>NA</v>
+      </c>
+      <c r="DF3" s="31">
         <v>2</v>
       </c>
-      <c r="DD3" s="34">
+      <c r="DG3" s="34">
         <v>4.1666666666666666E-3</v>
-      </c>
-      <c r="DE3" s="33">
-        <f t="shared" si="24"/>
-        <v>1.6203703703703692E-4</v>
-      </c>
-      <c r="DF3" s="31">
-        <v>4</v>
-      </c>
-      <c r="DG3" s="34">
-        <v>4.409722222222222E-3</v>
       </c>
       <c r="DH3" s="33">
         <f t="shared" si="25"/>
+        <v>1.6203703703703692E-4</v>
+      </c>
+      <c r="DI3" s="31">
+        <v>4</v>
+      </c>
+      <c r="DJ3" s="34">
+        <v>4.409722222222222E-3</v>
+      </c>
+      <c r="DK3" s="33">
+        <f t="shared" si="26"/>
         <v>4.0509259259259231E-4</v>
-      </c>
-      <c r="DI3" s="31"/>
-      <c r="DJ3" s="34"/>
-      <c r="DK3" s="33" t="str">
-        <f t="shared" si="26"/>
-        <v>NA</v>
       </c>
       <c r="DL3" s="31"/>
       <c r="DM3" s="34"/>
@@ -2429,19 +2453,25 @@
         <f t="shared" si="28"/>
         <v>NA</v>
       </c>
-      <c r="DR3" s="31">
+      <c r="DR3" s="31"/>
+      <c r="DS3" s="34"/>
+      <c r="DT3" s="33" t="str">
+        <f t="shared" si="29"/>
+        <v>NA</v>
+      </c>
+      <c r="DU3" s="31">
         <v>1</v>
       </c>
-      <c r="DS3" s="34">
+      <c r="DV3" s="34">
         <v>1.4409722222222223E-2</v>
       </c>
-      <c r="DT3" s="33">
-        <f t="shared" si="29"/>
+      <c r="DW3" s="33">
+        <f t="shared" si="30"/>
         <v>1.0405092592592594E-2</v>
       </c>
-      <c r="DU3" s="35"/>
+      <c r="DX3" s="35"/>
     </row>
-    <row r="4" spans="1:125" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:128" x14ac:dyDescent="0.35">
       <c r="A4" s="88" t="s">
         <v>213</v>
       </c>
@@ -2458,7 +2488,7 @@
         <v>5</v>
       </c>
       <c r="F4" s="74" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>L5</v>
       </c>
       <c r="G4" s="5">
@@ -2494,7 +2524,7 @@
         <v>3</v>
       </c>
       <c r="Q4" s="6">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>7.9166666666666718E-2</v>
       </c>
       <c r="R4" s="6" t="s">
@@ -2519,7 +2549,7 @@
       <c r="AA4" s="20"/>
       <c r="AB4" s="20"/>
       <c r="AC4" s="20">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AD4" s="20"/>
@@ -2707,9 +2737,15 @@
         <f t="shared" si="29"/>
         <v>NA</v>
       </c>
-      <c r="DU4" s="35"/>
+      <c r="DU4" s="31"/>
+      <c r="DV4" s="34"/>
+      <c r="DW4" s="33" t="str">
+        <f t="shared" si="30"/>
+        <v>NA</v>
+      </c>
+      <c r="DX4" s="35"/>
     </row>
-    <row r="5" spans="1:125" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:128" x14ac:dyDescent="0.35">
       <c r="A5" s="88" t="s">
         <v>213</v>
       </c>
@@ -2726,7 +2762,7 @@
         <v>5</v>
       </c>
       <c r="F5" s="74" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>D5</v>
       </c>
       <c r="G5" s="5">
@@ -2762,7 +2798,7 @@
         <v>4</v>
       </c>
       <c r="Q5" s="6">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>8.333333333333337E-2</v>
       </c>
       <c r="R5" s="6" t="s">
@@ -2787,7 +2823,7 @@
       <c r="AA5" s="20"/>
       <c r="AB5" s="20"/>
       <c r="AC5" s="20">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AD5" s="20"/>
@@ -2916,13 +2952,13 @@
         <v>NA</v>
       </c>
       <c r="CQ5" s="31"/>
-      <c r="CR5" s="34"/>
+      <c r="CR5" s="32"/>
       <c r="CS5" s="33" t="str">
         <f t="shared" si="20"/>
         <v>NA</v>
       </c>
       <c r="CT5" s="31"/>
-      <c r="CU5" s="32"/>
+      <c r="CU5" s="34"/>
       <c r="CV5" s="33" t="str">
         <f t="shared" si="21"/>
         <v>NA</v>
@@ -2975,9 +3011,15 @@
         <f t="shared" si="29"/>
         <v>NA</v>
       </c>
-      <c r="DU5" s="35"/>
+      <c r="DU5" s="31"/>
+      <c r="DV5" s="32"/>
+      <c r="DW5" s="33" t="str">
+        <f t="shared" si="30"/>
+        <v>NA</v>
+      </c>
+      <c r="DX5" s="35"/>
     </row>
-    <row r="6" spans="1:125" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:128" x14ac:dyDescent="0.35">
       <c r="A6" s="88" t="s">
         <v>213</v>
       </c>
@@ -2994,7 +3036,7 @@
         <v>4</v>
       </c>
       <c r="F6" s="74" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>L4</v>
       </c>
       <c r="G6" s="5">
@@ -3030,7 +3072,7 @@
         <v>2</v>
       </c>
       <c r="Q6" s="6">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>6.1805555555555558E-2</v>
       </c>
       <c r="R6" s="6" t="s">
@@ -3057,7 +3099,7 @@
       <c r="AA6" s="20"/>
       <c r="AB6" s="20"/>
       <c r="AC6" s="20">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>4.2187500000000003E-2</v>
       </c>
       <c r="AD6" s="20">
@@ -3200,13 +3242,13 @@
         <v>NA</v>
       </c>
       <c r="CQ6" s="31"/>
-      <c r="CR6" s="34"/>
+      <c r="CR6" s="32"/>
       <c r="CS6" s="33" t="str">
         <f t="shared" si="20"/>
         <v>NA</v>
       </c>
       <c r="CT6" s="31"/>
-      <c r="CU6" s="32"/>
+      <c r="CU6" s="34"/>
       <c r="CV6" s="33" t="str">
         <f t="shared" si="21"/>
         <v>NA</v>
@@ -3229,41 +3271,41 @@
         <f t="shared" si="24"/>
         <v>NA</v>
       </c>
-      <c r="DF6" s="31">
+      <c r="DF6" s="31"/>
+      <c r="DG6" s="32"/>
+      <c r="DH6" s="33" t="str">
+        <f t="shared" si="25"/>
+        <v>NA</v>
+      </c>
+      <c r="DI6" s="31">
         <v>3</v>
       </c>
-      <c r="DG6" s="34">
+      <c r="DJ6" s="34">
         <v>6.4236111111111117E-3</v>
-      </c>
-      <c r="DH6" s="33">
-        <f t="shared" si="25"/>
-        <v>1.7361111111111223E-4</v>
-      </c>
-      <c r="DI6" s="31">
-        <v>2</v>
-      </c>
-      <c r="DJ6" s="34">
-        <v>6.5856481481481478E-3</v>
       </c>
       <c r="DK6" s="33">
         <f t="shared" si="26"/>
-        <v>3.3564814814814829E-4</v>
+        <v>1.7361111111111223E-4</v>
       </c>
       <c r="DL6" s="31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DM6" s="34">
-        <v>2.5798611111111112E-2</v>
+        <v>6.5856481481481478E-3</v>
       </c>
       <c r="DN6" s="33">
         <f t="shared" si="27"/>
+        <v>3.3564814814814829E-4</v>
+      </c>
+      <c r="DO6" s="31">
+        <v>1</v>
+      </c>
+      <c r="DP6" s="34">
+        <v>2.5798611111111112E-2</v>
+      </c>
+      <c r="DQ6" s="33">
+        <f t="shared" si="28"/>
         <v>1.9548611111111114E-2</v>
-      </c>
-      <c r="DO6" s="31"/>
-      <c r="DP6" s="34"/>
-      <c r="DQ6" s="33" t="str">
-        <f t="shared" si="28"/>
-        <v>NA</v>
       </c>
       <c r="DR6" s="31"/>
       <c r="DS6" s="34"/>
@@ -3271,9 +3313,15 @@
         <f t="shared" si="29"/>
         <v>NA</v>
       </c>
-      <c r="DU6" s="35"/>
+      <c r="DU6" s="31"/>
+      <c r="DV6" s="34"/>
+      <c r="DW6" s="33" t="str">
+        <f t="shared" si="30"/>
+        <v>NA</v>
+      </c>
+      <c r="DX6" s="35"/>
     </row>
-    <row r="7" spans="1:125" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:128" x14ac:dyDescent="0.35">
       <c r="A7" s="88" t="s">
         <v>213</v>
       </c>
@@ -3290,7 +3338,7 @@
         <v>6</v>
       </c>
       <c r="F7" s="74" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>D6</v>
       </c>
       <c r="G7" s="5">
@@ -3326,7 +3374,7 @@
         <v>3</v>
       </c>
       <c r="Q7" s="6">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>5.6250000000000022E-2</v>
       </c>
       <c r="R7" s="6" t="s">
@@ -3355,7 +3403,7 @@
       <c r="AA7" s="20"/>
       <c r="AB7" s="20"/>
       <c r="AC7" s="20">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>4.0115740740740743E-2</v>
       </c>
       <c r="AD7" s="20">
@@ -3494,13 +3542,13 @@
         <v>NA</v>
       </c>
       <c r="CQ7" s="31"/>
-      <c r="CR7" s="34"/>
+      <c r="CR7" s="32"/>
       <c r="CS7" s="33" t="str">
         <f t="shared" si="20"/>
         <v>NA</v>
       </c>
       <c r="CT7" s="31"/>
-      <c r="CU7" s="32"/>
+      <c r="CU7" s="34"/>
       <c r="CV7" s="33" t="str">
         <f t="shared" si="21"/>
         <v>NA</v>
@@ -3517,61 +3565,67 @@
         <f t="shared" si="23"/>
         <v>NA</v>
       </c>
-      <c r="DC7" s="31">
+      <c r="DC7" s="31"/>
+      <c r="DD7" s="32"/>
+      <c r="DE7" s="33" t="str">
+        <f t="shared" si="24"/>
+        <v>NA</v>
+      </c>
+      <c r="DF7" s="31">
         <v>1</v>
       </c>
-      <c r="DD7" s="34">
+      <c r="DG7" s="34">
         <v>1.0567129629629629E-2</v>
-      </c>
-      <c r="DE7" s="33">
-        <f t="shared" si="24"/>
-        <v>6.5393518518518517E-3</v>
-      </c>
-      <c r="DF7" s="31">
-        <v>4</v>
-      </c>
-      <c r="DG7" s="34">
-        <v>5.9143518518518521E-3</v>
       </c>
       <c r="DH7" s="33">
         <f t="shared" si="25"/>
-        <v>1.8865740740740744E-3</v>
+        <v>6.5393518518518517E-3</v>
       </c>
       <c r="DI7" s="31">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="DJ7" s="34">
-        <v>1.0138888888888888E-2</v>
+        <v>5.9143518518518521E-3</v>
       </c>
       <c r="DK7" s="33">
         <f t="shared" si="26"/>
+        <v>1.8865740740740744E-3</v>
+      </c>
+      <c r="DL7" s="31">
+        <v>1</v>
+      </c>
+      <c r="DM7" s="34">
+        <v>1.0138888888888888E-2</v>
+      </c>
+      <c r="DN7" s="33">
+        <f t="shared" si="27"/>
         <v>6.1111111111111106E-3</v>
       </c>
-      <c r="DL7" s="31"/>
-      <c r="DM7" s="34"/>
-      <c r="DN7" s="33" t="str">
-        <f t="shared" si="27"/>
-        <v>NA</v>
-      </c>
-      <c r="DO7" s="31">
+      <c r="DO7" s="31"/>
+      <c r="DP7" s="34"/>
+      <c r="DQ7" s="33" t="str">
+        <f t="shared" si="28"/>
+        <v>NA</v>
+      </c>
+      <c r="DR7" s="31">
         <v>1</v>
       </c>
-      <c r="DP7" s="34">
+      <c r="DS7" s="34">
         <v>1.7407407407407406E-2</v>
       </c>
-      <c r="DQ7" s="33">
-        <f t="shared" si="28"/>
+      <c r="DT7" s="33">
+        <f t="shared" si="29"/>
         <v>1.3379629629629628E-2</v>
       </c>
-      <c r="DR7" s="31"/>
-      <c r="DS7" s="34"/>
-      <c r="DT7" s="33" t="str">
-        <f t="shared" si="29"/>
-        <v>NA</v>
-      </c>
-      <c r="DU7" s="35"/>
+      <c r="DU7" s="31"/>
+      <c r="DV7" s="34"/>
+      <c r="DW7" s="33" t="str">
+        <f t="shared" si="30"/>
+        <v>NA</v>
+      </c>
+      <c r="DX7" s="35"/>
     </row>
-    <row r="8" spans="1:125" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:128" x14ac:dyDescent="0.35">
       <c r="A8" s="88" t="s">
         <v>213</v>
       </c>
@@ -3588,7 +3642,7 @@
         <v>5</v>
       </c>
       <c r="F8" s="74" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>D5</v>
       </c>
       <c r="G8" s="5">
@@ -3624,7 +3678,7 @@
         <v>3</v>
       </c>
       <c r="Q8" s="6">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0.27013888888888887</v>
       </c>
       <c r="R8" s="6" t="s">
@@ -3655,7 +3709,7 @@
       <c r="AA8" s="20"/>
       <c r="AB8" s="20"/>
       <c r="AC8" s="20">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>4.4374999999999998E-2</v>
       </c>
       <c r="AD8" s="20">
@@ -3798,13 +3852,13 @@
         <v>NA</v>
       </c>
       <c r="CQ8" s="31"/>
-      <c r="CR8" s="34"/>
+      <c r="CR8" s="32"/>
       <c r="CS8" s="33" t="str">
         <f t="shared" si="20"/>
         <v>NA</v>
       </c>
       <c r="CT8" s="31"/>
-      <c r="CU8" s="32"/>
+      <c r="CU8" s="34"/>
       <c r="CV8" s="33" t="str">
         <f t="shared" si="21"/>
         <v>NA</v>
@@ -3816,52 +3870,52 @@
         <v>NA</v>
       </c>
       <c r="CZ8" s="31"/>
-      <c r="DA8" s="70"/>
+      <c r="DA8" s="32"/>
       <c r="DB8" s="33" t="str">
         <f t="shared" si="23"/>
         <v>NA</v>
       </c>
-      <c r="DC8" s="31">
+      <c r="DC8" s="31"/>
+      <c r="DD8" s="70"/>
+      <c r="DE8" s="33" t="str">
+        <f t="shared" si="24"/>
+        <v>NA</v>
+      </c>
+      <c r="DF8" s="31">
         <v>2</v>
       </c>
-      <c r="DD8" s="70">
+      <c r="DG8" s="70">
         <v>4.0856481481481481E-3</v>
-      </c>
-      <c r="DE8" s="33">
-        <f t="shared" si="24"/>
-        <v>1.7361111111111136E-4</v>
-      </c>
-      <c r="DF8" s="31">
-        <v>1</v>
-      </c>
-      <c r="DG8" s="70">
-        <v>2.6041666666666668E-2</v>
       </c>
       <c r="DH8" s="33">
         <f t="shared" si="25"/>
+        <v>1.7361111111111136E-4</v>
+      </c>
+      <c r="DI8" s="31">
+        <v>1</v>
+      </c>
+      <c r="DJ8" s="70">
+        <v>2.6041666666666668E-2</v>
+      </c>
+      <c r="DK8" s="33">
+        <f t="shared" si="26"/>
         <v>2.2129629629629631E-2</v>
       </c>
-      <c r="DI8" s="31"/>
-      <c r="DJ8" s="70"/>
-      <c r="DK8" s="33" t="str">
-        <f t="shared" si="26"/>
-        <v>NA</v>
-      </c>
-      <c r="DL8" s="31">
+      <c r="DL8" s="31"/>
+      <c r="DM8" s="70"/>
+      <c r="DN8" s="33" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DO8" s="31">
         <v>1</v>
       </c>
-      <c r="DM8" s="70">
+      <c r="DP8" s="70">
         <v>6.9791666666666665E-3</v>
       </c>
-      <c r="DN8" s="33">
-        <f t="shared" si="27"/>
+      <c r="DQ8" s="33">
+        <f t="shared" si="28"/>
         <v>3.0671296296296297E-3</v>
-      </c>
-      <c r="DO8" s="31"/>
-      <c r="DP8" s="70"/>
-      <c r="DQ8" s="33" t="str">
-        <f t="shared" si="28"/>
-        <v>NA</v>
       </c>
       <c r="DR8" s="31"/>
       <c r="DS8" s="70"/>
@@ -3869,9 +3923,15 @@
         <f t="shared" si="29"/>
         <v>NA</v>
       </c>
-      <c r="DU8" s="35"/>
+      <c r="DU8" s="31"/>
+      <c r="DV8" s="70"/>
+      <c r="DW8" s="33" t="str">
+        <f t="shared" si="30"/>
+        <v>NA</v>
+      </c>
+      <c r="DX8" s="35"/>
     </row>
-    <row r="9" spans="1:125" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:128" x14ac:dyDescent="0.35">
       <c r="A9" s="88" t="s">
         <v>213</v>
       </c>
@@ -3888,7 +3948,7 @@
         <v>5</v>
       </c>
       <c r="F9" s="74" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>L5</v>
       </c>
       <c r="G9" s="5">
@@ -3924,7 +3984,7 @@
         <v>3</v>
       </c>
       <c r="Q9" s="6">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0.26944444444444443</v>
       </c>
       <c r="R9" s="6" t="s">
@@ -3955,7 +4015,7 @@
       <c r="AA9" s="20"/>
       <c r="AB9" s="20"/>
       <c r="AC9" s="20">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>6.0324074074074072E-2</v>
       </c>
       <c r="AD9" s="20">
@@ -4100,13 +4160,13 @@
         <v>NA</v>
       </c>
       <c r="CQ9" s="31"/>
-      <c r="CR9" s="34"/>
+      <c r="CR9" s="32"/>
       <c r="CS9" s="33" t="str">
         <f t="shared" si="20"/>
         <v>NA</v>
       </c>
       <c r="CT9" s="31"/>
-      <c r="CU9" s="32"/>
+      <c r="CU9" s="34"/>
       <c r="CV9" s="33" t="str">
         <f t="shared" si="21"/>
         <v>NA</v>
@@ -4118,70 +4178,76 @@
         <v>NA</v>
       </c>
       <c r="CZ9" s="31"/>
-      <c r="DA9" s="56"/>
+      <c r="DA9" s="32"/>
       <c r="DB9" s="33" t="str">
         <f t="shared" si="23"/>
         <v>NA</v>
       </c>
-      <c r="DC9" s="31">
+      <c r="DC9" s="31"/>
+      <c r="DD9" s="56"/>
+      <c r="DE9" s="33" t="str">
+        <f t="shared" si="24"/>
+        <v>NA</v>
+      </c>
+      <c r="DF9" s="31">
         <v>2</v>
       </c>
-      <c r="DD9" s="56">
+      <c r="DG9" s="56">
         <v>5.5092592592592589E-3</v>
-      </c>
-      <c r="DE9" s="33">
-        <f t="shared" si="24"/>
-        <v>8.7962962962962864E-4</v>
-      </c>
-      <c r="DF9" s="31">
-        <v>3</v>
-      </c>
-      <c r="DG9" s="56">
-        <v>1.7141203703703704E-2</v>
       </c>
       <c r="DH9" s="33">
         <f t="shared" si="25"/>
-        <v>1.2511574074074074E-2</v>
+        <v>8.7962962962962864E-4</v>
       </c>
       <c r="DI9" s="31">
         <v>3</v>
       </c>
       <c r="DJ9" s="56">
-        <v>4.6296296296296294E-3</v>
+        <v>1.7141203703703704E-2</v>
       </c>
       <c r="DK9" s="33">
         <f t="shared" si="26"/>
-        <v>-8.6736173798840355E-19</v>
+        <v>1.2511574074074074E-2</v>
       </c>
       <c r="DL9" s="31">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="DM9" s="56">
-        <v>1.9652777777777779E-2</v>
+        <v>4.6296296296296294E-3</v>
       </c>
       <c r="DN9" s="33">
         <f t="shared" si="27"/>
-        <v>1.502314814814815E-2</v>
+        <v>-8.6736173798840355E-19</v>
       </c>
       <c r="DO9" s="31">
         <v>1</v>
       </c>
       <c r="DP9" s="56">
-        <v>2.4918981481481483E-2</v>
+        <v>1.9652777777777779E-2</v>
       </c>
       <c r="DQ9" s="33">
         <f t="shared" si="28"/>
+        <v>1.502314814814815E-2</v>
+      </c>
+      <c r="DR9" s="31">
+        <v>1</v>
+      </c>
+      <c r="DS9" s="56">
+        <v>2.4918981481481483E-2</v>
+      </c>
+      <c r="DT9" s="33">
+        <f t="shared" si="29"/>
         <v>2.0289351851851854E-2</v>
       </c>
-      <c r="DR9" s="31"/>
-      <c r="DS9" s="56"/>
-      <c r="DT9" s="33" t="str">
-        <f t="shared" si="29"/>
-        <v>NA</v>
-      </c>
-      <c r="DU9" s="35"/>
+      <c r="DU9" s="31"/>
+      <c r="DV9" s="56"/>
+      <c r="DW9" s="33" t="str">
+        <f t="shared" si="30"/>
+        <v>NA</v>
+      </c>
+      <c r="DX9" s="35"/>
     </row>
-    <row r="10" spans="1:125" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:128" x14ac:dyDescent="0.35">
       <c r="A10" s="88" t="s">
         <v>213</v>
       </c>
@@ -4198,7 +4264,7 @@
         <v>6</v>
       </c>
       <c r="F10" s="74" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>E6</v>
       </c>
       <c r="G10" s="5">
@@ -4234,7 +4300,7 @@
         <v>3</v>
       </c>
       <c r="Q10" s="6">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>7.5694444444444398E-2</v>
       </c>
       <c r="R10" s="6" t="s">
@@ -4259,7 +4325,7 @@
       <c r="AA10" s="20"/>
       <c r="AB10" s="20"/>
       <c r="AC10" s="20">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AD10" s="20"/>
@@ -4447,9 +4513,15 @@
         <f t="shared" si="29"/>
         <v>NA</v>
       </c>
-      <c r="DU10" s="35"/>
+      <c r="DU10" s="31"/>
+      <c r="DV10" s="34"/>
+      <c r="DW10" s="33" t="str">
+        <f t="shared" si="30"/>
+        <v>NA</v>
+      </c>
+      <c r="DX10" s="35"/>
     </row>
-    <row r="11" spans="1:125" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:128" x14ac:dyDescent="0.35">
       <c r="A11" s="88" t="s">
         <v>213</v>
       </c>
@@ -4466,7 +4538,7 @@
         <v>4</v>
       </c>
       <c r="F11" s="74" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>E4</v>
       </c>
       <c r="G11" s="5">
@@ -4502,7 +4574,7 @@
         <v>4</v>
       </c>
       <c r="Q11" s="6">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>6.8749999999999978E-2</v>
       </c>
       <c r="R11" s="6" t="s">
@@ -4533,7 +4605,7 @@
       <c r="AA11" s="20"/>
       <c r="AB11" s="20"/>
       <c r="AC11" s="20">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>5.7280092592592591E-2</v>
       </c>
       <c r="AD11" s="20">
@@ -4711,21 +4783,21 @@
         <f t="shared" si="22"/>
         <v>NA</v>
       </c>
-      <c r="CZ11" s="31">
+      <c r="CZ11" s="31"/>
+      <c r="DA11" s="34"/>
+      <c r="DB11" s="33" t="str">
+        <f t="shared" si="23"/>
+        <v>NA</v>
+      </c>
+      <c r="DC11" s="31">
         <v>1</v>
       </c>
-      <c r="DA11" s="34">
+      <c r="DD11" s="34">
         <v>4.1655092592592598E-2</v>
       </c>
-      <c r="DB11" s="33">
-        <f t="shared" si="23"/>
+      <c r="DE11" s="33">
+        <f t="shared" si="24"/>
         <v>3.7673611111111116E-2</v>
-      </c>
-      <c r="DC11" s="31"/>
-      <c r="DD11" s="34"/>
-      <c r="DE11" s="33" t="str">
-        <f t="shared" si="24"/>
-        <v>NA</v>
       </c>
       <c r="DF11" s="31"/>
       <c r="DG11" s="34"/>
@@ -4739,21 +4811,21 @@
         <f t="shared" si="26"/>
         <v>NA</v>
       </c>
-      <c r="DL11" s="31">
+      <c r="DL11" s="31"/>
+      <c r="DM11" s="34"/>
+      <c r="DN11" s="33" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DO11" s="31">
         <v>1</v>
       </c>
-      <c r="DM11" s="34">
+      <c r="DP11" s="34">
         <v>8.472222222222223E-3</v>
       </c>
-      <c r="DN11" s="33">
-        <f t="shared" si="27"/>
+      <c r="DQ11" s="33">
+        <f t="shared" si="28"/>
         <v>4.4907407407407413E-3</v>
-      </c>
-      <c r="DO11" s="31"/>
-      <c r="DP11" s="34"/>
-      <c r="DQ11" s="33" t="str">
-        <f t="shared" si="28"/>
-        <v>NA</v>
       </c>
       <c r="DR11" s="31"/>
       <c r="DS11" s="34"/>
@@ -4761,9 +4833,15 @@
         <f t="shared" si="29"/>
         <v>NA</v>
       </c>
-      <c r="DU11" s="35"/>
+      <c r="DU11" s="31"/>
+      <c r="DV11" s="34"/>
+      <c r="DW11" s="33" t="str">
+        <f t="shared" si="30"/>
+        <v>NA</v>
+      </c>
+      <c r="DX11" s="35"/>
     </row>
-    <row r="12" spans="1:125" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:128" x14ac:dyDescent="0.35">
       <c r="A12" s="88" t="s">
         <v>213</v>
       </c>
@@ -4780,7 +4858,7 @@
         <v>5</v>
       </c>
       <c r="F12" s="74" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>E5</v>
       </c>
       <c r="G12" s="5">
@@ -4816,7 +4894,7 @@
         <v>3</v>
       </c>
       <c r="Q12" s="6">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>4.8611111111111105E-2</v>
       </c>
       <c r="R12" s="6" t="s">
@@ -4845,7 +4923,7 @@
       <c r="AA12" s="20"/>
       <c r="AB12" s="20"/>
       <c r="AC12" s="20">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>3.9143518518518522E-2</v>
       </c>
       <c r="AD12" s="20">
@@ -4991,21 +5069,21 @@
         <f t="shared" si="19"/>
         <v>NA</v>
       </c>
-      <c r="CQ12" s="31">
+      <c r="CQ12" s="31"/>
+      <c r="CR12" s="70"/>
+      <c r="CS12" s="33" t="str">
+        <f t="shared" si="20"/>
+        <v>NA</v>
+      </c>
+      <c r="CT12" s="31">
         <v>1</v>
       </c>
-      <c r="CR12" s="34">
+      <c r="CU12" s="34">
         <v>2.9953703703703705E-2</v>
       </c>
-      <c r="CS12" s="33">
-        <f t="shared" si="20"/>
+      <c r="CV12" s="33">
+        <f t="shared" si="21"/>
         <v>2.6087962962962966E-2</v>
-      </c>
-      <c r="CT12" s="31"/>
-      <c r="CU12" s="70"/>
-      <c r="CV12" s="33" t="str">
-        <f t="shared" si="21"/>
-        <v>NA</v>
       </c>
       <c r="CW12" s="31"/>
       <c r="CX12" s="70"/>
@@ -5025,51 +5103,57 @@
         <f t="shared" si="24"/>
         <v>NA</v>
       </c>
-      <c r="DF12" s="31">
+      <c r="DF12" s="31"/>
+      <c r="DG12" s="70"/>
+      <c r="DH12" s="33" t="str">
+        <f t="shared" si="25"/>
+        <v>NA</v>
+      </c>
+      <c r="DI12" s="31">
         <v>1</v>
       </c>
-      <c r="DG12" s="70">
+      <c r="DJ12" s="70">
         <v>3.8657407407407408E-3</v>
       </c>
-      <c r="DH12" s="33">
-        <f t="shared" si="25"/>
+      <c r="DK12" s="33">
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="DI12" s="31"/>
-      <c r="DJ12" s="70"/>
-      <c r="DK12" s="33" t="str">
-        <f t="shared" si="26"/>
-        <v>NA</v>
-      </c>
-      <c r="DL12" s="31">
+      <c r="DL12" s="31"/>
+      <c r="DM12" s="70"/>
+      <c r="DN12" s="33" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DO12" s="31">
         <v>1</v>
       </c>
-      <c r="DM12" s="70">
+      <c r="DP12" s="70">
         <v>6.4351851851851853E-3</v>
-      </c>
-      <c r="DN12" s="33">
-        <f t="shared" si="27"/>
-        <v>2.5694444444444445E-3</v>
-      </c>
-      <c r="DO12" s="31">
-        <v>2</v>
-      </c>
-      <c r="DP12" s="70">
-        <v>1.5208333333333334E-2</v>
       </c>
       <c r="DQ12" s="33">
         <f t="shared" si="28"/>
+        <v>2.5694444444444445E-3</v>
+      </c>
+      <c r="DR12" s="31">
+        <v>2</v>
+      </c>
+      <c r="DS12" s="70">
+        <v>1.5208333333333334E-2</v>
+      </c>
+      <c r="DT12" s="33">
+        <f t="shared" si="29"/>
         <v>1.1342592592592593E-2</v>
       </c>
-      <c r="DR12" s="31"/>
-      <c r="DS12" s="70"/>
-      <c r="DT12" s="33" t="str">
-        <f t="shared" si="29"/>
-        <v>NA</v>
-      </c>
-      <c r="DU12" s="35"/>
+      <c r="DU12" s="31"/>
+      <c r="DV12" s="70"/>
+      <c r="DW12" s="33" t="str">
+        <f t="shared" si="30"/>
+        <v>NA</v>
+      </c>
+      <c r="DX12" s="35"/>
     </row>
-    <row r="13" spans="1:125" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:128" x14ac:dyDescent="0.35">
       <c r="A13" s="88" t="s">
         <v>213</v>
       </c>
@@ -5086,7 +5170,7 @@
         <v>2</v>
       </c>
       <c r="F13" s="74" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>L2</v>
       </c>
       <c r="G13" s="5">
@@ -5122,7 +5206,7 @@
         <v>3</v>
       </c>
       <c r="Q13" s="6">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0.11805555555555552</v>
       </c>
       <c r="R13" s="6" t="s">
@@ -5151,7 +5235,7 @@
       <c r="AA13" s="20"/>
       <c r="AB13" s="20"/>
       <c r="AC13" s="20">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>4.4976851851851851E-2</v>
       </c>
       <c r="AD13" s="20">
@@ -5314,25 +5398,25 @@
         <v>NA</v>
       </c>
       <c r="CQ13" s="31"/>
-      <c r="CR13" s="34"/>
+      <c r="CR13" s="32"/>
       <c r="CS13" s="33" t="str">
         <f t="shared" si="20"/>
         <v>NA</v>
       </c>
       <c r="CT13" s="31"/>
-      <c r="CU13" s="32"/>
+      <c r="CU13" s="34"/>
       <c r="CV13" s="33" t="str">
         <f t="shared" si="21"/>
         <v>NA</v>
       </c>
       <c r="CW13" s="31"/>
-      <c r="CX13" s="34"/>
+      <c r="CX13" s="32"/>
       <c r="CY13" s="33" t="str">
         <f t="shared" si="22"/>
         <v>NA</v>
       </c>
       <c r="CZ13" s="31"/>
-      <c r="DA13" s="32"/>
+      <c r="DA13" s="34"/>
       <c r="DB13" s="33" t="str">
         <f t="shared" si="23"/>
         <v>NA</v>
@@ -5343,24 +5427,24 @@
         <f t="shared" si="24"/>
         <v>NA</v>
       </c>
-      <c r="DF13" s="31">
+      <c r="DF13" s="31"/>
+      <c r="DG13" s="32"/>
+      <c r="DH13" s="33" t="str">
+        <f t="shared" si="25"/>
+        <v>NA</v>
+      </c>
+      <c r="DI13" s="31">
         <v>3</v>
       </c>
-      <c r="DG13" s="34">
+      <c r="DJ13" s="34">
         <v>5.6365740740740742E-3</v>
       </c>
-      <c r="DH13" s="33">
-        <f t="shared" si="25"/>
+      <c r="DK13" s="33">
+        <f t="shared" si="26"/>
         <v>8.1018518518518462E-5</v>
       </c>
-      <c r="DI13" s="31"/>
-      <c r="DJ13" s="32"/>
-      <c r="DK13" s="33" t="str">
-        <f t="shared" si="26"/>
-        <v>NA</v>
-      </c>
       <c r="DL13" s="31"/>
-      <c r="DM13" s="34"/>
+      <c r="DM13" s="32"/>
       <c r="DN13" s="33" t="str">
         <f t="shared" si="27"/>
         <v>NA</v>
@@ -5377,9 +5461,15 @@
         <f t="shared" si="29"/>
         <v>NA</v>
       </c>
-      <c r="DU13" s="35"/>
+      <c r="DU13" s="31"/>
+      <c r="DV13" s="34"/>
+      <c r="DW13" s="33" t="str">
+        <f t="shared" si="30"/>
+        <v>NA</v>
+      </c>
+      <c r="DX13" s="35"/>
     </row>
-    <row r="14" spans="1:125" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:128" x14ac:dyDescent="0.35">
       <c r="A14" s="88" t="s">
         <v>213</v>
       </c>
@@ -5396,7 +5486,7 @@
         <v>1</v>
       </c>
       <c r="F14" s="74" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>L1</v>
       </c>
       <c r="G14" s="5">
@@ -5432,7 +5522,7 @@
         <v>4</v>
       </c>
       <c r="Q14" s="6">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0.1159722222222222</v>
       </c>
       <c r="R14" s="6" t="s">
@@ -5461,7 +5551,7 @@
       <c r="AA14" s="20"/>
       <c r="AB14" s="20"/>
       <c r="AC14" s="20">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>6.6909722222222218E-2</v>
       </c>
       <c r="AD14" s="20">
@@ -5471,7 +5561,7 @@
         <v>1.8831018518518518E-2</v>
       </c>
       <c r="AF14" s="20">
-        <f t="shared" ref="AF14:AF22" si="33">AC14-AD14-AE14</f>
+        <f t="shared" ref="AF14:AF22" si="34">AC14-AD14-AE14</f>
         <v>4.1828703703703701E-2</v>
       </c>
       <c r="AG14" s="21">
@@ -5494,25 +5584,25 @@
         <v>2.732638888888889E-2</v>
       </c>
       <c r="AN14" s="33">
-        <f t="shared" ref="AN14:AN22" si="34">IF(AL14=0,"NA",AM14-$AD14)</f>
+        <f t="shared" ref="AN14:AN22" si="35">IF(AL14=0,"NA",AM14-$AD14)</f>
         <v>2.1076388888888891E-2</v>
       </c>
       <c r="AO14" s="31"/>
       <c r="AP14" s="32"/>
       <c r="AQ14" s="33" t="str">
-        <f t="shared" ref="AQ14:AQ22" si="35">IF(AO14=0,"NA",AP14-$AD14)</f>
+        <f t="shared" ref="AQ14:AQ22" si="36">IF(AO14=0,"NA",AP14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="AR14" s="31"/>
       <c r="AS14" s="32"/>
       <c r="AT14" s="33" t="str">
-        <f t="shared" ref="AT14:AT22" si="36">IF(AR14=0,"NA",AS14-$AD14)</f>
+        <f t="shared" ref="AT14:AT22" si="37">IF(AR14=0,"NA",AS14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="AU14" s="31"/>
       <c r="AV14" s="32"/>
       <c r="AW14" s="33" t="str">
-        <f t="shared" ref="AW14:AW22" si="37">IF(AU14=0,"NA",AV14-$AD14)</f>
+        <f t="shared" ref="AW14:AW22" si="38">IF(AU14=0,"NA",AV14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="AX14" s="31"/>
@@ -5530,13 +5620,13 @@
       <c r="BD14" s="31"/>
       <c r="BE14" s="34"/>
       <c r="BF14" s="33" t="str">
-        <f t="shared" ref="BF14:BF22" si="38">IF(BD14=0,"NA",BE14-$AD14)</f>
+        <f t="shared" ref="BF14:BF22" si="39">IF(BD14=0,"NA",BE14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="BG14" s="31"/>
       <c r="BH14" s="32"/>
       <c r="BI14" s="33" t="str">
-        <f t="shared" ref="BI14:BI22" si="39">IF(BG14=0,"NA",BH14-$AD14)</f>
+        <f t="shared" ref="BI14:BI22" si="40">IF(BG14=0,"NA",BH14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="BJ14" s="31">
@@ -5546,7 +5636,7 @@
         <v>2.4201388888888887E-2</v>
       </c>
       <c r="BL14" s="33">
-        <f t="shared" ref="BL14:BL22" si="40">IF(BJ14=0,"NA",BK14-$AD14)</f>
+        <f t="shared" ref="BL14:BL22" si="41">IF(BJ14=0,"NA",BK14-$AD14)</f>
         <v>1.7951388888888888E-2</v>
       </c>
       <c r="BM14" s="31">
@@ -5556,19 +5646,19 @@
         <v>2.4131944444444445E-2</v>
       </c>
       <c r="BO14" s="33">
-        <f t="shared" ref="BO14:BO22" si="41">IF(BM14=0,"NA",BN14-$AD14)</f>
+        <f t="shared" ref="BO14:BO22" si="42">IF(BM14=0,"NA",BN14-$AD14)</f>
         <v>1.7881944444444447E-2</v>
       </c>
       <c r="BP14" s="31"/>
       <c r="BQ14" s="32"/>
       <c r="BR14" s="33" t="str">
-        <f t="shared" ref="BR14:BR22" si="42">IF(BP14=0,"NA",BQ14-$AD14)</f>
+        <f t="shared" ref="BR14:BR22" si="43">IF(BP14=0,"NA",BQ14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="BS14" s="31"/>
       <c r="BT14" s="32"/>
       <c r="BU14" s="33" t="str">
-        <f t="shared" ref="BU14:BU22" si="43">IF(BS14=0,"NA",BT14-$AD14)</f>
+        <f t="shared" ref="BU14:BU22" si="44">IF(BS14=0,"NA",BT14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="BV14" s="31"/>
@@ -5580,7 +5670,7 @@
       <c r="BY14" s="31"/>
       <c r="BZ14" s="34"/>
       <c r="CA14" s="33" t="str">
-        <f t="shared" ref="CA14:CA22" si="44">IF(BY14=0,"NA",BZ14-$AD14)</f>
+        <f t="shared" ref="CA14:CA22" si="45">IF(BY14=0,"NA",BZ14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="CB14" s="31"/>
@@ -5614,13 +5704,13 @@
         <v>NA</v>
       </c>
       <c r="CQ14" s="31"/>
-      <c r="CR14" s="34"/>
+      <c r="CR14" s="32"/>
       <c r="CS14" s="33" t="str">
         <f t="shared" si="20"/>
         <v>NA</v>
       </c>
       <c r="CT14" s="31"/>
-      <c r="CU14" s="32"/>
+      <c r="CU14" s="34"/>
       <c r="CV14" s="33" t="str">
         <f t="shared" si="21"/>
         <v>NA</v>
@@ -5649,41 +5739,47 @@
         <f t="shared" si="25"/>
         <v>NA</v>
       </c>
-      <c r="DI14" s="31">
-        <v>1</v>
-      </c>
-      <c r="DJ14" s="34">
-        <v>3.3831018518518517E-2</v>
-      </c>
-      <c r="DK14" s="33">
+      <c r="DI14" s="31"/>
+      <c r="DJ14" s="32"/>
+      <c r="DK14" s="33" t="str">
         <f t="shared" si="26"/>
-        <v>2.7581018518518519E-2</v>
+        <v>NA</v>
       </c>
       <c r="DL14" s="31">
         <v>1</v>
       </c>
       <c r="DM14" s="34">
-        <v>1.3472222222222222E-2</v>
+        <v>3.3831018518518517E-2</v>
       </c>
       <c r="DN14" s="33">
         <f t="shared" si="27"/>
+        <v>2.7581018518518519E-2</v>
+      </c>
+      <c r="DO14" s="31">
+        <v>1</v>
+      </c>
+      <c r="DP14" s="34">
+        <v>1.3472222222222222E-2</v>
+      </c>
+      <c r="DQ14" s="33">
+        <f t="shared" si="28"/>
         <v>7.2222222222222228E-3</v>
-      </c>
-      <c r="DO14" s="31"/>
-      <c r="DP14" s="32"/>
-      <c r="DQ14" s="33" t="str">
-        <f t="shared" si="28"/>
-        <v>NA</v>
       </c>
       <c r="DR14" s="31"/>
       <c r="DS14" s="32"/>
       <c r="DT14" s="33" t="str">
-        <f t="shared" ref="DT14:DT22" si="45">IF(DR14=0,"NA",DS14-$AD14)</f>
-        <v>NA</v>
-      </c>
-      <c r="DU14" s="35"/>
+        <f t="shared" si="29"/>
+        <v>NA</v>
+      </c>
+      <c r="DU14" s="31"/>
+      <c r="DV14" s="32"/>
+      <c r="DW14" s="33" t="str">
+        <f t="shared" ref="DW14:DW22" si="46">IF(DU14=0,"NA",DV14-$AD14)</f>
+        <v>NA</v>
+      </c>
+      <c r="DX14" s="35"/>
     </row>
-    <row r="15" spans="1:125" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:128" x14ac:dyDescent="0.35">
       <c r="A15" s="88" t="s">
         <v>213</v>
       </c>
@@ -5700,7 +5796,7 @@
         <v>3</v>
       </c>
       <c r="F15" s="74" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>L3</v>
       </c>
       <c r="G15" s="5">
@@ -5736,7 +5832,7 @@
         <v>3</v>
       </c>
       <c r="Q15" s="6">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>9.5833333333333381E-2</v>
       </c>
       <c r="R15" s="6" t="s">
@@ -5765,7 +5861,7 @@
       <c r="AA15" s="20"/>
       <c r="AB15" s="20"/>
       <c r="AC15" s="20">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>5.5925925925925928E-2</v>
       </c>
       <c r="AD15" s="20">
@@ -5775,7 +5871,7 @@
         <v>5.9027777777777776E-3</v>
       </c>
       <c r="AF15" s="20">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>4.5023148148148152E-2</v>
       </c>
       <c r="AG15" s="21">
@@ -5798,7 +5894,7 @@
         <v>3.6354166666666667E-2</v>
       </c>
       <c r="AN15" s="33">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>3.1354166666666669E-2</v>
       </c>
       <c r="AO15" s="31">
@@ -5808,19 +5904,19 @@
         <v>6.1921296296296299E-3</v>
       </c>
       <c r="AQ15" s="33">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>1.1921296296296298E-3</v>
       </c>
       <c r="AR15" s="31"/>
       <c r="AS15" s="32"/>
       <c r="AT15" s="33" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>NA</v>
       </c>
       <c r="AU15" s="31"/>
       <c r="AV15" s="32"/>
       <c r="AW15" s="33" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>NA</v>
       </c>
       <c r="AX15" s="31"/>
@@ -5838,19 +5934,19 @@
       <c r="BD15" s="31"/>
       <c r="BE15" s="32"/>
       <c r="BF15" s="33" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>NA</v>
       </c>
       <c r="BG15" s="31"/>
       <c r="BH15" s="32"/>
       <c r="BI15" s="33" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>NA</v>
       </c>
       <c r="BJ15" s="31"/>
       <c r="BK15" s="34"/>
       <c r="BL15" s="33" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>NA</v>
       </c>
       <c r="BM15" s="31">
@@ -5860,19 +5956,19 @@
         <v>6.9675925925925929E-3</v>
       </c>
       <c r="BO15" s="33">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>1.9675925925925928E-3</v>
       </c>
       <c r="BP15" s="31"/>
       <c r="BQ15" s="32"/>
       <c r="BR15" s="33" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>NA</v>
       </c>
       <c r="BS15" s="31"/>
       <c r="BT15" s="32"/>
       <c r="BU15" s="33" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>NA</v>
       </c>
       <c r="BV15" s="31"/>
@@ -5888,7 +5984,7 @@
         <v>3.8310185185185183E-2</v>
       </c>
       <c r="CA15" s="33">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>3.3310185185185186E-2</v>
       </c>
       <c r="CB15" s="31"/>
@@ -5916,19 +6012,19 @@
         <v>NA</v>
       </c>
       <c r="CN15" s="31"/>
-      <c r="CO15" s="32"/>
+      <c r="CO15" s="70"/>
       <c r="CP15" s="33" t="str">
         <f t="shared" si="19"/>
         <v>NA</v>
       </c>
       <c r="CQ15" s="31"/>
-      <c r="CR15" s="34"/>
+      <c r="CR15" s="32"/>
       <c r="CS15" s="33" t="str">
         <f t="shared" si="20"/>
         <v>NA</v>
       </c>
       <c r="CT15" s="31"/>
-      <c r="CU15" s="32"/>
+      <c r="CU15" s="34"/>
       <c r="CV15" s="33" t="str">
         <f t="shared" si="21"/>
         <v>NA</v>
@@ -5945,61 +6041,67 @@
         <f t="shared" si="23"/>
         <v>NA</v>
       </c>
-      <c r="DC15" s="31">
+      <c r="DC15" s="31"/>
+      <c r="DD15" s="32"/>
+      <c r="DE15" s="33" t="str">
+        <f t="shared" si="24"/>
+        <v>NA</v>
+      </c>
+      <c r="DF15" s="31">
         <v>2</v>
       </c>
-      <c r="DD15" s="70">
+      <c r="DG15" s="70">
         <v>8.0555555555555554E-3</v>
-      </c>
-      <c r="DE15" s="33">
-        <f t="shared" si="24"/>
-        <v>3.0555555555555553E-3</v>
-      </c>
-      <c r="DF15" s="31">
-        <v>1</v>
-      </c>
-      <c r="DG15" s="34">
-        <v>5.9027777777777776E-3</v>
       </c>
       <c r="DH15" s="33">
         <f t="shared" si="25"/>
+        <v>3.0555555555555553E-3</v>
+      </c>
+      <c r="DI15" s="31">
+        <v>1</v>
+      </c>
+      <c r="DJ15" s="34">
+        <v>5.9027777777777776E-3</v>
+      </c>
+      <c r="DK15" s="33">
+        <f t="shared" si="26"/>
         <v>9.0277777777777752E-4</v>
       </c>
-      <c r="DI15" s="31"/>
-      <c r="DJ15" s="70"/>
-      <c r="DK15" s="33" t="str">
-        <f t="shared" si="26"/>
-        <v>NA</v>
-      </c>
       <c r="DL15" s="31"/>
-      <c r="DM15" s="32"/>
+      <c r="DM15" s="70"/>
       <c r="DN15" s="33" t="str">
         <f t="shared" si="27"/>
         <v>NA</v>
       </c>
-      <c r="DO15" s="31">
-        <v>1</v>
-      </c>
-      <c r="DP15" s="34">
-        <v>1.4907407407407407E-2</v>
-      </c>
-      <c r="DQ15" s="33">
+      <c r="DO15" s="31"/>
+      <c r="DP15" s="32"/>
+      <c r="DQ15" s="33" t="str">
         <f t="shared" si="28"/>
-        <v>9.9074074074074064E-3</v>
+        <v>NA</v>
       </c>
       <c r="DR15" s="31">
         <v>1</v>
       </c>
       <c r="DS15" s="34">
+        <v>1.4907407407407407E-2</v>
+      </c>
+      <c r="DT15" s="33">
+        <f t="shared" si="29"/>
+        <v>9.9074074074074064E-3</v>
+      </c>
+      <c r="DU15" s="31">
+        <v>1</v>
+      </c>
+      <c r="DV15" s="34">
         <v>1.1030092592592593E-2</v>
       </c>
-      <c r="DT15" s="33">
-        <f t="shared" si="45"/>
+      <c r="DW15" s="33">
+        <f t="shared" si="46"/>
         <v>6.030092592592593E-3</v>
       </c>
-      <c r="DU15" s="35"/>
+      <c r="DX15" s="35"/>
     </row>
-    <row r="16" spans="1:125" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:128" x14ac:dyDescent="0.35">
       <c r="A16" s="88" t="s">
         <v>213</v>
       </c>
@@ -6016,7 +6118,7 @@
         <v>1</v>
       </c>
       <c r="F16" s="74" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>D1</v>
       </c>
       <c r="G16" s="5">
@@ -6052,7 +6154,7 @@
         <v>6</v>
       </c>
       <c r="Q16" s="6">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>8.8888888888888851E-2</v>
       </c>
       <c r="R16" s="6" t="s">
@@ -6087,7 +6189,7 @@
         <v>1.486111111111111E-2</v>
       </c>
       <c r="AC16" s="20">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>8.9166666666666644E-2</v>
       </c>
       <c r="AD16" s="20">
@@ -6097,7 +6199,7 @@
         <v>4.1111111111111112E-2</v>
       </c>
       <c r="AF16" s="20">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>4.393518518518516E-2</v>
       </c>
       <c r="AG16" s="21">
@@ -6116,25 +6218,25 @@
       <c r="AL16" s="31"/>
       <c r="AM16" s="34"/>
       <c r="AN16" s="33" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>NA</v>
       </c>
       <c r="AO16" s="31"/>
       <c r="AP16" s="34"/>
       <c r="AQ16" s="33" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>NA</v>
       </c>
       <c r="AR16" s="31"/>
       <c r="AS16" s="34"/>
       <c r="AT16" s="33" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>NA</v>
       </c>
       <c r="AU16" s="31"/>
       <c r="AV16" s="34"/>
       <c r="AW16" s="33" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>NA</v>
       </c>
       <c r="AX16" s="31"/>
@@ -6152,19 +6254,19 @@
       <c r="BD16" s="31"/>
       <c r="BE16" s="34"/>
       <c r="BF16" s="33" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>NA</v>
       </c>
       <c r="BG16" s="31"/>
       <c r="BH16" s="34"/>
       <c r="BI16" s="33" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>NA</v>
       </c>
       <c r="BJ16" s="31"/>
       <c r="BK16" s="34"/>
       <c r="BL16" s="56" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>NA</v>
       </c>
       <c r="BM16" s="31">
@@ -6174,13 +6276,13 @@
         <v>4.2476851851851851E-3</v>
       </c>
       <c r="BO16" s="33">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>1.2731481481481448E-4</v>
       </c>
       <c r="BP16" s="31"/>
       <c r="BQ16" s="32"/>
       <c r="BR16" s="33" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>NA</v>
       </c>
       <c r="BS16" s="31">
@@ -6190,7 +6292,7 @@
         <v>9.5486111111111101E-3</v>
       </c>
       <c r="BU16" s="33">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>5.4282407407407396E-3</v>
       </c>
       <c r="BV16" s="31"/>
@@ -6202,7 +6304,7 @@
       <c r="BY16" s="31"/>
       <c r="BZ16" s="56"/>
       <c r="CA16" s="33" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>NA</v>
       </c>
       <c r="CB16" s="31"/>
@@ -6271,41 +6373,47 @@
         <f t="shared" si="25"/>
         <v>NA</v>
       </c>
-      <c r="DI16" s="31">
+      <c r="DI16" s="31"/>
+      <c r="DJ16" s="34"/>
+      <c r="DK16" s="33" t="str">
+        <f t="shared" si="26"/>
+        <v>NA</v>
+      </c>
+      <c r="DL16" s="31">
         <v>1</v>
       </c>
-      <c r="DJ16" s="34">
+      <c r="DM16" s="34">
         <v>6.2847222222222219E-3</v>
       </c>
-      <c r="DK16" s="33">
-        <f t="shared" si="26"/>
+      <c r="DN16" s="33">
+        <f t="shared" si="27"/>
         <v>2.1643518518518513E-3</v>
       </c>
-      <c r="DL16" s="31"/>
-      <c r="DM16" s="34"/>
-      <c r="DN16" s="33" t="str">
-        <f t="shared" si="27"/>
-        <v>NA</v>
-      </c>
-      <c r="DO16" s="31">
+      <c r="DO16" s="31"/>
+      <c r="DP16" s="34"/>
+      <c r="DQ16" s="33" t="str">
+        <f t="shared" si="28"/>
+        <v>NA</v>
+      </c>
+      <c r="DR16" s="31">
         <v>1</v>
       </c>
-      <c r="DP16" s="34">
+      <c r="DS16" s="34">
         <v>4.4444444444444444E-3</v>
       </c>
-      <c r="DQ16" s="33">
-        <f t="shared" si="28"/>
+      <c r="DT16" s="33">
+        <f t="shared" si="29"/>
         <v>3.2407407407407385E-4</v>
       </c>
-      <c r="DR16" s="31"/>
-      <c r="DS16" s="34"/>
-      <c r="DT16" s="33" t="str">
-        <f t="shared" si="45"/>
-        <v>NA</v>
-      </c>
-      <c r="DU16" s="35"/>
+      <c r="DU16" s="31"/>
+      <c r="DV16" s="34"/>
+      <c r="DW16" s="33" t="str">
+        <f t="shared" si="46"/>
+        <v>NA</v>
+      </c>
+      <c r="DX16" s="35"/>
     </row>
-    <row r="17" spans="1:125" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:128" x14ac:dyDescent="0.35">
       <c r="A17" s="88" t="s">
         <v>213</v>
       </c>
@@ -6322,7 +6430,7 @@
         <v>6</v>
       </c>
       <c r="F17" s="74" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>E6</v>
       </c>
       <c r="G17" s="5">
@@ -6358,7 +6466,7 @@
         <v>3</v>
       </c>
       <c r="Q17" s="6">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>5.2083333333333315E-2</v>
       </c>
       <c r="R17" s="6" t="s">
@@ -6389,7 +6497,7 @@
       <c r="AA17" s="20"/>
       <c r="AB17" s="20"/>
       <c r="AC17" s="20">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>4.4826388888888888E-2</v>
       </c>
       <c r="AD17" s="20">
@@ -6397,7 +6505,7 @@
       </c>
       <c r="AE17" s="20"/>
       <c r="AF17" s="20">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>4.1006944444444443E-2</v>
       </c>
       <c r="AG17" s="21">
@@ -6416,25 +6524,25 @@
       <c r="AL17" s="31"/>
       <c r="AM17" s="34"/>
       <c r="AN17" s="33" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>NA</v>
       </c>
       <c r="AO17" s="31"/>
       <c r="AP17" s="34"/>
       <c r="AQ17" s="33" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>NA</v>
       </c>
       <c r="AR17" s="31"/>
       <c r="AS17" s="34"/>
       <c r="AT17" s="33" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>NA</v>
       </c>
       <c r="AU17" s="31"/>
       <c r="AV17" s="34"/>
       <c r="AW17" s="33" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>NA</v>
       </c>
       <c r="AX17" s="31"/>
@@ -6456,37 +6564,37 @@
         <v>1.5416666666666667E-2</v>
       </c>
       <c r="BF17" s="33">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>1.1597222222222222E-2</v>
       </c>
       <c r="BG17" s="31"/>
       <c r="BH17" s="34"/>
       <c r="BI17" s="33" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>NA</v>
       </c>
       <c r="BJ17" s="31"/>
       <c r="BK17" s="34"/>
       <c r="BL17" s="33" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>NA</v>
       </c>
       <c r="BM17" s="31"/>
       <c r="BN17" s="34"/>
       <c r="BO17" s="33" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>NA</v>
       </c>
       <c r="BP17" s="31"/>
       <c r="BQ17" s="34"/>
       <c r="BR17" s="33" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>NA</v>
       </c>
       <c r="BS17" s="31"/>
       <c r="BT17" s="34"/>
       <c r="BU17" s="33" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>NA</v>
       </c>
       <c r="BV17" s="31"/>
@@ -6502,7 +6610,7 @@
         <v>4.0509259259259257E-3</v>
       </c>
       <c r="CA17" s="33">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>2.3148148148148138E-4</v>
       </c>
       <c r="CB17" s="31"/>
@@ -6523,21 +6631,21 @@
         <f t="shared" si="17"/>
         <v>NA</v>
       </c>
-      <c r="CK17" s="31">
+      <c r="CK17" s="31"/>
+      <c r="CL17" s="34"/>
+      <c r="CM17" s="33" t="str">
+        <f t="shared" si="18"/>
+        <v>NA</v>
+      </c>
+      <c r="CN17" s="31">
         <v>1</v>
       </c>
-      <c r="CL17" s="34">
+      <c r="CO17" s="34">
         <v>1.0937500000000001E-2</v>
       </c>
-      <c r="CM17" s="33">
-        <f t="shared" si="18"/>
+      <c r="CP17" s="33">
+        <f t="shared" si="19"/>
         <v>7.1180555555555563E-3</v>
-      </c>
-      <c r="CN17" s="31"/>
-      <c r="CO17" s="34"/>
-      <c r="CP17" s="33" t="str">
-        <f t="shared" si="19"/>
-        <v>NA</v>
       </c>
       <c r="CQ17" s="31"/>
       <c r="CR17" s="34"/>
@@ -6581,31 +6689,37 @@
         <f t="shared" si="26"/>
         <v>NA</v>
       </c>
-      <c r="DL17" s="31">
+      <c r="DL17" s="31"/>
+      <c r="DM17" s="34"/>
+      <c r="DN17" s="33" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DO17" s="31">
         <v>1</v>
       </c>
-      <c r="DM17" s="34">
+      <c r="DP17" s="34">
         <v>4.178240740740741E-3</v>
       </c>
-      <c r="DN17" s="33">
-        <f t="shared" si="27"/>
+      <c r="DQ17" s="33">
+        <f t="shared" si="28"/>
         <v>3.5879629629629673E-4</v>
-      </c>
-      <c r="DO17" s="31"/>
-      <c r="DP17" s="34"/>
-      <c r="DQ17" s="33" t="str">
-        <f t="shared" si="28"/>
-        <v>NA</v>
       </c>
       <c r="DR17" s="31"/>
       <c r="DS17" s="34"/>
       <c r="DT17" s="33" t="str">
-        <f t="shared" si="45"/>
-        <v>NA</v>
-      </c>
-      <c r="DU17" s="35"/>
+        <f t="shared" si="29"/>
+        <v>NA</v>
+      </c>
+      <c r="DU17" s="31"/>
+      <c r="DV17" s="34"/>
+      <c r="DW17" s="33" t="str">
+        <f t="shared" si="46"/>
+        <v>NA</v>
+      </c>
+      <c r="DX17" s="35"/>
     </row>
-    <row r="18" spans="1:125" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:128" x14ac:dyDescent="0.35">
       <c r="A18" s="88" t="s">
         <v>213</v>
       </c>
@@ -6622,7 +6736,7 @@
         <v>2</v>
       </c>
       <c r="F18" s="74" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>D2</v>
       </c>
       <c r="G18" s="5">
@@ -6658,7 +6772,7 @@
         <v>3</v>
       </c>
       <c r="Q18" s="6">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0.1152777777777777</v>
       </c>
       <c r="R18" s="6" t="s">
@@ -6687,7 +6801,7 @@
       <c r="AA18" s="20"/>
       <c r="AB18" s="20"/>
       <c r="AC18" s="20">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>4.4664351851851851E-2</v>
       </c>
       <c r="AD18" s="20">
@@ -6695,7 +6809,7 @@
       </c>
       <c r="AE18" s="20"/>
       <c r="AF18" s="20">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>4.0497685185185185E-2</v>
       </c>
       <c r="AG18" s="21">
@@ -6714,7 +6828,7 @@
       <c r="AL18" s="31"/>
       <c r="AM18" s="34"/>
       <c r="AN18" s="33" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>NA</v>
       </c>
       <c r="AO18" s="31">
@@ -6724,19 +6838,19 @@
         <v>2.3252314814814812E-2</v>
       </c>
       <c r="AQ18" s="33">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>1.9085648148148147E-2</v>
       </c>
       <c r="AR18" s="31"/>
       <c r="AS18" s="34"/>
       <c r="AT18" s="33" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>NA</v>
       </c>
       <c r="AU18" s="31"/>
       <c r="AV18" s="34"/>
       <c r="AW18" s="33" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>NA</v>
       </c>
       <c r="AX18" s="31"/>
@@ -6758,19 +6872,19 @@
         <v>3.1828703703703706E-2</v>
       </c>
       <c r="BF18" s="33">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>2.7662037037037041E-2</v>
       </c>
       <c r="BG18" s="31"/>
       <c r="BH18" s="34"/>
       <c r="BI18" s="33" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>NA</v>
       </c>
       <c r="BJ18" s="31"/>
       <c r="BK18" s="34"/>
       <c r="BL18" s="33" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>NA</v>
       </c>
       <c r="BM18" s="31">
@@ -6780,19 +6894,19 @@
         <v>2.6643518518518521E-2</v>
       </c>
       <c r="BO18" s="33">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>2.2476851851851855E-2</v>
       </c>
       <c r="BP18" s="31"/>
       <c r="BQ18" s="34"/>
       <c r="BR18" s="33" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>NA</v>
       </c>
       <c r="BS18" s="31"/>
       <c r="BT18" s="34"/>
       <c r="BU18" s="33" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>NA</v>
       </c>
       <c r="BV18" s="31">
@@ -6812,7 +6926,7 @@
         <v>3.5891203703703703E-2</v>
       </c>
       <c r="CA18" s="33">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>3.1724537037037037E-2</v>
       </c>
       <c r="CB18" s="31"/>
@@ -6837,21 +6951,21 @@
         <f t="shared" si="17"/>
         <v>2.013888888888889E-2</v>
       </c>
-      <c r="CK18" s="31">
+      <c r="CK18" s="31"/>
+      <c r="CL18" s="34"/>
+      <c r="CM18" s="33" t="str">
+        <f t="shared" si="18"/>
+        <v>NA</v>
+      </c>
+      <c r="CN18" s="31">
         <v>1</v>
       </c>
-      <c r="CL18" s="34">
+      <c r="CO18" s="34">
         <v>1.7534722222222222E-2</v>
       </c>
-      <c r="CM18" s="33">
-        <f t="shared" si="18"/>
+      <c r="CP18" s="33">
+        <f t="shared" si="19"/>
         <v>1.3368055555555557E-2</v>
-      </c>
-      <c r="CN18" s="31"/>
-      <c r="CO18" s="34"/>
-      <c r="CP18" s="33" t="str">
-        <f t="shared" si="19"/>
-        <v>NA</v>
       </c>
       <c r="CQ18" s="31"/>
       <c r="CR18" s="34"/>
@@ -6883,21 +6997,21 @@
         <f t="shared" si="24"/>
         <v>NA</v>
       </c>
-      <c r="DF18" s="31">
+      <c r="DF18" s="31"/>
+      <c r="DG18" s="34"/>
+      <c r="DH18" s="33" t="str">
+        <f t="shared" si="25"/>
+        <v>NA</v>
+      </c>
+      <c r="DI18" s="31">
         <v>4</v>
       </c>
-      <c r="DG18" s="34">
+      <c r="DJ18" s="34">
         <v>1.3587962962962963E-2</v>
       </c>
-      <c r="DH18" s="33">
-        <f t="shared" si="25"/>
+      <c r="DK18" s="33">
+        <f t="shared" si="26"/>
         <v>9.4212962962962957E-3</v>
-      </c>
-      <c r="DI18" s="31"/>
-      <c r="DJ18" s="34"/>
-      <c r="DK18" s="33" t="str">
-        <f t="shared" si="26"/>
-        <v>NA</v>
       </c>
       <c r="DL18" s="31"/>
       <c r="DM18" s="34"/>
@@ -6914,12 +7028,18 @@
       <c r="DR18" s="31"/>
       <c r="DS18" s="34"/>
       <c r="DT18" s="33" t="str">
-        <f t="shared" si="45"/>
-        <v>NA</v>
-      </c>
-      <c r="DU18" s="35"/>
+        <f t="shared" si="29"/>
+        <v>NA</v>
+      </c>
+      <c r="DU18" s="31"/>
+      <c r="DV18" s="34"/>
+      <c r="DW18" s="33" t="str">
+        <f t="shared" si="46"/>
+        <v>NA</v>
+      </c>
+      <c r="DX18" s="35"/>
     </row>
-    <row r="19" spans="1:125" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:128" x14ac:dyDescent="0.35">
       <c r="A19" s="88" t="s">
         <v>213</v>
       </c>
@@ -6936,7 +7056,7 @@
         <v>3</v>
       </c>
       <c r="F19" s="74" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>D3</v>
       </c>
       <c r="G19" s="5">
@@ -6972,7 +7092,7 @@
         <v>3</v>
       </c>
       <c r="Q19" s="6">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="R19" s="6" t="s">
@@ -7001,7 +7121,7 @@
       <c r="AA19" s="20"/>
       <c r="AB19" s="20"/>
       <c r="AC19" s="20">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>4.5949074074074073E-2</v>
       </c>
       <c r="AD19" s="20">
@@ -7009,7 +7129,7 @@
       </c>
       <c r="AE19" s="20"/>
       <c r="AF19" s="20">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>4.1840277777777775E-2</v>
       </c>
       <c r="AG19" s="21">
@@ -7028,7 +7148,7 @@
       <c r="AL19" s="31"/>
       <c r="AM19" s="34"/>
       <c r="AN19" s="33" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>NA</v>
       </c>
       <c r="AO19" s="31">
@@ -7038,19 +7158,19 @@
         <v>9.6064814814814815E-3</v>
       </c>
       <c r="AQ19" s="33">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>5.4976851851851844E-3</v>
       </c>
       <c r="AR19" s="31"/>
       <c r="AS19" s="34"/>
       <c r="AT19" s="33" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>NA</v>
       </c>
       <c r="AU19" s="31"/>
       <c r="AV19" s="34"/>
       <c r="AW19" s="33" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>NA</v>
       </c>
       <c r="AX19" s="31"/>
@@ -7068,19 +7188,19 @@
       <c r="BD19" s="31"/>
       <c r="BE19" s="34"/>
       <c r="BF19" s="33" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>NA</v>
       </c>
       <c r="BG19" s="31"/>
       <c r="BH19" s="34"/>
       <c r="BI19" s="33" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>NA</v>
       </c>
       <c r="BJ19" s="31"/>
       <c r="BK19" s="34"/>
       <c r="BL19" s="33" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>NA</v>
       </c>
       <c r="BM19" s="31">
@@ -7090,19 +7210,19 @@
         <v>5.0925925925925921E-3</v>
       </c>
       <c r="BO19" s="33">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>9.8379629629629511E-4</v>
       </c>
       <c r="BP19" s="31"/>
       <c r="BQ19" s="34"/>
       <c r="BR19" s="33" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>NA</v>
       </c>
       <c r="BS19" s="31"/>
       <c r="BT19" s="34"/>
       <c r="BU19" s="33" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>NA</v>
       </c>
       <c r="BV19" s="31"/>
@@ -7118,7 +7238,7 @@
         <v>1.0231481481481482E-2</v>
       </c>
       <c r="CA19" s="33">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>6.122685185185185E-3</v>
       </c>
       <c r="CB19" s="31"/>
@@ -7139,11 +7259,15 @@
         <f t="shared" si="17"/>
         <v>NA</v>
       </c>
-      <c r="CK19" s="31"/>
-      <c r="CL19" s="34"/>
-      <c r="CM19" s="33" t="str">
+      <c r="CK19" s="31">
+        <v>2</v>
+      </c>
+      <c r="CL19" s="34">
+        <v>3.1956018518518516E-2</v>
+      </c>
+      <c r="CM19" s="33">
         <f t="shared" si="18"/>
-        <v>NA</v>
+        <v>2.7847222222222218E-2</v>
       </c>
       <c r="CN19" s="31"/>
       <c r="CO19" s="34"/>
@@ -7175,21 +7299,21 @@
         <f t="shared" si="23"/>
         <v>NA</v>
       </c>
-      <c r="DC19" s="31">
+      <c r="DC19" s="31"/>
+      <c r="DD19" s="34"/>
+      <c r="DE19" s="33" t="str">
+        <f t="shared" si="24"/>
+        <v>NA</v>
+      </c>
+      <c r="DF19" s="31">
         <v>1</v>
       </c>
-      <c r="DD19" s="34">
+      <c r="DG19" s="34">
         <v>3.5196759259259254E-2</v>
       </c>
-      <c r="DE19" s="33">
-        <f t="shared" si="24"/>
+      <c r="DH19" s="33">
+        <f t="shared" si="25"/>
         <v>3.1087962962962956E-2</v>
-      </c>
-      <c r="DF19" s="31"/>
-      <c r="DG19" s="34"/>
-      <c r="DH19" s="33" t="str">
-        <f t="shared" si="25"/>
-        <v>NA</v>
       </c>
       <c r="DI19" s="31"/>
       <c r="DJ19" s="34"/>
@@ -7197,35 +7321,41 @@
         <f t="shared" si="26"/>
         <v>NA</v>
       </c>
-      <c r="DL19" s="31">
-        <v>1</v>
-      </c>
-      <c r="DM19" s="34">
-        <v>6.7939814814814816E-3</v>
-      </c>
-      <c r="DN19" s="33">
+      <c r="DL19" s="31"/>
+      <c r="DM19" s="34"/>
+      <c r="DN19" s="33" t="str">
         <f t="shared" si="27"/>
-        <v>2.6851851851851846E-3</v>
+        <v>NA</v>
       </c>
       <c r="DO19" s="31">
         <v>1</v>
       </c>
       <c r="DP19" s="34">
-        <v>5.092592592592593E-3</v>
+        <v>6.7939814814814816E-3</v>
       </c>
       <c r="DQ19" s="33">
         <f t="shared" si="28"/>
+        <v>2.6851851851851846E-3</v>
+      </c>
+      <c r="DR19" s="31">
+        <v>1</v>
+      </c>
+      <c r="DS19" s="34">
+        <v>5.092592592592593E-3</v>
+      </c>
+      <c r="DT19" s="33">
+        <f t="shared" si="29"/>
         <v>9.8379629629629598E-4</v>
       </c>
-      <c r="DR19" s="31"/>
-      <c r="DS19" s="34"/>
-      <c r="DT19" s="33" t="str">
-        <f t="shared" si="45"/>
-        <v>NA</v>
-      </c>
-      <c r="DU19" s="35"/>
+      <c r="DU19" s="31"/>
+      <c r="DV19" s="34"/>
+      <c r="DW19" s="33" t="str">
+        <f t="shared" si="46"/>
+        <v>NA</v>
+      </c>
+      <c r="DX19" s="35"/>
     </row>
-    <row r="20" spans="1:125" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:128" x14ac:dyDescent="0.35">
       <c r="A20" s="88" t="s">
         <v>213</v>
       </c>
@@ -7242,7 +7372,7 @@
         <v>2</v>
       </c>
       <c r="F20" s="74" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>E2</v>
       </c>
       <c r="G20" s="5">
@@ -7278,7 +7408,7 @@
         <v>3</v>
       </c>
       <c r="Q20" s="6">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>7.3611111111111183E-2</v>
       </c>
       <c r="R20" s="6" t="s">
@@ -7307,7 +7437,7 @@
       <c r="AA20" s="20"/>
       <c r="AB20" s="20"/>
       <c r="AC20" s="20">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>5.3576388888888889E-2</v>
       </c>
       <c r="AD20" s="20">
@@ -7317,7 +7447,7 @@
         <v>6.9444444444444441E-3</v>
       </c>
       <c r="AF20" s="20">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>4.2638888888888893E-2</v>
       </c>
       <c r="AG20" s="21">
@@ -7336,7 +7466,7 @@
       <c r="AL20" s="31"/>
       <c r="AM20" s="34"/>
       <c r="AN20" s="33" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>NA</v>
       </c>
       <c r="AO20" s="31">
@@ -7346,19 +7476,19 @@
         <v>2.344907407407407E-2</v>
       </c>
       <c r="AQ20" s="33">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>1.9456018518518515E-2</v>
       </c>
       <c r="AR20" s="31"/>
       <c r="AS20" s="34"/>
       <c r="AT20" s="33" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>NA</v>
       </c>
       <c r="AU20" s="31"/>
       <c r="AV20" s="34"/>
       <c r="AW20" s="33" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>NA</v>
       </c>
       <c r="AX20" s="31"/>
@@ -7376,19 +7506,19 @@
       <c r="BD20" s="31"/>
       <c r="BE20" s="34"/>
       <c r="BF20" s="33" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>NA</v>
       </c>
       <c r="BG20" s="31"/>
       <c r="BH20" s="34"/>
       <c r="BI20" s="33" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>NA</v>
       </c>
       <c r="BJ20" s="31"/>
       <c r="BK20" s="34"/>
       <c r="BL20" s="33" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>NA</v>
       </c>
       <c r="BM20" s="31">
@@ -7398,19 +7528,19 @@
         <v>3.9930555555555561E-3</v>
       </c>
       <c r="BO20" s="33">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="BP20" s="31"/>
       <c r="BQ20" s="34"/>
       <c r="BR20" s="33" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>NA</v>
       </c>
       <c r="BS20" s="31"/>
       <c r="BT20" s="34"/>
       <c r="BU20" s="33" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>NA</v>
       </c>
       <c r="BV20" s="31"/>
@@ -7422,7 +7552,7 @@
       <c r="BY20" s="31"/>
       <c r="BZ20" s="34"/>
       <c r="CA20" s="33" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>NA</v>
       </c>
       <c r="CB20" s="31"/>
@@ -7479,61 +7609,67 @@
         <f t="shared" si="23"/>
         <v>NA</v>
       </c>
-      <c r="DC20" s="31">
+      <c r="DC20" s="31"/>
+      <c r="DD20" s="34"/>
+      <c r="DE20" s="33" t="str">
+        <f t="shared" si="24"/>
+        <v>NA</v>
+      </c>
+      <c r="DF20" s="31">
         <v>1</v>
       </c>
-      <c r="DD20" s="34">
+      <c r="DG20" s="34">
         <v>1.6793981481481483E-2</v>
       </c>
-      <c r="DE20" s="33">
-        <f t="shared" si="24"/>
+      <c r="DH20" s="33">
+        <f t="shared" si="25"/>
         <v>1.2800925925925927E-2</v>
       </c>
-      <c r="DF20" s="31"/>
-      <c r="DG20" s="34"/>
-      <c r="DH20" s="33" t="str">
-        <f t="shared" si="25"/>
-        <v>NA</v>
-      </c>
-      <c r="DI20" s="31">
+      <c r="DI20" s="31"/>
+      <c r="DJ20" s="34"/>
+      <c r="DK20" s="33" t="str">
+        <f t="shared" si="26"/>
+        <v>NA</v>
+      </c>
+      <c r="DL20" s="31">
         <v>3</v>
       </c>
-      <c r="DJ20" s="34">
+      <c r="DM20" s="34">
         <v>9.4444444444444445E-3</v>
       </c>
-      <c r="DK20" s="33">
-        <f t="shared" si="26"/>
+      <c r="DN20" s="33">
+        <f t="shared" si="27"/>
         <v>5.4513888888888884E-3</v>
       </c>
-      <c r="DL20" s="31"/>
-      <c r="DM20" s="34"/>
-      <c r="DN20" s="33" t="str">
-        <f t="shared" si="27"/>
-        <v>NA</v>
-      </c>
-      <c r="DO20" s="31">
-        <v>1</v>
-      </c>
-      <c r="DP20" s="34">
-        <v>2.3090277777777779E-2</v>
-      </c>
-      <c r="DQ20" s="33">
+      <c r="DO20" s="31"/>
+      <c r="DP20" s="34"/>
+      <c r="DQ20" s="33" t="str">
         <f t="shared" si="28"/>
-        <v>1.9097222222222224E-2</v>
+        <v>NA</v>
       </c>
       <c r="DR20" s="31">
         <v>1</v>
       </c>
       <c r="DS20" s="34">
+        <v>2.3090277777777779E-2</v>
+      </c>
+      <c r="DT20" s="33">
+        <f t="shared" si="29"/>
+        <v>1.9097222222222224E-2</v>
+      </c>
+      <c r="DU20" s="31">
+        <v>1</v>
+      </c>
+      <c r="DV20" s="34">
         <v>6.9791666666666665E-3</v>
       </c>
-      <c r="DT20" s="33">
-        <f t="shared" si="45"/>
+      <c r="DW20" s="33">
+        <f t="shared" si="46"/>
         <v>2.9861111111111104E-3</v>
       </c>
-      <c r="DU20" s="35"/>
+      <c r="DX20" s="35"/>
     </row>
-    <row r="21" spans="1:125" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:128" x14ac:dyDescent="0.35">
       <c r="A21" s="88" t="s">
         <v>213</v>
       </c>
@@ -7550,7 +7686,7 @@
         <v>3</v>
       </c>
       <c r="F21" s="74" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>E3</v>
       </c>
       <c r="G21" s="5">
@@ -7586,7 +7722,7 @@
         <v>3</v>
       </c>
       <c r="Q21" s="6">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>6.8055555555555536E-2</v>
       </c>
       <c r="R21" s="6" t="s">
@@ -7615,7 +7751,7 @@
       <c r="AA21" s="77"/>
       <c r="AB21" s="77"/>
       <c r="AC21" s="20">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>3.3865740740740738E-2</v>
       </c>
       <c r="AD21" s="78">
@@ -7623,7 +7759,7 @@
       </c>
       <c r="AE21" s="78"/>
       <c r="AF21" s="20">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>2.9699074074074072E-2</v>
       </c>
       <c r="AG21" s="21">
@@ -7644,25 +7780,25 @@
       <c r="AL21" s="31"/>
       <c r="AM21" s="32"/>
       <c r="AN21" s="33" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>NA</v>
       </c>
       <c r="AO21" s="31"/>
       <c r="AP21" s="32"/>
       <c r="AQ21" s="33" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>NA</v>
       </c>
       <c r="AR21" s="31"/>
       <c r="AS21" s="32"/>
       <c r="AT21" s="33" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>NA</v>
       </c>
       <c r="AU21" s="31"/>
       <c r="AV21" s="32"/>
       <c r="AW21" s="33" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>NA</v>
       </c>
       <c r="AX21" s="31"/>
@@ -7680,19 +7816,19 @@
       <c r="BD21" s="31"/>
       <c r="BE21" s="34"/>
       <c r="BF21" s="33" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>NA</v>
       </c>
       <c r="BG21" s="31"/>
       <c r="BH21" s="32"/>
       <c r="BI21" s="33" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>NA</v>
       </c>
       <c r="BJ21" s="31"/>
       <c r="BK21" s="32"/>
       <c r="BL21" s="33" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>NA</v>
       </c>
       <c r="BM21" s="31">
@@ -7702,19 +7838,19 @@
         <v>3.2858796296296296E-2</v>
       </c>
       <c r="BO21" s="33">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>2.869212962962963E-2</v>
       </c>
       <c r="BP21" s="31"/>
       <c r="BQ21" s="32"/>
       <c r="BR21" s="33" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>NA</v>
       </c>
       <c r="BS21" s="31"/>
       <c r="BT21" s="32"/>
       <c r="BU21" s="33" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>NA</v>
       </c>
       <c r="BV21" s="31"/>
@@ -7730,7 +7866,7 @@
         <v>2.1956018518518517E-2</v>
       </c>
       <c r="CA21" s="33">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>1.7789351851851851E-2</v>
       </c>
       <c r="CB21" s="31"/>
@@ -7751,30 +7887,30 @@
         <f t="shared" si="17"/>
         <v>NA</v>
       </c>
-      <c r="CK21" s="31">
+      <c r="CK21" s="31"/>
+      <c r="CL21" s="32"/>
+      <c r="CM21" s="33" t="str">
+        <f t="shared" si="18"/>
+        <v>NA</v>
+      </c>
+      <c r="CN21" s="31">
         <v>2</v>
       </c>
-      <c r="CL21" s="34">
+      <c r="CO21" s="34">
         <v>1.7615740740740741E-2</v>
       </c>
-      <c r="CM21" s="33">
-        <f t="shared" si="18"/>
+      <c r="CP21" s="33">
+        <f t="shared" si="19"/>
         <v>1.3449074074074075E-2</v>
       </c>
-      <c r="CN21" s="31"/>
-      <c r="CO21" s="32"/>
-      <c r="CP21" s="33" t="str">
-        <f t="shared" si="19"/>
-        <v>NA</v>
-      </c>
       <c r="CQ21" s="31"/>
-      <c r="CR21" s="34"/>
+      <c r="CR21" s="32"/>
       <c r="CS21" s="33" t="str">
         <f t="shared" si="20"/>
         <v>NA</v>
       </c>
       <c r="CT21" s="31"/>
-      <c r="CU21" s="32"/>
+      <c r="CU21" s="34"/>
       <c r="CV21" s="33" t="str">
         <f t="shared" si="21"/>
         <v>NA</v>
@@ -7792,7 +7928,7 @@
         <v>NA</v>
       </c>
       <c r="DC21" s="31"/>
-      <c r="DD21" s="56"/>
+      <c r="DD21" s="32"/>
       <c r="DE21" s="33" t="str">
         <f t="shared" si="24"/>
         <v>NA</v>
@@ -7809,31 +7945,37 @@
         <f t="shared" si="26"/>
         <v>NA</v>
       </c>
-      <c r="DL21" s="31">
+      <c r="DL21" s="31"/>
+      <c r="DM21" s="56"/>
+      <c r="DN21" s="33" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DO21" s="31">
         <v>1</v>
       </c>
-      <c r="DM21" s="56">
+      <c r="DP21" s="56">
         <v>1.6805555555555556E-2</v>
       </c>
-      <c r="DN21" s="33">
-        <f t="shared" si="27"/>
+      <c r="DQ21" s="33">
+        <f t="shared" si="28"/>
         <v>1.263888888888889E-2</v>
-      </c>
-      <c r="DO21" s="31"/>
-      <c r="DP21" s="56"/>
-      <c r="DQ21" s="33" t="str">
-        <f t="shared" si="28"/>
-        <v>NA</v>
       </c>
       <c r="DR21" s="31"/>
       <c r="DS21" s="56"/>
       <c r="DT21" s="33" t="str">
-        <f t="shared" si="45"/>
-        <v>NA</v>
-      </c>
-      <c r="DU21" s="35"/>
+        <f t="shared" si="29"/>
+        <v>NA</v>
+      </c>
+      <c r="DU21" s="31"/>
+      <c r="DV21" s="56"/>
+      <c r="DW21" s="33" t="str">
+        <f t="shared" si="46"/>
+        <v>NA</v>
+      </c>
+      <c r="DX21" s="35"/>
     </row>
-    <row r="22" spans="1:125" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:128" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A22" s="94" t="s">
         <v>213</v>
       </c>
@@ -7850,7 +7992,7 @@
         <v>1</v>
       </c>
       <c r="F22" s="75" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>E1</v>
       </c>
       <c r="G22" s="11">
@@ -7886,7 +8028,7 @@
         <v>3</v>
       </c>
       <c r="Q22" s="12">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>5.2083333333333259E-2</v>
       </c>
       <c r="R22" s="12" t="s">
@@ -7915,7 +8057,7 @@
       <c r="AA22" s="69"/>
       <c r="AB22" s="69"/>
       <c r="AC22" s="23">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>5.289351851851852E-2</v>
       </c>
       <c r="AD22" s="80">
@@ -7925,7 +8067,7 @@
         <v>1.1388888888888888E-2</v>
       </c>
       <c r="AF22" s="23">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>3.6180555555555556E-2</v>
       </c>
       <c r="AG22" s="24">
@@ -7944,25 +8086,25 @@
       <c r="AL22" s="38"/>
       <c r="AM22" s="40"/>
       <c r="AN22" s="41" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>NA</v>
       </c>
       <c r="AO22" s="38"/>
       <c r="AP22" s="40"/>
       <c r="AQ22" s="41" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>NA</v>
       </c>
       <c r="AR22" s="38"/>
       <c r="AS22" s="82"/>
       <c r="AT22" s="41" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>NA</v>
       </c>
       <c r="AU22" s="38"/>
       <c r="AV22" s="82"/>
       <c r="AW22" s="41" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>NA</v>
       </c>
       <c r="AX22" s="38"/>
@@ -7984,13 +8126,13 @@
       <c r="BD22" s="38"/>
       <c r="BE22" s="40"/>
       <c r="BF22" s="41" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>NA</v>
       </c>
       <c r="BG22" s="38"/>
       <c r="BH22" s="82"/>
       <c r="BI22" s="41" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>NA</v>
       </c>
       <c r="BJ22" s="38">
@@ -8000,7 +8142,7 @@
         <v>8.1018518518518514E-3</v>
       </c>
       <c r="BL22" s="41">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>2.7777777777777766E-3</v>
       </c>
       <c r="BM22" s="38">
@@ -8010,19 +8152,19 @@
         <v>5.37037037037037E-3</v>
       </c>
       <c r="BO22" s="41">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>4.6296296296295149E-5</v>
       </c>
       <c r="BP22" s="38"/>
       <c r="BQ22" s="82"/>
       <c r="BR22" s="41" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>NA</v>
       </c>
       <c r="BS22" s="38"/>
       <c r="BT22" s="82"/>
       <c r="BU22" s="41" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>NA</v>
       </c>
       <c r="BV22" s="38"/>
@@ -8038,7 +8180,7 @@
         <v>3.0173611111111113E-2</v>
       </c>
       <c r="CA22" s="41">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>2.4849537037037038E-2</v>
       </c>
       <c r="CB22" s="38"/>
@@ -8064,29 +8206,29 @@
         <v>0</v>
       </c>
       <c r="CK22" s="38"/>
-      <c r="CL22" s="82"/>
+      <c r="CL22" s="40"/>
       <c r="CM22" s="41" t="str">
         <f t="shared" si="18"/>
         <v>NA</v>
       </c>
-      <c r="CN22" s="38">
+      <c r="CN22" s="38"/>
+      <c r="CO22" s="82"/>
+      <c r="CP22" s="41" t="str">
+        <f t="shared" si="19"/>
+        <v>NA</v>
+      </c>
+      <c r="CQ22" s="38">
         <v>1</v>
       </c>
-      <c r="CO22" s="40">
+      <c r="CR22" s="40">
         <v>2.1331018518518517E-2</v>
       </c>
-      <c r="CP22" s="41">
-        <f t="shared" si="19"/>
+      <c r="CS22" s="41">
+        <f t="shared" si="20"/>
         <v>1.6006944444444442E-2</v>
       </c>
-      <c r="CQ22" s="38"/>
-      <c r="CR22" s="40"/>
-      <c r="CS22" s="41" t="str">
-        <f t="shared" si="20"/>
-        <v>NA</v>
-      </c>
       <c r="CT22" s="38"/>
-      <c r="CU22" s="82"/>
+      <c r="CU22" s="40"/>
       <c r="CV22" s="41" t="str">
         <f t="shared" si="21"/>
         <v>NA</v>
@@ -8098,7 +8240,7 @@
         <v>NA</v>
       </c>
       <c r="CZ22" s="38"/>
-      <c r="DA22" s="40"/>
+      <c r="DA22" s="82"/>
       <c r="DB22" s="41" t="str">
         <f t="shared" si="23"/>
         <v>NA</v>
@@ -8115,43 +8257,49 @@
         <f t="shared" si="25"/>
         <v>NA</v>
       </c>
-      <c r="DI22" s="38">
+      <c r="DI22" s="38"/>
+      <c r="DJ22" s="40"/>
+      <c r="DK22" s="41" t="str">
+        <f t="shared" si="26"/>
+        <v>NA</v>
+      </c>
+      <c r="DL22" s="38">
         <v>1</v>
       </c>
-      <c r="DJ22" s="40">
+      <c r="DM22" s="40">
         <v>2.042824074074074E-2</v>
-      </c>
-      <c r="DK22" s="41">
-        <f t="shared" si="26"/>
-        <v>1.5104166666666665E-2</v>
-      </c>
-      <c r="DL22" s="38">
-        <v>3</v>
-      </c>
-      <c r="DM22" s="40">
-        <v>5.324074074074074E-3</v>
       </c>
       <c r="DN22" s="41">
         <f t="shared" si="27"/>
-        <v>-8.6736173798840355E-19</v>
+        <v>1.5104166666666665E-2</v>
       </c>
       <c r="DO22" s="38">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="DP22" s="40">
-        <v>3.259259259259259E-2</v>
+        <v>5.324074074074074E-3</v>
       </c>
       <c r="DQ22" s="41">
         <f t="shared" si="28"/>
+        <v>-8.6736173798840355E-19</v>
+      </c>
+      <c r="DR22" s="38">
+        <v>1</v>
+      </c>
+      <c r="DS22" s="40">
+        <v>3.259259259259259E-2</v>
+      </c>
+      <c r="DT22" s="41">
+        <f t="shared" si="29"/>
         <v>2.7268518518518515E-2</v>
       </c>
-      <c r="DR22" s="38"/>
-      <c r="DS22" s="40"/>
-      <c r="DT22" s="41" t="str">
-        <f t="shared" si="45"/>
-        <v>NA</v>
-      </c>
-      <c r="DU22" s="39"/>
+      <c r="DU22" s="38"/>
+      <c r="DV22" s="40"/>
+      <c r="DW22" s="41" t="str">
+        <f t="shared" si="46"/>
+        <v>NA</v>
+      </c>
+      <c r="DX22" s="39"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/URUVS/Datasheets/URUV/04.2024/April_RecordingData.xlsx
+++ b/URUVS/Datasheets/URUV/04.2024/April_RecordingData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\swulfing\Documents\GitHub\TanakekeProject\URUVS\Datasheets\URUV\04.2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D71F8297-70A8-412A-804D-281A7AAE8AF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73266193-4EE9-4EBD-9952-1F27C936594C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43095" yWindow="-9285" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RecordingData_04.2024" sheetId="2" r:id="rId1"/>
@@ -713,9 +713,6 @@
     <t>T1_ULAR</t>
   </si>
   <si>
-    <t>MAXNSHRIMP</t>
-  </si>
-  <si>
     <t>TIME_1STSHRIMP</t>
   </si>
   <si>
@@ -729,6 +726,9 @@
   </si>
   <si>
     <t>T1_FISHO</t>
+  </si>
+  <si>
+    <t>MAXN_SHRIMP</t>
   </si>
 </sst>
 </file>
@@ -1729,13 +1729,13 @@
         <v>140</v>
       </c>
       <c r="CK1" s="81" t="s">
+        <v>226</v>
+      </c>
+      <c r="CL1" s="27" t="s">
         <v>227</v>
       </c>
-      <c r="CL1" s="27" t="s">
+      <c r="CM1" s="59" t="s">
         <v>228</v>
-      </c>
-      <c r="CM1" s="59" t="s">
-        <v>229</v>
       </c>
       <c r="CN1" s="81" t="s">
         <v>123</v>
@@ -1828,13 +1828,13 @@
         <v>220</v>
       </c>
       <c r="DR1" s="81" t="s">
+        <v>229</v>
+      </c>
+      <c r="DS1" s="27" t="s">
         <v>224</v>
       </c>
-      <c r="DS1" s="27" t="s">
+      <c r="DT1" s="59" t="s">
         <v>225</v>
-      </c>
-      <c r="DT1" s="59" t="s">
-        <v>226</v>
       </c>
       <c r="DU1" s="81" t="s">
         <v>221</v>
@@ -2057,11 +2057,11 @@
         <v>1</v>
       </c>
       <c r="CF2" s="56">
-        <v>2.1270833333333332</v>
+        <v>3.5451388888888886E-2</v>
       </c>
       <c r="CG2" s="33">
         <f t="shared" ref="CG2:CG22" si="16">IF(CE2=0,"NA",CF2-$AD2)</f>
-        <v>2.1232870370370369</v>
+        <v>3.1655092592592589E-2</v>
       </c>
       <c r="CH2" s="58"/>
       <c r="CI2" s="71"/>
